--- a/datosSesionesPruebaMedias.xlsx
+++ b/datosSesionesPruebaMedias.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\hlocal\C_TFG\Datos\Mision Colombia-20260209T150018Z-3-001\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\hlocal\C_TFG\Datos\Mision Colombia-20260209T150018Z-3-001\jsonToCsv_TFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27C73C29-2CD4-4758-9F1B-8CCE24663F1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5651021-4444-4F33-89E3-47BFCB2921D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,164 +19,7 @@
   <definedNames>
     <definedName name="_xlchart.v1.0" hidden="1">Sheet1!$B$2:$B$76</definedName>
     <definedName name="_xlchart.v1.1" hidden="1">Sheet1!$K$1</definedName>
-    <definedName name="_xlchart.v1.10" hidden="1">Sheet1!$A$10:$G$10</definedName>
-    <definedName name="_xlchart.v1.100" hidden="1">Sheet1!$H$25:$U$25</definedName>
-    <definedName name="_xlchart.v1.101" hidden="1">Sheet1!$H$26:$U$26</definedName>
-    <definedName name="_xlchart.v1.102" hidden="1">Sheet1!$H$27:$U$27</definedName>
-    <definedName name="_xlchart.v1.103" hidden="1">Sheet1!$H$28:$U$28</definedName>
-    <definedName name="_xlchart.v1.104" hidden="1">Sheet1!$H$29:$U$29</definedName>
-    <definedName name="_xlchart.v1.105" hidden="1">Sheet1!$H$2:$U$2</definedName>
-    <definedName name="_xlchart.v1.106" hidden="1">Sheet1!$H$30:$U$30</definedName>
-    <definedName name="_xlchart.v1.107" hidden="1">Sheet1!$H$31:$U$31</definedName>
-    <definedName name="_xlchart.v1.108" hidden="1">Sheet1!$H$32:$U$32</definedName>
-    <definedName name="_xlchart.v1.109" hidden="1">Sheet1!$H$33:$U$33</definedName>
-    <definedName name="_xlchart.v1.11" hidden="1">Sheet1!$A$11:$G$11</definedName>
-    <definedName name="_xlchart.v1.110" hidden="1">Sheet1!$H$34:$U$34</definedName>
-    <definedName name="_xlchart.v1.111" hidden="1">Sheet1!$H$35:$U$35</definedName>
-    <definedName name="_xlchart.v1.112" hidden="1">Sheet1!$H$36:$U$36</definedName>
-    <definedName name="_xlchart.v1.113" hidden="1">Sheet1!$H$37:$U$37</definedName>
-    <definedName name="_xlchart.v1.114" hidden="1">Sheet1!$H$38:$U$38</definedName>
-    <definedName name="_xlchart.v1.115" hidden="1">Sheet1!$H$39:$U$39</definedName>
-    <definedName name="_xlchart.v1.116" hidden="1">Sheet1!$H$3:$U$3</definedName>
-    <definedName name="_xlchart.v1.117" hidden="1">Sheet1!$H$40:$U$40</definedName>
-    <definedName name="_xlchart.v1.118" hidden="1">Sheet1!$H$41:$U$41</definedName>
-    <definedName name="_xlchart.v1.119" hidden="1">Sheet1!$H$42:$U$42</definedName>
-    <definedName name="_xlchart.v1.12" hidden="1">Sheet1!$A$12:$G$12</definedName>
-    <definedName name="_xlchart.v1.120" hidden="1">Sheet1!$H$43:$U$43</definedName>
-    <definedName name="_xlchart.v1.121" hidden="1">Sheet1!$H$44:$U$44</definedName>
-    <definedName name="_xlchart.v1.122" hidden="1">Sheet1!$H$45:$U$45</definedName>
-    <definedName name="_xlchart.v1.123" hidden="1">Sheet1!$H$46:$U$46</definedName>
-    <definedName name="_xlchart.v1.124" hidden="1">Sheet1!$H$47:$U$47</definedName>
-    <definedName name="_xlchart.v1.125" hidden="1">Sheet1!$H$48:$U$48</definedName>
-    <definedName name="_xlchart.v1.126" hidden="1">Sheet1!$H$49:$U$49</definedName>
-    <definedName name="_xlchart.v1.127" hidden="1">Sheet1!$H$4:$U$4</definedName>
-    <definedName name="_xlchart.v1.128" hidden="1">Sheet1!$H$50:$U$50</definedName>
-    <definedName name="_xlchart.v1.129" hidden="1">Sheet1!$H$51:$U$51</definedName>
-    <definedName name="_xlchart.v1.13" hidden="1">Sheet1!$A$13:$G$13</definedName>
-    <definedName name="_xlchart.v1.130" hidden="1">Sheet1!$H$52:$U$52</definedName>
-    <definedName name="_xlchart.v1.131" hidden="1">Sheet1!$H$53:$U$53</definedName>
-    <definedName name="_xlchart.v1.132" hidden="1">Sheet1!$H$54:$U$54</definedName>
-    <definedName name="_xlchart.v1.133" hidden="1">Sheet1!$H$55:$U$55</definedName>
-    <definedName name="_xlchart.v1.134" hidden="1">Sheet1!$H$56:$U$56</definedName>
-    <definedName name="_xlchart.v1.135" hidden="1">Sheet1!$H$57:$U$57</definedName>
-    <definedName name="_xlchart.v1.136" hidden="1">Sheet1!$H$58:$U$58</definedName>
-    <definedName name="_xlchart.v1.137" hidden="1">Sheet1!$H$59:$U$59</definedName>
-    <definedName name="_xlchart.v1.138" hidden="1">Sheet1!$H$5:$U$5</definedName>
-    <definedName name="_xlchart.v1.139" hidden="1">Sheet1!$H$60:$U$60</definedName>
-    <definedName name="_xlchart.v1.14" hidden="1">Sheet1!$A$14:$G$14</definedName>
-    <definedName name="_xlchart.v1.140" hidden="1">Sheet1!$H$61:$U$61</definedName>
-    <definedName name="_xlchart.v1.141" hidden="1">Sheet1!$H$62:$U$62</definedName>
-    <definedName name="_xlchart.v1.142" hidden="1">Sheet1!$H$63:$U$63</definedName>
-    <definedName name="_xlchart.v1.143" hidden="1">Sheet1!$H$64:$U$64</definedName>
-    <definedName name="_xlchart.v1.144" hidden="1">Sheet1!$H$65:$U$65</definedName>
-    <definedName name="_xlchart.v1.145" hidden="1">Sheet1!$H$66:$U$66</definedName>
-    <definedName name="_xlchart.v1.146" hidden="1">Sheet1!$H$67:$U$67</definedName>
-    <definedName name="_xlchart.v1.147" hidden="1">Sheet1!$H$68:$U$68</definedName>
-    <definedName name="_xlchart.v1.148" hidden="1">Sheet1!$H$69:$U$69</definedName>
-    <definedName name="_xlchart.v1.149" hidden="1">Sheet1!$H$6:$U$6</definedName>
-    <definedName name="_xlchart.v1.15" hidden="1">Sheet1!$A$15:$G$15</definedName>
-    <definedName name="_xlchart.v1.150" hidden="1">Sheet1!$H$70:$U$70</definedName>
-    <definedName name="_xlchart.v1.151" hidden="1">Sheet1!$H$71:$U$71</definedName>
-    <definedName name="_xlchart.v1.152" hidden="1">Sheet1!$H$72:$U$72</definedName>
-    <definedName name="_xlchart.v1.153" hidden="1">Sheet1!$H$73:$U$73</definedName>
-    <definedName name="_xlchart.v1.154" hidden="1">Sheet1!$H$74:$U$74</definedName>
-    <definedName name="_xlchart.v1.155" hidden="1">Sheet1!$H$75:$U$75</definedName>
-    <definedName name="_xlchart.v1.156" hidden="1">Sheet1!$H$76:$U$76</definedName>
-    <definedName name="_xlchart.v1.157" hidden="1">Sheet1!$H$7:$U$7</definedName>
-    <definedName name="_xlchart.v1.158" hidden="1">Sheet1!$H$8:$U$8</definedName>
-    <definedName name="_xlchart.v1.159" hidden="1">Sheet1!$H$9:$U$9</definedName>
-    <definedName name="_xlchart.v1.16" hidden="1">Sheet1!$A$16:$G$16</definedName>
-    <definedName name="_xlchart.v1.17" hidden="1">Sheet1!$A$17:$G$17</definedName>
-    <definedName name="_xlchart.v1.18" hidden="1">Sheet1!$A$18:$G$18</definedName>
-    <definedName name="_xlchart.v1.19" hidden="1">Sheet1!$A$19:$G$19</definedName>
     <definedName name="_xlchart.v1.2" hidden="1">Sheet1!$K$2:$K$76</definedName>
-    <definedName name="_xlchart.v1.20" hidden="1">Sheet1!$A$20:$G$20</definedName>
-    <definedName name="_xlchart.v1.21" hidden="1">Sheet1!$A$21:$G$21</definedName>
-    <definedName name="_xlchart.v1.22" hidden="1">Sheet1!$A$22:$G$22</definedName>
-    <definedName name="_xlchart.v1.23" hidden="1">Sheet1!$A$23:$G$23</definedName>
-    <definedName name="_xlchart.v1.24" hidden="1">Sheet1!$A$24:$G$24</definedName>
-    <definedName name="_xlchart.v1.25" hidden="1">Sheet1!$A$25:$G$25</definedName>
-    <definedName name="_xlchart.v1.26" hidden="1">Sheet1!$A$26:$G$26</definedName>
-    <definedName name="_xlchart.v1.27" hidden="1">Sheet1!$A$27:$G$27</definedName>
-    <definedName name="_xlchart.v1.28" hidden="1">Sheet1!$A$28:$G$28</definedName>
-    <definedName name="_xlchart.v1.29" hidden="1">Sheet1!$A$29:$G$29</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">Sheet1!$B$2:$B$76</definedName>
-    <definedName name="_xlchart.v1.30" hidden="1">Sheet1!$A$2:$G$2</definedName>
-    <definedName name="_xlchart.v1.31" hidden="1">Sheet1!$A$30:$G$30</definedName>
-    <definedName name="_xlchart.v1.32" hidden="1">Sheet1!$A$31:$G$31</definedName>
-    <definedName name="_xlchart.v1.33" hidden="1">Sheet1!$A$32:$G$32</definedName>
-    <definedName name="_xlchart.v1.34" hidden="1">Sheet1!$A$33:$G$33</definedName>
-    <definedName name="_xlchart.v1.35" hidden="1">Sheet1!$A$34:$G$34</definedName>
-    <definedName name="_xlchart.v1.36" hidden="1">Sheet1!$A$35:$G$35</definedName>
-    <definedName name="_xlchart.v1.37" hidden="1">Sheet1!$A$36:$G$36</definedName>
-    <definedName name="_xlchart.v1.38" hidden="1">Sheet1!$A$37:$G$37</definedName>
-    <definedName name="_xlchart.v1.39" hidden="1">Sheet1!$A$38:$G$38</definedName>
-    <definedName name="_xlchart.v1.4" hidden="1">Sheet1!$K$1</definedName>
-    <definedName name="_xlchart.v1.40" hidden="1">Sheet1!$A$39:$G$39</definedName>
-    <definedName name="_xlchart.v1.41" hidden="1">Sheet1!$A$3:$G$3</definedName>
-    <definedName name="_xlchart.v1.42" hidden="1">Sheet1!$A$40:$G$40</definedName>
-    <definedName name="_xlchart.v1.43" hidden="1">Sheet1!$A$41:$G$41</definedName>
-    <definedName name="_xlchart.v1.44" hidden="1">Sheet1!$A$42:$G$42</definedName>
-    <definedName name="_xlchart.v1.45" hidden="1">Sheet1!$A$43:$G$43</definedName>
-    <definedName name="_xlchart.v1.46" hidden="1">Sheet1!$A$44:$G$44</definedName>
-    <definedName name="_xlchart.v1.47" hidden="1">Sheet1!$A$45:$G$45</definedName>
-    <definedName name="_xlchart.v1.48" hidden="1">Sheet1!$A$46:$G$46</definedName>
-    <definedName name="_xlchart.v1.49" hidden="1">Sheet1!$A$47:$G$47</definedName>
-    <definedName name="_xlchart.v1.5" hidden="1">Sheet1!$K$2:$K$76</definedName>
-    <definedName name="_xlchart.v1.50" hidden="1">Sheet1!$A$48:$G$48</definedName>
-    <definedName name="_xlchart.v1.51" hidden="1">Sheet1!$A$49:$G$49</definedName>
-    <definedName name="_xlchart.v1.52" hidden="1">Sheet1!$A$4:$G$4</definedName>
-    <definedName name="_xlchart.v1.53" hidden="1">Sheet1!$A$50:$G$50</definedName>
-    <definedName name="_xlchart.v1.54" hidden="1">Sheet1!$A$51:$G$51</definedName>
-    <definedName name="_xlchart.v1.55" hidden="1">Sheet1!$A$52:$G$52</definedName>
-    <definedName name="_xlchart.v1.56" hidden="1">Sheet1!$A$53:$G$53</definedName>
-    <definedName name="_xlchart.v1.57" hidden="1">Sheet1!$A$54:$G$54</definedName>
-    <definedName name="_xlchart.v1.58" hidden="1">Sheet1!$A$55:$G$55</definedName>
-    <definedName name="_xlchart.v1.59" hidden="1">Sheet1!$A$56:$G$56</definedName>
-    <definedName name="_xlchart.v1.6" hidden="1">Hoja1!$A$1:$B$1</definedName>
-    <definedName name="_xlchart.v1.60" hidden="1">Sheet1!$A$57:$G$57</definedName>
-    <definedName name="_xlchart.v1.61" hidden="1">Sheet1!$A$58:$G$58</definedName>
-    <definedName name="_xlchart.v1.62" hidden="1">Sheet1!$A$59:$G$59</definedName>
-    <definedName name="_xlchart.v1.63" hidden="1">Sheet1!$A$5:$G$5</definedName>
-    <definedName name="_xlchart.v1.64" hidden="1">Sheet1!$A$60:$G$60</definedName>
-    <definedName name="_xlchart.v1.65" hidden="1">Sheet1!$A$61:$G$61</definedName>
-    <definedName name="_xlchart.v1.66" hidden="1">Sheet1!$A$62:$G$62</definedName>
-    <definedName name="_xlchart.v1.67" hidden="1">Sheet1!$A$63:$G$63</definedName>
-    <definedName name="_xlchart.v1.68" hidden="1">Sheet1!$A$64:$G$64</definedName>
-    <definedName name="_xlchart.v1.69" hidden="1">Sheet1!$A$65:$G$65</definedName>
-    <definedName name="_xlchart.v1.7" hidden="1">Hoja1!$A$2:$B$2</definedName>
-    <definedName name="_xlchart.v1.70" hidden="1">Sheet1!$A$66:$G$66</definedName>
-    <definedName name="_xlchart.v1.71" hidden="1">Sheet1!$A$67:$G$67</definedName>
-    <definedName name="_xlchart.v1.72" hidden="1">Sheet1!$A$68:$G$68</definedName>
-    <definedName name="_xlchart.v1.73" hidden="1">Sheet1!$A$69:$G$69</definedName>
-    <definedName name="_xlchart.v1.74" hidden="1">Sheet1!$A$6:$G$6</definedName>
-    <definedName name="_xlchart.v1.75" hidden="1">Sheet1!$A$70:$G$70</definedName>
-    <definedName name="_xlchart.v1.76" hidden="1">Sheet1!$A$71:$G$71</definedName>
-    <definedName name="_xlchart.v1.77" hidden="1">Sheet1!$A$72:$G$72</definedName>
-    <definedName name="_xlchart.v1.78" hidden="1">Sheet1!$A$73:$G$73</definedName>
-    <definedName name="_xlchart.v1.79" hidden="1">Sheet1!$A$74:$G$74</definedName>
-    <definedName name="_xlchart.v1.8" hidden="1">Hoja1!$A$3:$B$3</definedName>
-    <definedName name="_xlchart.v1.80" hidden="1">Sheet1!$A$75:$G$75</definedName>
-    <definedName name="_xlchart.v1.81" hidden="1">Sheet1!$A$76:$G$76</definedName>
-    <definedName name="_xlchart.v1.82" hidden="1">Sheet1!$A$7:$G$7</definedName>
-    <definedName name="_xlchart.v1.83" hidden="1">Sheet1!$A$8:$G$8</definedName>
-    <definedName name="_xlchart.v1.84" hidden="1">Sheet1!$A$9:$G$9</definedName>
-    <definedName name="_xlchart.v1.85" hidden="1">Sheet1!$H$10:$U$10</definedName>
-    <definedName name="_xlchart.v1.86" hidden="1">Sheet1!$H$11:$U$11</definedName>
-    <definedName name="_xlchart.v1.87" hidden="1">Sheet1!$H$12:$U$12</definedName>
-    <definedName name="_xlchart.v1.88" hidden="1">Sheet1!$H$13:$U$13</definedName>
-    <definedName name="_xlchart.v1.89" hidden="1">Sheet1!$H$14:$U$14</definedName>
-    <definedName name="_xlchart.v1.9" hidden="1">Hoja1!$A$4:$B$4</definedName>
-    <definedName name="_xlchart.v1.90" hidden="1">Sheet1!$H$15:$U$15</definedName>
-    <definedName name="_xlchart.v1.91" hidden="1">Sheet1!$H$16:$U$16</definedName>
-    <definedName name="_xlchart.v1.92" hidden="1">Sheet1!$H$17:$U$17</definedName>
-    <definedName name="_xlchart.v1.93" hidden="1">Sheet1!$H$18:$U$18</definedName>
-    <definedName name="_xlchart.v1.94" hidden="1">Sheet1!$H$19:$U$19</definedName>
-    <definedName name="_xlchart.v1.95" hidden="1">Sheet1!$H$20:$U$20</definedName>
-    <definedName name="_xlchart.v1.96" hidden="1">Sheet1!$H$21:$U$21</definedName>
-    <definedName name="_xlchart.v1.97" hidden="1">Sheet1!$H$22:$U$22</definedName>
-    <definedName name="_xlchart.v1.98" hidden="1">Sheet1!$H$23:$U$23</definedName>
-    <definedName name="_xlchart.v1.99" hidden="1">Sheet1!$H$24:$U$24</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -196,7 +39,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -218,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="206">
   <si>
     <t>ID</t>
   </si>
@@ -812,6 +655,30 @@
   </si>
   <si>
     <t>Stdev errores tiempo excedido</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Media duracion</t>
+  </si>
+  <si>
+    <t>Stdev duracion</t>
+  </si>
+  <si>
+    <t>Media n niveles</t>
+  </si>
+  <si>
+    <t>Stdev n niveles</t>
+  </si>
+  <si>
+    <t>Media n intentos</t>
+  </si>
+  <si>
+    <t>Stdev n intentos</t>
+  </si>
+  <si>
+    <t>Media completados</t>
+  </si>
+  <si>
+    <t>Stdev completados</t>
   </si>
 </sst>
 </file>
@@ -876,6 +743,20 @@
   </cellStyles>
   <dxfs count="3">
     <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -901,20 +782,6 @@
         </right>
         <top/>
         <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color auto="1"/>
-        </top>
       </border>
     </dxf>
   </dxfs>
@@ -1578,8 +1445,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="6629400" y="9577387"/>
-              <a:ext cx="4572000" cy="2743200"/>
+              <a:off x="6810375" y="9196387"/>
+              <a:ext cx="4720590" cy="2636520"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -1613,7 +1480,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{AD8B7A24-8C82-432D-8F40-107C6140EF70}" name="data" displayName="data" ref="A1:U76" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="1" tableBorderDxfId="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{AD8B7A24-8C82-432D-8F40-107C6140EF70}" name="data" displayName="data" ref="A1:U76" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="1" tableBorderDxfId="0">
   <autoFilter ref="A1:U76" xr:uid="{AD8B7A24-8C82-432D-8F40-107C6140EF70}"/>
   <tableColumns count="21">
     <tableColumn id="1" xr3:uid="{E9C60595-13C0-4ABA-BDC8-21DAAB7F3D42}" name="ID"/>
@@ -1928,30 +1795,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:U76"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="14.28515625" customWidth="1"/>
-    <col min="4" max="4" width="15.28515625" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" customWidth="1"/>
-    <col min="6" max="6" width="15.140625" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" customWidth="1"/>
+    <col min="3" max="3" width="14.33203125" customWidth="1"/>
+    <col min="4" max="4" width="15.33203125" customWidth="1"/>
+    <col min="5" max="5" width="14.88671875" customWidth="1"/>
+    <col min="6" max="6" width="15.109375" customWidth="1"/>
+    <col min="7" max="7" width="14.33203125" customWidth="1"/>
     <col min="8" max="8" width="18" customWidth="1"/>
-    <col min="9" max="9" width="19.28515625" customWidth="1"/>
-    <col min="10" max="10" width="18.28515625" customWidth="1"/>
-    <col min="11" max="11" width="18.42578125" customWidth="1"/>
-    <col min="12" max="12" width="24.140625" customWidth="1"/>
+    <col min="9" max="9" width="19.33203125" customWidth="1"/>
+    <col min="10" max="10" width="18.33203125" customWidth="1"/>
+    <col min="11" max="11" width="18.44140625" customWidth="1"/>
+    <col min="12" max="12" width="24.109375" customWidth="1"/>
     <col min="13" max="13" width="18" customWidth="1"/>
-    <col min="14" max="14" width="15.85546875" customWidth="1"/>
-    <col min="15" max="15" width="26.5703125" customWidth="1"/>
-    <col min="16" max="16" width="20.42578125" customWidth="1"/>
-    <col min="17" max="17" width="18.28515625" customWidth="1"/>
-    <col min="18" max="18" width="17.85546875" customWidth="1"/>
-    <col min="19" max="19" width="19.28515625" customWidth="1"/>
-    <col min="20" max="20" width="34.7109375" customWidth="1"/>
-    <col min="21" max="21" width="33.140625" customWidth="1"/>
+    <col min="14" max="14" width="15.88671875" customWidth="1"/>
+    <col min="15" max="15" width="26.5546875" customWidth="1"/>
+    <col min="16" max="16" width="20.44140625" customWidth="1"/>
+    <col min="17" max="17" width="18.33203125" customWidth="1"/>
+    <col min="18" max="18" width="17.88671875" customWidth="1"/>
+    <col min="19" max="19" width="19.33203125" customWidth="1"/>
+    <col min="20" max="20" width="34.6640625" customWidth="1"/>
+    <col min="21" max="21" width="33.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2016,7 +1883,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>10</v>
       </c>
@@ -2081,7 +1948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>10</v>
       </c>
@@ -2146,7 +2013,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>11</v>
       </c>
@@ -2211,7 +2078,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>11</v>
       </c>
@@ -2276,7 +2143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>13</v>
       </c>
@@ -2341,7 +2208,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>13</v>
       </c>
@@ -2406,7 +2273,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>15</v>
       </c>
@@ -2471,7 +2338,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>16</v>
       </c>
@@ -2536,7 +2403,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>16</v>
       </c>
@@ -2601,7 +2468,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>17</v>
       </c>
@@ -2666,7 +2533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>17</v>
       </c>
@@ -2731,7 +2598,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>18</v>
       </c>
@@ -2796,7 +2663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>18</v>
       </c>
@@ -2861,7 +2728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>18</v>
       </c>
@@ -2926,7 +2793,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>19</v>
       </c>
@@ -2991,7 +2858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>19</v>
       </c>
@@ -3056,7 +2923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>1</v>
       </c>
@@ -3121,7 +2988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>21</v>
       </c>
@@ -3186,7 +3053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>21</v>
       </c>
@@ -3251,7 +3118,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>22</v>
       </c>
@@ -3316,7 +3183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>22</v>
       </c>
@@ -3381,7 +3248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>23</v>
       </c>
@@ -3446,7 +3313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>24</v>
       </c>
@@ -3511,7 +3378,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
@@ -3576,7 +3443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
@@ -3641,7 +3508,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>25</v>
       </c>
@@ -3706,7 +3573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>26</v>
       </c>
@@ -3771,7 +3638,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>26</v>
       </c>
@@ -3836,7 +3703,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>27</v>
       </c>
@@ -3901,7 +3768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>27</v>
       </c>
@@ -3966,7 +3833,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>2</v>
       </c>
@@ -4031,7 +3898,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>30</v>
       </c>
@@ -4096,7 +3963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>30</v>
       </c>
@@ -4161,7 +4028,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>31</v>
       </c>
@@ -4226,7 +4093,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>31</v>
       </c>
@@ -4291,7 +4158,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>32</v>
       </c>
@@ -4356,7 +4223,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>32</v>
       </c>
@@ -4421,7 +4288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>33</v>
       </c>
@@ -4486,7 +4353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>34</v>
       </c>
@@ -4551,7 +4418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>35</v>
       </c>
@@ -4616,7 +4483,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>35</v>
       </c>
@@ -4681,7 +4548,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>37</v>
       </c>
@@ -4746,7 +4613,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>37</v>
       </c>
@@ -4811,7 +4678,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>3</v>
       </c>
@@ -4876,7 +4743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>3</v>
       </c>
@@ -4941,7 +4808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>41</v>
       </c>
@@ -5006,7 +4873,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>42</v>
       </c>
@@ -5071,7 +4938,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>43</v>
       </c>
@@ -5136,7 +5003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>43</v>
       </c>
@@ -5201,7 +5068,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="51" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>44</v>
       </c>
@@ -5266,7 +5133,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>45</v>
       </c>
@@ -5331,7 +5198,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>45</v>
       </c>
@@ -5396,7 +5263,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="54" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>46</v>
       </c>
@@ -5461,7 +5328,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="55" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>47</v>
       </c>
@@ -5526,7 +5393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>47</v>
       </c>
@@ -5591,7 +5458,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="57" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>48</v>
       </c>
@@ -5656,7 +5523,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>4</v>
       </c>
@@ -5721,7 +5588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>50</v>
       </c>
@@ -5786,7 +5653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>51</v>
       </c>
@@ -5851,7 +5718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>51</v>
       </c>
@@ -5916,7 +5783,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>52</v>
       </c>
@@ -5981,7 +5848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>53</v>
       </c>
@@ -6046,7 +5913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>5</v>
       </c>
@@ -6111,7 +5978,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="65" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>65</v>
       </c>
@@ -6176,7 +6043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>6</v>
       </c>
@@ -6241,7 +6108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>6</v>
       </c>
@@ -6306,7 +6173,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>6</v>
       </c>
@@ -6371,7 +6238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>7</v>
       </c>
@@ -6436,7 +6303,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>7</v>
       </c>
@@ -6501,7 +6368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>7</v>
       </c>
@@ -6566,7 +6433,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>8</v>
       </c>
@@ -6631,7 +6498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>8</v>
       </c>
@@ -6696,7 +6563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>8</v>
       </c>
@@ -6761,7 +6628,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="75" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>9</v>
       </c>
@@ -6826,7 +6693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>9</v>
       </c>
@@ -6902,14 +6769,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0EE1E7D-EAFC-4A2F-AF1A-E8C144B15E47}">
-  <dimension ref="A1:AB4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AB9"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.7109375" customWidth="1"/>
+    <col min="3" max="3" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -6995,7 +6862,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -7108,7 +6975,7 @@
         <v>1.2830803929426717</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -7221,7 +7088,7 @@
         <v>0.4330127018922193</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -7332,6 +7199,134 @@
       <c r="AB4" cm="1">
         <f t="array" ref="AB4">_xlfn.STDEV.P(IF(data[Sesion]=A4,data[Num errores por tiempo excedido]))</f>
         <v>1.8129241852622839</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="C6" t="s">
+        <v>198</v>
+      </c>
+      <c r="D6" t="s">
+        <v>199</v>
+      </c>
+      <c r="E6" t="s">
+        <v>200</v>
+      </c>
+      <c r="F6" t="s">
+        <v>201</v>
+      </c>
+      <c r="G6" t="s">
+        <v>202</v>
+      </c>
+      <c r="H6" t="s">
+        <v>203</v>
+      </c>
+      <c r="I6" t="s">
+        <v>204</v>
+      </c>
+      <c r="J6" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="C7">
+        <f>AVERAGEIF(data[Sesion],A2,data[Tiempo duracion])</f>
+        <v>1391.2371627906978</v>
+      </c>
+      <c r="D7" cm="1">
+        <f t="array" ref="D7">_xlfn.STDEV.P(IF(data[Sesion]=A2,data[Tiempo duracion]))</f>
+        <v>752.30981030420571</v>
+      </c>
+      <c r="E7">
+        <f>AVERAGEIF(data[Sesion],A2,data[Num niveles])</f>
+        <v>2.5116279069767442</v>
+      </c>
+      <c r="F7" cm="1">
+        <f t="array" ref="F7">_xlfn.STDEV.P(IF(data[Sesion]=A2,data[Num niveles]))</f>
+        <v>1.2270610193742251</v>
+      </c>
+      <c r="G7">
+        <f>AVERAGEIF(data[Sesion],A2,data[Num intentos])</f>
+        <v>7.9767441860465116</v>
+      </c>
+      <c r="H7" cm="1">
+        <f t="array" ref="H7">_xlfn.STDEV.P(IF(data[Sesion]=A2,data[Num intentos]))</f>
+        <v>3.2456652458390702</v>
+      </c>
+      <c r="I7">
+        <f>AVERAGEIF(data[Sesion],A2,data[Completados])</f>
+        <v>0.81395348837209303</v>
+      </c>
+      <c r="J7" cm="1">
+        <f t="array" ref="J7">_xlfn.STDEV.P(IF(data[Sesion]=A2,data[Completados]))</f>
+        <v>1.2985826612384852</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="C8">
+        <f>AVERAGEIF(data[Sesion],A3,data[Tiempo duracion])</f>
+        <v>548.99350000000004</v>
+      </c>
+      <c r="D8" cm="1">
+        <f t="array" ref="D8">_xlfn.STDEV.P(IF(data[Sesion]=A3,data[Tiempo duracion]))</f>
+        <v>399.60607282578923</v>
+      </c>
+      <c r="E8">
+        <f>AVERAGEIF(data[Sesion],A3,data[Num niveles])</f>
+        <v>1.25</v>
+      </c>
+      <c r="F8" cm="1">
+        <f t="array" ref="F8">_xlfn.STDEV.P(IF(data[Sesion]=A3,data[Num niveles]))</f>
+        <v>0.4330127018922193</v>
+      </c>
+      <c r="G8">
+        <f>AVERAGEIF(data[Sesion],A3,data[Num intentos])</f>
+        <v>3.5</v>
+      </c>
+      <c r="H8" cm="1">
+        <f t="array" ref="H8">_xlfn.STDEV.P(IF(data[Sesion]=A3,data[Num intentos]))</f>
+        <v>2.8722813232690143</v>
+      </c>
+      <c r="I8">
+        <f>AVERAGEIF(data[Sesion],A3,data[Completados])</f>
+        <v>0.5</v>
+      </c>
+      <c r="J8" cm="1">
+        <f t="array" ref="J8">_xlfn.STDEV.P(IF(data[Sesion]=A3,data[Completados]))</f>
+        <v>0.8660254037844386</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="C9">
+        <f>AVERAGEIF(data[Sesion],A4,data[Tiempo duracion])</f>
+        <v>1634.4362592592588</v>
+      </c>
+      <c r="D9" cm="1">
+        <f t="array" ref="D9">_xlfn.STDEV.P(IF(data[Sesion]=A4,data[Tiempo duracion]))</f>
+        <v>3285.1750964942448</v>
+      </c>
+      <c r="E9">
+        <f>AVERAGEIF(data[Sesion],A4,data[Num niveles])</f>
+        <v>3.5555555555555554</v>
+      </c>
+      <c r="F9" cm="1">
+        <f t="array" ref="F9">_xlfn.STDEV.P(IF(data[Sesion]=A4,data[Num niveles]))</f>
+        <v>1.1653431646335017</v>
+      </c>
+      <c r="G9">
+        <f>AVERAGEIF(data[Sesion],A4,data[Num intentos])</f>
+        <v>11.518518518518519</v>
+      </c>
+      <c r="H9" cm="1">
+        <f t="array" ref="H9">_xlfn.STDEV.P(IF(data[Sesion]=A4,data[Num intentos]))</f>
+        <v>5.3980131486835754</v>
+      </c>
+      <c r="I9">
+        <f>AVERAGEIF(data[Sesion],A4,data[Completados])</f>
+        <v>1.7037037037037037</v>
+      </c>
+      <c r="J9" cm="1">
+        <f t="array" ref="J9">_xlfn.STDEV.P(IF(data[Sesion]=A4,data[Completados]))</f>
+        <v>1.4609691054308163</v>
       </c>
     </row>
   </sheetData>

--- a/datosSesionesPruebaMedias.xlsx
+++ b/datosSesionesPruebaMedias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\hlocal\C_TFG\Datos\Mision Colombia-20260209T150018Z-3-001\jsonToCsv_TFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5651021-4444-4F33-89E3-47BFCB2921D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0B1FC6B-4C10-4AFD-BFC7-710FB22D9234}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1400,16 +1400,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>485775</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>52387</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>386715</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>82867</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>128587</xdr:rowOff>
+      <xdr:colOff>1259205</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>159067</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" Requires="cx1">
@@ -1445,7 +1445,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="6810375" y="9196387"/>
+              <a:off x="7945755" y="9409747"/>
               <a:ext cx="4720590" cy="2636520"/>
             </a:xfrm>
             <a:prstGeom prst="rect">

--- a/datosSesionesPruebaMedias.xlsx
+++ b/datosSesionesPruebaMedias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\hlocal\C_TFG\Datos\Mision Colombia-20260209T150018Z-3-001\jsonToCsv_TFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0B1FC6B-4C10-4AFD-BFC7-710FB22D9234}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FF0F5E0-8184-4DB2-B3C6-C90CCA2DC0F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -279,9 +279,6 @@
     <t>14:57:25.697</t>
   </si>
   <si>
-    <t>10:55:38.321</t>
-  </si>
-  <si>
     <t>14:57:14.599</t>
   </si>
   <si>
@@ -679,6 +676,9 @@
   </si>
   <si>
     <t>Stdev completados</t>
+  </si>
+  <si>
+    <t>15:42:14.394</t>
   </si>
 </sst>
 </file>
@@ -3519,7 +3519,7 @@
         <v>3</v>
       </c>
       <c r="D27">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -3528,10 +3528,10 @@
         <v>71</v>
       </c>
       <c r="G27" t="s">
-        <v>72</v>
+        <v>205</v>
       </c>
       <c r="H27">
-        <v>-14507.376</v>
+        <v>2688.6970000000001</v>
       </c>
       <c r="I27">
         <v>48</v>
@@ -3590,10 +3590,10 @@
         <v>0</v>
       </c>
       <c r="F28" t="s">
+        <v>72</v>
+      </c>
+      <c r="G28" t="s">
         <v>73</v>
-      </c>
-      <c r="G28" t="s">
-        <v>74</v>
       </c>
       <c r="H28">
         <v>1721.7370000000001</v>
@@ -3655,10 +3655,10 @@
         <v>0</v>
       </c>
       <c r="F29" t="s">
+        <v>74</v>
+      </c>
+      <c r="G29" t="s">
         <v>75</v>
-      </c>
-      <c r="G29" t="s">
-        <v>76</v>
       </c>
       <c r="H29">
         <v>2568.2379999999998</v>
@@ -3720,10 +3720,10 @@
         <v>0</v>
       </c>
       <c r="F30" t="s">
+        <v>76</v>
+      </c>
+      <c r="G30" t="s">
         <v>77</v>
-      </c>
-      <c r="G30" t="s">
-        <v>78</v>
       </c>
       <c r="H30">
         <v>924.42499999999995</v>
@@ -3785,10 +3785,10 @@
         <v>0</v>
       </c>
       <c r="F31" t="s">
+        <v>78</v>
+      </c>
+      <c r="G31" t="s">
         <v>79</v>
-      </c>
-      <c r="G31" t="s">
-        <v>80</v>
       </c>
       <c r="H31">
         <v>2739.4659999999999</v>
@@ -3850,10 +3850,10 @@
         <v>1</v>
       </c>
       <c r="F32" t="s">
+        <v>80</v>
+      </c>
+      <c r="G32" t="s">
         <v>81</v>
-      </c>
-      <c r="G32" t="s">
-        <v>82</v>
       </c>
       <c r="H32">
         <v>2110.4520000000002</v>
@@ -3915,10 +3915,10 @@
         <v>3</v>
       </c>
       <c r="F33" t="s">
+        <v>82</v>
+      </c>
+      <c r="G33" t="s">
         <v>83</v>
-      </c>
-      <c r="G33" t="s">
-        <v>84</v>
       </c>
       <c r="H33">
         <v>1783.269</v>
@@ -3980,10 +3980,10 @@
         <v>4</v>
       </c>
       <c r="F34" t="s">
+        <v>84</v>
+      </c>
+      <c r="G34" t="s">
         <v>85</v>
-      </c>
-      <c r="G34" t="s">
-        <v>86</v>
       </c>
       <c r="H34">
         <v>2483.3719999999998</v>
@@ -4045,10 +4045,10 @@
         <v>0</v>
       </c>
       <c r="F35" t="s">
+        <v>86</v>
+      </c>
+      <c r="G35" t="s">
         <v>87</v>
-      </c>
-      <c r="G35" t="s">
-        <v>88</v>
       </c>
       <c r="H35">
         <v>1807.5719999999999</v>
@@ -4110,10 +4110,10 @@
         <v>0</v>
       </c>
       <c r="F36" t="s">
+        <v>88</v>
+      </c>
+      <c r="G36" t="s">
         <v>89</v>
-      </c>
-      <c r="G36" t="s">
-        <v>90</v>
       </c>
       <c r="H36">
         <v>3250.85</v>
@@ -4175,10 +4175,10 @@
         <v>2</v>
       </c>
       <c r="F37" t="s">
+        <v>90</v>
+      </c>
+      <c r="G37" t="s">
         <v>91</v>
-      </c>
-      <c r="G37" t="s">
-        <v>92</v>
       </c>
       <c r="H37">
         <v>1931.99</v>
@@ -4240,10 +4240,10 @@
         <v>3</v>
       </c>
       <c r="F38" t="s">
+        <v>92</v>
+      </c>
+      <c r="G38" t="s">
         <v>93</v>
-      </c>
-      <c r="G38" t="s">
-        <v>94</v>
       </c>
       <c r="H38">
         <v>781.06899999999996</v>
@@ -4305,10 +4305,10 @@
         <v>0</v>
       </c>
       <c r="F39" t="s">
+        <v>94</v>
+      </c>
+      <c r="G39" t="s">
         <v>95</v>
-      </c>
-      <c r="G39" t="s">
-        <v>96</v>
       </c>
       <c r="H39">
         <v>1462.616</v>
@@ -4370,10 +4370,10 @@
         <v>0</v>
       </c>
       <c r="F40" t="s">
+        <v>96</v>
+      </c>
+      <c r="G40" t="s">
         <v>97</v>
-      </c>
-      <c r="G40" t="s">
-        <v>98</v>
       </c>
       <c r="H40">
         <v>1267.6220000000001</v>
@@ -4435,10 +4435,10 @@
         <v>0</v>
       </c>
       <c r="F41" t="s">
+        <v>98</v>
+      </c>
+      <c r="G41" t="s">
         <v>99</v>
-      </c>
-      <c r="G41" t="s">
-        <v>100</v>
       </c>
       <c r="H41">
         <v>1885.146</v>
@@ -4500,10 +4500,10 @@
         <v>0</v>
       </c>
       <c r="F42" t="s">
+        <v>100</v>
+      </c>
+      <c r="G42" t="s">
         <v>101</v>
-      </c>
-      <c r="G42" t="s">
-        <v>102</v>
       </c>
       <c r="H42">
         <v>3121.1120000000001</v>
@@ -4565,10 +4565,10 @@
         <v>1</v>
       </c>
       <c r="F43" t="s">
+        <v>102</v>
+      </c>
+      <c r="G43" t="s">
         <v>103</v>
-      </c>
-      <c r="G43" t="s">
-        <v>104</v>
       </c>
       <c r="H43">
         <v>1967.492</v>
@@ -4630,10 +4630,10 @@
         <v>1</v>
       </c>
       <c r="F44" t="s">
+        <v>104</v>
+      </c>
+      <c r="G44" t="s">
         <v>105</v>
-      </c>
-      <c r="G44" t="s">
-        <v>106</v>
       </c>
       <c r="H44">
         <v>1566.9590000000001</v>
@@ -4695,10 +4695,10 @@
         <v>0</v>
       </c>
       <c r="F45" t="s">
+        <v>106</v>
+      </c>
+      <c r="G45" t="s">
         <v>107</v>
-      </c>
-      <c r="G45" t="s">
-        <v>108</v>
       </c>
       <c r="H45">
         <v>7.0000000000000001E-3</v>
@@ -4760,10 +4760,10 @@
         <v>0</v>
       </c>
       <c r="F46" t="s">
+        <v>108</v>
+      </c>
+      <c r="G46" t="s">
         <v>109</v>
-      </c>
-      <c r="G46" t="s">
-        <v>110</v>
       </c>
       <c r="H46">
         <v>379.57600000000002</v>
@@ -4825,10 +4825,10 @@
         <v>1</v>
       </c>
       <c r="F47" t="s">
+        <v>110</v>
+      </c>
+      <c r="G47" t="s">
         <v>111</v>
-      </c>
-      <c r="G47" t="s">
-        <v>112</v>
       </c>
       <c r="H47">
         <v>1186.057</v>
@@ -4890,10 +4890,10 @@
         <v>0</v>
       </c>
       <c r="F48" t="s">
+        <v>112</v>
+      </c>
+      <c r="G48" t="s">
         <v>113</v>
-      </c>
-      <c r="G48" t="s">
-        <v>114</v>
       </c>
       <c r="H48">
         <v>1128.722</v>
@@ -4955,10 +4955,10 @@
         <v>0</v>
       </c>
       <c r="F49" t="s">
+        <v>114</v>
+      </c>
+      <c r="G49" t="s">
         <v>115</v>
-      </c>
-      <c r="G49" t="s">
-        <v>116</v>
       </c>
       <c r="H49">
         <v>1324.854</v>
@@ -5020,10 +5020,10 @@
         <v>1</v>
       </c>
       <c r="F50" t="s">
+        <v>116</v>
+      </c>
+      <c r="G50" t="s">
         <v>117</v>
-      </c>
-      <c r="G50" t="s">
-        <v>118</v>
       </c>
       <c r="H50">
         <v>1245.463</v>
@@ -5085,10 +5085,10 @@
         <v>0</v>
       </c>
       <c r="F51" t="s">
+        <v>118</v>
+      </c>
+      <c r="G51" t="s">
         <v>119</v>
-      </c>
-      <c r="G51" t="s">
-        <v>120</v>
       </c>
       <c r="H51">
         <v>744.75</v>
@@ -5150,10 +5150,10 @@
         <v>1</v>
       </c>
       <c r="F52" t="s">
+        <v>120</v>
+      </c>
+      <c r="G52" t="s">
         <v>121</v>
-      </c>
-      <c r="G52" t="s">
-        <v>122</v>
       </c>
       <c r="H52">
         <v>1124.6210000000001</v>
@@ -5215,10 +5215,10 @@
         <v>3</v>
       </c>
       <c r="F53" t="s">
+        <v>122</v>
+      </c>
+      <c r="G53" t="s">
         <v>123</v>
-      </c>
-      <c r="G53" t="s">
-        <v>124</v>
       </c>
       <c r="H53">
         <v>2983.34</v>
@@ -5280,10 +5280,10 @@
         <v>0</v>
       </c>
       <c r="F54" t="s">
+        <v>124</v>
+      </c>
+      <c r="G54" t="s">
         <v>125</v>
-      </c>
-      <c r="G54" t="s">
-        <v>126</v>
       </c>
       <c r="H54">
         <v>791.346</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="F55" t="s">
+        <v>126</v>
+      </c>
+      <c r="G55" t="s">
         <v>127</v>
-      </c>
-      <c r="G55" t="s">
-        <v>128</v>
       </c>
       <c r="H55">
         <v>302.63299999999998</v>
@@ -5410,10 +5410,10 @@
         <v>1</v>
       </c>
       <c r="F56" t="s">
+        <v>128</v>
+      </c>
+      <c r="G56" t="s">
         <v>129</v>
-      </c>
-      <c r="G56" t="s">
-        <v>130</v>
       </c>
       <c r="H56">
         <v>3785.3609999999999</v>
@@ -5475,10 +5475,10 @@
         <v>1</v>
       </c>
       <c r="F57" t="s">
+        <v>130</v>
+      </c>
+      <c r="G57" t="s">
         <v>131</v>
-      </c>
-      <c r="G57" t="s">
-        <v>132</v>
       </c>
       <c r="H57">
         <v>2002.558</v>
@@ -5540,10 +5540,10 @@
         <v>1</v>
       </c>
       <c r="F58" t="s">
+        <v>132</v>
+      </c>
+      <c r="G58" t="s">
         <v>133</v>
-      </c>
-      <c r="G58" t="s">
-        <v>134</v>
       </c>
       <c r="H58">
         <v>4101.415</v>
@@ -5605,10 +5605,10 @@
         <v>1</v>
       </c>
       <c r="F59" t="s">
+        <v>134</v>
+      </c>
+      <c r="G59" t="s">
         <v>135</v>
-      </c>
-      <c r="G59" t="s">
-        <v>136</v>
       </c>
       <c r="H59">
         <v>1904.759</v>
@@ -5670,10 +5670,10 @@
         <v>4</v>
       </c>
       <c r="F60" t="s">
+        <v>136</v>
+      </c>
+      <c r="G60" t="s">
         <v>137</v>
-      </c>
-      <c r="G60" t="s">
-        <v>138</v>
       </c>
       <c r="H60">
         <v>1371.93</v>
@@ -5735,10 +5735,10 @@
         <v>3</v>
       </c>
       <c r="F61" t="s">
+        <v>138</v>
+      </c>
+      <c r="G61" t="s">
         <v>139</v>
-      </c>
-      <c r="G61" t="s">
-        <v>140</v>
       </c>
       <c r="H61">
         <v>1040.058</v>
@@ -5800,10 +5800,10 @@
         <v>0</v>
       </c>
       <c r="F62" t="s">
+        <v>140</v>
+      </c>
+      <c r="G62" t="s">
         <v>141</v>
-      </c>
-      <c r="G62" t="s">
-        <v>142</v>
       </c>
       <c r="H62">
         <v>1945.4490000000001</v>
@@ -5865,10 +5865,10 @@
         <v>3</v>
       </c>
       <c r="F63" t="s">
+        <v>142</v>
+      </c>
+      <c r="G63" t="s">
         <v>143</v>
-      </c>
-      <c r="G63" t="s">
-        <v>144</v>
       </c>
       <c r="H63">
         <v>2758.1469999999999</v>
@@ -5930,10 +5930,10 @@
         <v>0</v>
       </c>
       <c r="F64" t="s">
+        <v>144</v>
+      </c>
+      <c r="G64" t="s">
         <v>145</v>
-      </c>
-      <c r="G64" t="s">
-        <v>146</v>
       </c>
       <c r="H64">
         <v>4857.0079999999998</v>
@@ -5995,10 +5995,10 @@
         <v>1</v>
       </c>
       <c r="F65" t="s">
+        <v>146</v>
+      </c>
+      <c r="G65" t="s">
         <v>147</v>
-      </c>
-      <c r="G65" t="s">
-        <v>148</v>
       </c>
       <c r="H65">
         <v>136.624</v>
@@ -6060,10 +6060,10 @@
         <v>0</v>
       </c>
       <c r="F66" t="s">
+        <v>148</v>
+      </c>
+      <c r="G66" t="s">
         <v>149</v>
-      </c>
-      <c r="G66" t="s">
-        <v>150</v>
       </c>
       <c r="H66">
         <v>1212.942</v>
@@ -6125,10 +6125,10 @@
         <v>2</v>
       </c>
       <c r="F67" t="s">
+        <v>150</v>
+      </c>
+      <c r="G67" t="s">
         <v>151</v>
-      </c>
-      <c r="G67" t="s">
-        <v>152</v>
       </c>
       <c r="H67">
         <v>585.04700000000003</v>
@@ -6190,10 +6190,10 @@
         <v>3</v>
       </c>
       <c r="F68" t="s">
+        <v>152</v>
+      </c>
+      <c r="G68" t="s">
         <v>153</v>
-      </c>
-      <c r="G68" t="s">
-        <v>154</v>
       </c>
       <c r="H68">
         <v>1203.318</v>
@@ -6255,10 +6255,10 @@
         <v>0</v>
       </c>
       <c r="F69" t="s">
+        <v>154</v>
+      </c>
+      <c r="G69" t="s">
         <v>155</v>
-      </c>
-      <c r="G69" t="s">
-        <v>156</v>
       </c>
       <c r="H69">
         <v>919.29399999999998</v>
@@ -6320,10 +6320,10 @@
         <v>0</v>
       </c>
       <c r="F70" t="s">
+        <v>156</v>
+      </c>
+      <c r="G70" t="s">
         <v>157</v>
-      </c>
-      <c r="G70" t="s">
-        <v>158</v>
       </c>
       <c r="H70">
         <v>33.176000000000002</v>
@@ -6385,10 +6385,10 @@
         <v>0</v>
       </c>
       <c r="F71" t="s">
+        <v>158</v>
+      </c>
+      <c r="G71" t="s">
         <v>159</v>
-      </c>
-      <c r="G71" t="s">
-        <v>160</v>
       </c>
       <c r="H71">
         <v>1650.8009999999999</v>
@@ -6450,10 +6450,10 @@
         <v>0</v>
       </c>
       <c r="F72" t="s">
+        <v>160</v>
+      </c>
+      <c r="G72" t="s">
         <v>161</v>
-      </c>
-      <c r="G72" t="s">
-        <v>162</v>
       </c>
       <c r="H72">
         <v>979.68100000000004</v>
@@ -6515,10 +6515,10 @@
         <v>0</v>
       </c>
       <c r="F73" t="s">
+        <v>162</v>
+      </c>
+      <c r="G73" t="s">
         <v>163</v>
-      </c>
-      <c r="G73" t="s">
-        <v>164</v>
       </c>
       <c r="H73">
         <v>1146.846</v>
@@ -6580,10 +6580,10 @@
         <v>0</v>
       </c>
       <c r="F74" t="s">
+        <v>164</v>
+      </c>
+      <c r="G74" t="s">
         <v>165</v>
-      </c>
-      <c r="G74" t="s">
-        <v>166</v>
       </c>
       <c r="H74">
         <v>2677.895</v>
@@ -6645,10 +6645,10 @@
         <v>4</v>
       </c>
       <c r="F75" t="s">
+        <v>166</v>
+      </c>
+      <c r="G75" t="s">
         <v>167</v>
-      </c>
-      <c r="G75" t="s">
-        <v>168</v>
       </c>
       <c r="H75">
         <v>2086.569</v>
@@ -6710,10 +6710,10 @@
         <v>3</v>
       </c>
       <c r="F76" t="s">
+        <v>168</v>
+      </c>
+      <c r="G76" t="s">
         <v>169</v>
-      </c>
-      <c r="G76" t="s">
-        <v>170</v>
       </c>
       <c r="H76">
         <v>1740.5429999999999</v>
@@ -6781,85 +6781,85 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D1" t="s">
+        <v>174</v>
+      </c>
+      <c r="E1" t="s">
+        <v>175</v>
+      </c>
+      <c r="F1" t="s">
+        <v>176</v>
+      </c>
+      <c r="G1" t="s">
         <v>171</v>
       </c>
-      <c r="C1" t="s">
-        <v>174</v>
-      </c>
-      <c r="D1" t="s">
-        <v>175</v>
-      </c>
-      <c r="E1" t="s">
-        <v>176</v>
-      </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
+        <v>172</v>
+      </c>
+      <c r="I1" t="s">
         <v>177</v>
       </c>
-      <c r="G1" t="s">
-        <v>172</v>
-      </c>
-      <c r="H1" t="s">
-        <v>173</v>
-      </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>178</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>179</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>180</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>181</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>182</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>183</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>184</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>185</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>186</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>187</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>188</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>189</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>190</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>191</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>192</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>193</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>194</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>195</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>196</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.3">
@@ -7203,28 +7203,28 @@
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.3">
       <c r="C6" t="s">
+        <v>197</v>
+      </c>
+      <c r="D6" t="s">
         <v>198</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>199</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>200</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>201</v>
       </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
         <v>202</v>
       </c>
-      <c r="H6" t="s">
+      <c r="I6" t="s">
         <v>203</v>
       </c>
-      <c r="I6" t="s">
+      <c r="J6" t="s">
         <v>204</v>
-      </c>
-      <c r="J6" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.3">
@@ -7298,11 +7298,11 @@
     <row r="9" spans="1:28" x14ac:dyDescent="0.3">
       <c r="C9">
         <f>AVERAGEIF(data[Sesion],A4,data[Tiempo duracion])</f>
-        <v>1634.4362592592588</v>
+        <v>2271.3278518518518</v>
       </c>
       <c r="D9" cm="1">
         <f t="array" ref="D9">_xlfn.STDEV.P(IF(data[Sesion]=A4,data[Tiempo duracion]))</f>
-        <v>3285.1750964942448</v>
+        <v>881.82186350690699</v>
       </c>
       <c r="E9">
         <f>AVERAGEIF(data[Sesion],A4,data[Num niveles])</f>
@@ -7314,11 +7314,11 @@
       </c>
       <c r="G9">
         <f>AVERAGEIF(data[Sesion],A4,data[Num intentos])</f>
-        <v>11.518518518518519</v>
+        <v>11.481481481481481</v>
       </c>
       <c r="H9" cm="1">
         <f t="array" ref="H9">_xlfn.STDEV.P(IF(data[Sesion]=A4,data[Num intentos]))</f>
-        <v>5.3980131486835754</v>
+        <v>5.3704980827726274</v>
       </c>
       <c r="I9">
         <f>AVERAGEIF(data[Sesion],A4,data[Completados])</f>

--- a/datosSesionesPruebaMedias.xlsx
+++ b/datosSesionesPruebaMedias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\hlocal\C_TFG\Datos\Mision Colombia-20260209T150018Z-3-001\jsonToCsv_TFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FF0F5E0-8184-4DB2-B3C6-C90CCA2DC0F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{449E054E-E7B1-45FD-84F1-51E9FB4DFB2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="310">
   <si>
     <t>ID</t>
   </si>
@@ -679,6 +679,318 @@
   </si>
   <si>
     <t>15:42:14.394</t>
+  </si>
+  <si>
+    <t>% Aciertos</t>
+  </si>
+  <si>
+    <t>% Mal</t>
+  </si>
+  <si>
+    <t>78.57142857142857</t>
+  </si>
+  <si>
+    <t>21.42857142857143</t>
+  </si>
+  <si>
+    <t>88.23529411764706</t>
+  </si>
+  <si>
+    <t>11.764705882352942</t>
+  </si>
+  <si>
+    <t>84.61538461538461</t>
+  </si>
+  <si>
+    <t>15.384615384615387</t>
+  </si>
+  <si>
+    <t>84.21052631578948</t>
+  </si>
+  <si>
+    <t>15.78947368421052</t>
+  </si>
+  <si>
+    <t>88.88888888888889</t>
+  </si>
+  <si>
+    <t>11.111111111111114</t>
+  </si>
+  <si>
+    <t>95.0</t>
+  </si>
+  <si>
+    <t>5.0</t>
+  </si>
+  <si>
+    <t>0 planificado</t>
+  </si>
+  <si>
+    <t>62.5</t>
+  </si>
+  <si>
+    <t>37.5</t>
+  </si>
+  <si>
+    <t>95.23809523809524</t>
+  </si>
+  <si>
+    <t>4.761904761904759</t>
+  </si>
+  <si>
+    <t>92.85714285714286</t>
+  </si>
+  <si>
+    <t>7.142857142857139</t>
+  </si>
+  <si>
+    <t>93.75</t>
+  </si>
+  <si>
+    <t>6.25</t>
+  </si>
+  <si>
+    <t>76.47058823529412</t>
+  </si>
+  <si>
+    <t>23.529411764705884</t>
+  </si>
+  <si>
+    <t>86.66666666666667</t>
+  </si>
+  <si>
+    <t>13.333333333333329</t>
+  </si>
+  <si>
+    <t>83.33333333333333</t>
+  </si>
+  <si>
+    <t>16.66666666666667</t>
+  </si>
+  <si>
+    <t>81.25</t>
+  </si>
+  <si>
+    <t>18.75</t>
+  </si>
+  <si>
+    <t>92.5925925925926</t>
+  </si>
+  <si>
+    <t>7.407407407407405</t>
+  </si>
+  <si>
+    <t>90.3225806451613</t>
+  </si>
+  <si>
+    <t>9.677419354838705</t>
+  </si>
+  <si>
+    <t>90.9090909090909</t>
+  </si>
+  <si>
+    <t>9.090909090909093</t>
+  </si>
+  <si>
+    <t>94.73684210526316</t>
+  </si>
+  <si>
+    <t>5.263157894736835</t>
+  </si>
+  <si>
+    <t>88.63636363636364</t>
+  </si>
+  <si>
+    <t>11.36363636363636</t>
+  </si>
+  <si>
+    <t>50.0</t>
+  </si>
+  <si>
+    <t>76.74418604651163</t>
+  </si>
+  <si>
+    <t>23.25581395348837</t>
+  </si>
+  <si>
+    <t>87.5</t>
+  </si>
+  <si>
+    <t>12.5</t>
+  </si>
+  <si>
+    <t>100.0</t>
+  </si>
+  <si>
+    <t>0.0</t>
+  </si>
+  <si>
+    <t>75.0</t>
+  </si>
+  <si>
+    <t>25.0</t>
+  </si>
+  <si>
+    <t>60.0</t>
+  </si>
+  <si>
+    <t>40.0</t>
+  </si>
+  <si>
+    <t>78.94736842105263</t>
+  </si>
+  <si>
+    <t>21.05263157894737</t>
+  </si>
+  <si>
+    <t>76.78571428571429</t>
+  </si>
+  <si>
+    <t>23.214285714285708</t>
+  </si>
+  <si>
+    <t>92.3076923076923</t>
+  </si>
+  <si>
+    <t>7.692307692307693</t>
+  </si>
+  <si>
+    <t>83.78378378378379</t>
+  </si>
+  <si>
+    <t>16.21621621621621</t>
+  </si>
+  <si>
+    <t>90.2439024390244</t>
+  </si>
+  <si>
+    <t>9.756097560975604</t>
+  </si>
+  <si>
+    <t>90.47619047619048</t>
+  </si>
+  <si>
+    <t>9.523809523809518</t>
+  </si>
+  <si>
+    <t>83.87096774193549</t>
+  </si>
+  <si>
+    <t>16.129032258064512</t>
+  </si>
+  <si>
+    <t>80.76923076923077</t>
+  </si>
+  <si>
+    <t>19.230769230769226</t>
+  </si>
+  <si>
+    <t>96.42857142857143</t>
+  </si>
+  <si>
+    <t>3.5714285714285694</t>
+  </si>
+  <si>
+    <t>80.95238095238095</t>
+  </si>
+  <si>
+    <t>19.04761904761905</t>
+  </si>
+  <si>
+    <t>78.78787878787878</t>
+  </si>
+  <si>
+    <t>21.212121212121218</t>
+  </si>
+  <si>
+    <t>57.142857142857146</t>
+  </si>
+  <si>
+    <t>42.857142857142854</t>
+  </si>
+  <si>
+    <t>90.0</t>
+  </si>
+  <si>
+    <t>10.0</t>
+  </si>
+  <si>
+    <t>94.11764705882354</t>
+  </si>
+  <si>
+    <t>5.882352941176464</t>
+  </si>
+  <si>
+    <t>83.60655737704919</t>
+  </si>
+  <si>
+    <t>16.393442622950815</t>
+  </si>
+  <si>
+    <t>91.66666666666667</t>
+  </si>
+  <si>
+    <t>8.333333333333329</t>
+  </si>
+  <si>
+    <t>90.625</t>
+  </si>
+  <si>
+    <t>9.375</t>
+  </si>
+  <si>
+    <t>89.28571428571429</t>
+  </si>
+  <si>
+    <t>10.714285714285708</t>
+  </si>
+  <si>
+    <t>56.25</t>
+  </si>
+  <si>
+    <t>43.75</t>
+  </si>
+  <si>
+    <t>96.29629629629629</t>
+  </si>
+  <si>
+    <t>3.7037037037037095</t>
+  </si>
+  <si>
+    <t>66.66666666666667</t>
+  </si>
+  <si>
+    <t>33.33333333333333</t>
+  </si>
+  <si>
+    <t>75.86206896551724</t>
+  </si>
+  <si>
+    <t>24.13793103448276</t>
+  </si>
+  <si>
+    <t>71.42857142857143</t>
+  </si>
+  <si>
+    <t>28.57142857142857</t>
+  </si>
+  <si>
+    <t>76.0</t>
+  </si>
+  <si>
+    <t>24.0</t>
+  </si>
+  <si>
+    <t>91.30434782608695</t>
+  </si>
+  <si>
+    <t>8.695652173913047</t>
+  </si>
+  <si>
+    <t>77.14285714285714</t>
+  </si>
+  <si>
+    <t>22.85714285714286</t>
   </si>
 </sst>
 </file>
@@ -1480,9 +1792,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{AD8B7A24-8C82-432D-8F40-107C6140EF70}" name="data" displayName="data" ref="A1:U76" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="1" tableBorderDxfId="0">
-  <autoFilter ref="A1:U76" xr:uid="{AD8B7A24-8C82-432D-8F40-107C6140EF70}"/>
-  <tableColumns count="21">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{AD8B7A24-8C82-432D-8F40-107C6140EF70}" name="data" displayName="data" ref="A1:W76" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="1" tableBorderDxfId="0">
+  <autoFilter ref="A1:W76" xr:uid="{AD8B7A24-8C82-432D-8F40-107C6140EF70}"/>
+  <tableColumns count="23">
     <tableColumn id="1" xr3:uid="{E9C60595-13C0-4ABA-BDC8-21DAAB7F3D42}" name="ID"/>
     <tableColumn id="2" xr3:uid="{9FACE59C-239F-4A71-B8BE-F4FEB003A591}" name="Sesion"/>
     <tableColumn id="3" xr3:uid="{79C6D1C3-A60F-414A-92D5-DE9C600BEF77}" name="Num niveles"/>
@@ -1504,6 +1816,8 @@
     <tableColumn id="19" xr3:uid="{734148C9-249D-45E3-AEB7-9E097DF3E0D8}" name="Paradas realizadas"/>
     <tableColumn id="20" xr3:uid="{97C6F595-D16D-433B-BB44-CA7C478E90FA}" name="Errores parada por tiempo excedido"/>
     <tableColumn id="21" xr3:uid="{6DCC0F6D-47AE-44A8-B3EF-D75D91D818B8}" name="Num errores por tiempo excedido"/>
+    <tableColumn id="22" xr3:uid="{6BB76774-135C-4D4D-BE0D-D83590AFB522}" name="% Aciertos"/>
+    <tableColumn id="23" xr3:uid="{9C9F4625-8EA8-476D-A95C-1546132B3A03}" name="% Mal"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1794,7 +2108,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U76"/>
+  <dimension ref="A1:W76"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="14.33203125" customWidth="1"/>
@@ -1816,9 +2130,10 @@
     <col min="19" max="19" width="19.33203125" customWidth="1"/>
     <col min="20" max="20" width="34.6640625" customWidth="1"/>
     <col min="21" max="21" width="33.109375" customWidth="1"/>
+    <col min="22" max="23" width="18.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1882,8 +2197,14 @@
       <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V1" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>10</v>
       </c>
@@ -1947,8 +2268,14 @@
       <c r="U2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V2" t="s">
+        <v>208</v>
+      </c>
+      <c r="W2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>10</v>
       </c>
@@ -2012,8 +2339,14 @@
       <c r="U3">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V3" t="s">
+        <v>210</v>
+      </c>
+      <c r="W3" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>11</v>
       </c>
@@ -2077,8 +2410,14 @@
       <c r="U4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V4" t="s">
+        <v>212</v>
+      </c>
+      <c r="W4" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>11</v>
       </c>
@@ -2142,8 +2481,14 @@
       <c r="U5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V5" t="s">
+        <v>214</v>
+      </c>
+      <c r="W5" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>13</v>
       </c>
@@ -2207,8 +2552,14 @@
       <c r="U6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V6" t="s">
+        <v>216</v>
+      </c>
+      <c r="W6" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>13</v>
       </c>
@@ -2272,8 +2623,14 @@
       <c r="U7">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V7" t="s">
+        <v>218</v>
+      </c>
+      <c r="W7" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>15</v>
       </c>
@@ -2337,8 +2694,14 @@
       <c r="U8">
         <v>2</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V8" t="s">
+        <v>220</v>
+      </c>
+      <c r="W8" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>16</v>
       </c>
@@ -2402,8 +2765,14 @@
       <c r="U9">
         <v>2</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V9" t="s">
+        <v>221</v>
+      </c>
+      <c r="W9" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>16</v>
       </c>
@@ -2467,8 +2836,14 @@
       <c r="U10">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V10" t="s">
+        <v>223</v>
+      </c>
+      <c r="W10" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>17</v>
       </c>
@@ -2532,8 +2907,14 @@
       <c r="U11">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V11" t="s">
+        <v>225</v>
+      </c>
+      <c r="W11" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>17</v>
       </c>
@@ -2597,8 +2978,14 @@
       <c r="U12">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V12" t="s">
+        <v>227</v>
+      </c>
+      <c r="W12" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>18</v>
       </c>
@@ -2662,8 +3049,14 @@
       <c r="U13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V13" t="s">
+        <v>229</v>
+      </c>
+      <c r="W13" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>18</v>
       </c>
@@ -2727,8 +3120,14 @@
       <c r="U14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V14" t="s">
+        <v>231</v>
+      </c>
+      <c r="W14" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>18</v>
       </c>
@@ -2792,8 +3191,14 @@
       <c r="U15">
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V15" t="s">
+        <v>233</v>
+      </c>
+      <c r="W15" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>19</v>
       </c>
@@ -2857,8 +3262,14 @@
       <c r="U16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V16" t="s">
+        <v>235</v>
+      </c>
+      <c r="W16" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>19</v>
       </c>
@@ -2922,8 +3333,14 @@
       <c r="U17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V17" t="s">
+        <v>237</v>
+      </c>
+      <c r="W17" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>1</v>
       </c>
@@ -2987,8 +3404,14 @@
       <c r="U18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V18" t="s">
+        <v>220</v>
+      </c>
+      <c r="W18" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>21</v>
       </c>
@@ -3052,8 +3475,14 @@
       <c r="U19">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V19" t="s">
+        <v>239</v>
+      </c>
+      <c r="W19" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>21</v>
       </c>
@@ -3117,8 +3546,14 @@
       <c r="U20">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V20" t="s">
+        <v>241</v>
+      </c>
+      <c r="W20" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>22</v>
       </c>
@@ -3182,8 +3617,14 @@
       <c r="U21">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V21" t="s">
+        <v>243</v>
+      </c>
+      <c r="W21" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="22" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>22</v>
       </c>
@@ -3247,8 +3688,14 @@
       <c r="U22">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V22" t="s">
+        <v>245</v>
+      </c>
+      <c r="W22" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="23" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>23</v>
       </c>
@@ -3312,8 +3759,14 @@
       <c r="U23">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V23" t="s">
+        <v>208</v>
+      </c>
+      <c r="W23" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="24" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>24</v>
       </c>
@@ -3377,8 +3830,14 @@
       <c r="U24">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V24" t="s">
+        <v>247</v>
+      </c>
+      <c r="W24" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="25" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
@@ -3442,8 +3901,14 @@
       <c r="U25">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V25" t="s">
+        <v>248</v>
+      </c>
+      <c r="W25" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="26" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
@@ -3507,8 +3972,14 @@
       <c r="U26">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V26" t="s">
+        <v>218</v>
+      </c>
+      <c r="W26" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="27" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>25</v>
       </c>
@@ -3572,8 +4043,14 @@
       <c r="U27">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V27" t="s">
+        <v>250</v>
+      </c>
+      <c r="W27" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="28" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>26</v>
       </c>
@@ -3637,8 +4114,14 @@
       <c r="U28">
         <v>2</v>
       </c>
-    </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V28" t="s">
+        <v>252</v>
+      </c>
+      <c r="W28" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="29" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>26</v>
       </c>
@@ -3702,8 +4185,14 @@
       <c r="U29">
         <v>2</v>
       </c>
-    </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V29" t="s">
+        <v>254</v>
+      </c>
+      <c r="W29" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="30" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>27</v>
       </c>
@@ -3767,8 +4256,14 @@
       <c r="U30">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V30" t="s">
+        <v>256</v>
+      </c>
+      <c r="W30" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="31" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>27</v>
       </c>
@@ -3832,8 +4327,14 @@
       <c r="U31">
         <v>3</v>
       </c>
-    </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V31" t="s">
+        <v>254</v>
+      </c>
+      <c r="W31" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="32" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>2</v>
       </c>
@@ -3897,8 +4398,14 @@
       <c r="U32">
         <v>1</v>
       </c>
-    </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V32" t="s">
+        <v>250</v>
+      </c>
+      <c r="W32" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>30</v>
       </c>
@@ -3962,8 +4469,14 @@
       <c r="U33">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V33" t="s">
+        <v>258</v>
+      </c>
+      <c r="W33" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>30</v>
       </c>
@@ -4027,8 +4540,14 @@
       <c r="U34">
         <v>2</v>
       </c>
-    </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V34" t="s">
+        <v>260</v>
+      </c>
+      <c r="W34" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>31</v>
       </c>
@@ -4092,8 +4611,14 @@
       <c r="U35">
         <v>3</v>
       </c>
-    </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V35" t="s">
+        <v>262</v>
+      </c>
+      <c r="W35" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>31</v>
       </c>
@@ -4157,8 +4682,14 @@
       <c r="U36">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V36" t="s">
+        <v>264</v>
+      </c>
+      <c r="W36" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>32</v>
       </c>
@@ -4222,8 +4753,14 @@
       <c r="U37">
         <v>1</v>
       </c>
-    </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V37" t="s">
+        <v>266</v>
+      </c>
+      <c r="W37" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>32</v>
       </c>
@@ -4287,8 +4824,14 @@
       <c r="U38">
         <v>0</v>
       </c>
-    </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V38" t="s">
+        <v>268</v>
+      </c>
+      <c r="W38" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>33</v>
       </c>
@@ -4352,8 +4895,14 @@
       <c r="U39">
         <v>0</v>
       </c>
-    </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V39" t="s">
+        <v>220</v>
+      </c>
+      <c r="W39" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="40" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>34</v>
       </c>
@@ -4417,8 +4966,14 @@
       <c r="U40">
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V40" t="s">
+        <v>220</v>
+      </c>
+      <c r="W40" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>35</v>
       </c>
@@ -4482,8 +5037,14 @@
       <c r="U41">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V41" t="s">
+        <v>220</v>
+      </c>
+      <c r="W41" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>35</v>
       </c>
@@ -4547,8 +5108,14 @@
       <c r="U42">
         <v>2</v>
       </c>
-    </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V42" t="s">
+        <v>270</v>
+      </c>
+      <c r="W42" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="43" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>37</v>
       </c>
@@ -4612,8 +5179,14 @@
       <c r="U43">
         <v>1</v>
       </c>
-    </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V43" t="s">
+        <v>272</v>
+      </c>
+      <c r="W43" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>37</v>
       </c>
@@ -4677,8 +5250,14 @@
       <c r="U44">
         <v>2</v>
       </c>
-    </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V44" t="s">
+        <v>274</v>
+      </c>
+      <c r="W44" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>3</v>
       </c>
@@ -4742,8 +5321,14 @@
       <c r="U45">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V45" t="s">
+        <v>220</v>
+      </c>
+      <c r="W45" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>3</v>
       </c>
@@ -4807,8 +5392,14 @@
       <c r="U46">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V46" t="s">
+        <v>220</v>
+      </c>
+      <c r="W46" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>41</v>
       </c>
@@ -4872,8 +5463,14 @@
       <c r="U47">
         <v>1</v>
       </c>
-    </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V47" t="s">
+        <v>276</v>
+      </c>
+      <c r="W47" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>42</v>
       </c>
@@ -4937,8 +5534,14 @@
       <c r="U48">
         <v>2</v>
       </c>
-    </row>
-    <row r="49" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V48" t="s">
+        <v>220</v>
+      </c>
+      <c r="W48" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="49" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>43</v>
       </c>
@@ -5002,8 +5605,14 @@
       <c r="U49">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V49" t="s">
+        <v>216</v>
+      </c>
+      <c r="W49" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="50" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>43</v>
       </c>
@@ -5067,8 +5676,14 @@
       <c r="U50">
         <v>2</v>
       </c>
-    </row>
-    <row r="51" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V50" t="s">
+        <v>278</v>
+      </c>
+      <c r="W50" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="51" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>44</v>
       </c>
@@ -5132,8 +5747,14 @@
       <c r="U51">
         <v>1</v>
       </c>
-    </row>
-    <row r="52" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V51" t="s">
+        <v>220</v>
+      </c>
+      <c r="W51" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="52" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>45</v>
       </c>
@@ -5197,8 +5818,14 @@
       <c r="U52">
         <v>5</v>
       </c>
-    </row>
-    <row r="53" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V52" t="s">
+        <v>280</v>
+      </c>
+      <c r="W52" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="53" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>45</v>
       </c>
@@ -5262,8 +5889,14 @@
       <c r="U53">
         <v>6</v>
       </c>
-    </row>
-    <row r="54" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V53" t="s">
+        <v>282</v>
+      </c>
+      <c r="W53" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="54" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>46</v>
       </c>
@@ -5327,8 +5960,14 @@
       <c r="U54">
         <v>2</v>
       </c>
-    </row>
-    <row r="55" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V54" t="s">
+        <v>254</v>
+      </c>
+      <c r="W54" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="55" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>47</v>
       </c>
@@ -5392,8 +6031,14 @@
       <c r="U55">
         <v>0</v>
       </c>
-    </row>
-    <row r="56" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V55" t="s">
+        <v>252</v>
+      </c>
+      <c r="W55" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="56" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>47</v>
       </c>
@@ -5457,8 +6102,14 @@
       <c r="U56">
         <v>7</v>
       </c>
-    </row>
-    <row r="57" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V56" t="s">
+        <v>247</v>
+      </c>
+      <c r="W56" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="57" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>48</v>
       </c>
@@ -5522,8 +6173,14 @@
       <c r="U57">
         <v>2</v>
       </c>
-    </row>
-    <row r="58" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V57" t="s">
+        <v>284</v>
+      </c>
+      <c r="W57" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="58" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>4</v>
       </c>
@@ -5587,8 +6244,14 @@
       <c r="U58">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V58" t="s">
+        <v>286</v>
+      </c>
+      <c r="W58" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="59" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>50</v>
       </c>
@@ -5652,8 +6315,14 @@
       <c r="U59">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V59" t="s">
+        <v>280</v>
+      </c>
+      <c r="W59" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="60" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>51</v>
       </c>
@@ -5717,8 +6386,14 @@
       <c r="U60">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V60" t="s">
+        <v>288</v>
+      </c>
+      <c r="W60" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="61" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>51</v>
       </c>
@@ -5782,8 +6457,14 @@
       <c r="U61">
         <v>1</v>
       </c>
-    </row>
-    <row r="62" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V61" t="s">
+        <v>290</v>
+      </c>
+      <c r="W61" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="62" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>52</v>
       </c>
@@ -5847,8 +6528,14 @@
       <c r="U62">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V62" t="s">
+        <v>231</v>
+      </c>
+      <c r="W62" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="63" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>53</v>
       </c>
@@ -5912,8 +6599,14 @@
       <c r="U63">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V63" t="s">
+        <v>292</v>
+      </c>
+      <c r="W63" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="64" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>5</v>
       </c>
@@ -5977,8 +6670,14 @@
       <c r="U64">
         <v>3</v>
       </c>
-    </row>
-    <row r="65" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V64" t="s">
+        <v>294</v>
+      </c>
+      <c r="W64" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="65" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>65</v>
       </c>
@@ -6042,8 +6741,14 @@
       <c r="U65">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V65" t="s">
+        <v>252</v>
+      </c>
+      <c r="W65" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="66" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>6</v>
       </c>
@@ -6107,8 +6812,14 @@
       <c r="U66">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V66" t="s">
+        <v>254</v>
+      </c>
+      <c r="W66" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="67" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>6</v>
       </c>
@@ -6172,8 +6883,14 @@
       <c r="U67">
         <v>1</v>
       </c>
-    </row>
-    <row r="68" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V67" t="s">
+        <v>262</v>
+      </c>
+      <c r="W67" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="68" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>6</v>
       </c>
@@ -6237,8 +6954,14 @@
       <c r="U68">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V68" t="s">
+        <v>296</v>
+      </c>
+      <c r="W68" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="69" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>7</v>
       </c>
@@ -6302,8 +7025,14 @@
       <c r="U69">
         <v>1</v>
       </c>
-    </row>
-    <row r="70" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V69" t="s">
+        <v>298</v>
+      </c>
+      <c r="W69" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="70" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>7</v>
       </c>
@@ -6367,8 +7096,14 @@
       <c r="U70">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V70" t="s">
+        <v>220</v>
+      </c>
+      <c r="W70" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="71" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>7</v>
       </c>
@@ -6432,8 +7167,14 @@
       <c r="U71">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V71" t="s">
+        <v>300</v>
+      </c>
+      <c r="W71" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="72" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>8</v>
       </c>
@@ -6497,8 +7238,14 @@
       <c r="U72">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V72" t="s">
+        <v>220</v>
+      </c>
+      <c r="W72" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="73" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>8</v>
       </c>
@@ -6562,8 +7309,14 @@
       <c r="U73">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V73" t="s">
+        <v>302</v>
+      </c>
+      <c r="W73" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="74" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>8</v>
       </c>
@@ -6627,8 +7380,14 @@
       <c r="U74">
         <v>2</v>
       </c>
-    </row>
-    <row r="75" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V74" t="s">
+        <v>304</v>
+      </c>
+      <c r="W74" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="75" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>9</v>
       </c>
@@ -6692,8 +7451,14 @@
       <c r="U75">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V75" t="s">
+        <v>306</v>
+      </c>
+      <c r="W75" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="76" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>9</v>
       </c>
@@ -6756,6 +7521,12 @@
       </c>
       <c r="U76">
         <v>0</v>
+      </c>
+      <c r="V76" t="s">
+        <v>308</v>
+      </c>
+      <c r="W76" t="s">
+        <v>309</v>
       </c>
     </row>
   </sheetData>

--- a/datosSesionesPruebaMedias.xlsx
+++ b/datosSesionesPruebaMedias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\hlocal\C_TFG\Datos\Mision Colombia-20260209T150018Z-3-001\jsonToCsv_TFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{449E054E-E7B1-45FD-84F1-51E9FB4DFB2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEF10A7C-BE4B-4AB3-A375-3AB17A2AD797}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="217">
   <si>
     <t>ID</t>
   </si>
@@ -687,310 +687,31 @@
     <t>% Mal</t>
   </si>
   <si>
-    <t>78.57142857142857</t>
-  </si>
-  <si>
-    <t>21.42857142857143</t>
-  </si>
-  <si>
-    <t>88.23529411764706</t>
-  </si>
-  <si>
-    <t>11.764705882352942</t>
-  </si>
-  <si>
-    <t>84.61538461538461</t>
-  </si>
-  <si>
-    <t>15.384615384615387</t>
-  </si>
-  <si>
-    <t>84.21052631578948</t>
-  </si>
-  <si>
-    <t>15.78947368421052</t>
-  </si>
-  <si>
-    <t>88.88888888888889</t>
-  </si>
-  <si>
-    <t>11.111111111111114</t>
-  </si>
-  <si>
-    <t>95.0</t>
-  </si>
-  <si>
-    <t>5.0</t>
-  </si>
-  <si>
     <t>0 planificado</t>
   </si>
   <si>
-    <t>62.5</t>
-  </si>
-  <si>
-    <t>37.5</t>
-  </si>
-  <si>
-    <t>95.23809523809524</t>
-  </si>
-  <si>
-    <t>4.761904761904759</t>
-  </si>
-  <si>
-    <t>92.85714285714286</t>
-  </si>
-  <si>
-    <t>7.142857142857139</t>
-  </si>
-  <si>
-    <t>93.75</t>
-  </si>
-  <si>
-    <t>6.25</t>
-  </si>
-  <si>
-    <t>76.47058823529412</t>
-  </si>
-  <si>
-    <t>23.529411764705884</t>
-  </si>
-  <si>
-    <t>86.66666666666667</t>
-  </si>
-  <si>
-    <t>13.333333333333329</t>
-  </si>
-  <si>
-    <t>83.33333333333333</t>
-  </si>
-  <si>
-    <t>16.66666666666667</t>
-  </si>
-  <si>
-    <t>81.25</t>
-  </si>
-  <si>
-    <t>18.75</t>
-  </si>
-  <si>
-    <t>92.5925925925926</t>
-  </si>
-  <si>
-    <t>7.407407407407405</t>
-  </si>
-  <si>
-    <t>90.3225806451613</t>
-  </si>
-  <si>
-    <t>9.677419354838705</t>
-  </si>
-  <si>
-    <t>90.9090909090909</t>
-  </si>
-  <si>
-    <t>9.090909090909093</t>
-  </si>
-  <si>
-    <t>94.73684210526316</t>
-  </si>
-  <si>
-    <t>5.263157894736835</t>
-  </si>
-  <si>
-    <t>88.63636363636364</t>
-  </si>
-  <si>
-    <t>11.36363636363636</t>
-  </si>
-  <si>
-    <t>50.0</t>
-  </si>
-  <si>
-    <t>76.74418604651163</t>
-  </si>
-  <si>
-    <t>23.25581395348837</t>
-  </si>
-  <si>
-    <t>87.5</t>
-  </si>
-  <si>
-    <t>12.5</t>
-  </si>
-  <si>
-    <t>100.0</t>
-  </si>
-  <si>
-    <t>0.0</t>
-  </si>
-  <si>
-    <t>75.0</t>
-  </si>
-  <si>
-    <t>25.0</t>
-  </si>
-  <si>
-    <t>60.0</t>
-  </si>
-  <si>
-    <t>40.0</t>
-  </si>
-  <si>
-    <t>78.94736842105263</t>
-  </si>
-  <si>
-    <t>21.05263157894737</t>
-  </si>
-  <si>
-    <t>76.78571428571429</t>
-  </si>
-  <si>
-    <t>23.214285714285708</t>
-  </si>
-  <si>
-    <t>92.3076923076923</t>
-  </si>
-  <si>
-    <t>7.692307692307693</t>
-  </si>
-  <si>
-    <t>83.78378378378379</t>
-  </si>
-  <si>
-    <t>16.21621621621621</t>
-  </si>
-  <si>
-    <t>90.2439024390244</t>
-  </si>
-  <si>
-    <t>9.756097560975604</t>
-  </si>
-  <si>
-    <t>90.47619047619048</t>
-  </si>
-  <si>
-    <t>9.523809523809518</t>
-  </si>
-  <si>
-    <t>83.87096774193549</t>
-  </si>
-  <si>
-    <t>16.129032258064512</t>
-  </si>
-  <si>
-    <t>80.76923076923077</t>
-  </si>
-  <si>
-    <t>19.230769230769226</t>
-  </si>
-  <si>
-    <t>96.42857142857143</t>
-  </si>
-  <si>
-    <t>3.5714285714285694</t>
-  </si>
-  <si>
-    <t>80.95238095238095</t>
-  </si>
-  <si>
-    <t>19.04761904761905</t>
-  </si>
-  <si>
-    <t>78.78787878787878</t>
-  </si>
-  <si>
-    <t>21.212121212121218</t>
-  </si>
-  <si>
-    <t>57.142857142857146</t>
-  </si>
-  <si>
-    <t>42.857142857142854</t>
-  </si>
-  <si>
-    <t>90.0</t>
-  </si>
-  <si>
-    <t>10.0</t>
-  </si>
-  <si>
-    <t>94.11764705882354</t>
-  </si>
-  <si>
-    <t>5.882352941176464</t>
-  </si>
-  <si>
-    <t>83.60655737704919</t>
-  </si>
-  <si>
-    <t>16.393442622950815</t>
-  </si>
-  <si>
-    <t>91.66666666666667</t>
-  </si>
-  <si>
-    <t>8.333333333333329</t>
-  </si>
-  <si>
-    <t>90.625</t>
-  </si>
-  <si>
-    <t>9.375</t>
-  </si>
-  <si>
-    <t>89.28571428571429</t>
-  </si>
-  <si>
-    <t>10.714285714285708</t>
-  </si>
-  <si>
-    <t>56.25</t>
-  </si>
-  <si>
-    <t>43.75</t>
-  </si>
-  <si>
-    <t>96.29629629629629</t>
-  </si>
-  <si>
-    <t>3.7037037037037095</t>
-  </si>
-  <si>
-    <t>66.66666666666667</t>
-  </si>
-  <si>
-    <t>33.33333333333333</t>
-  </si>
-  <si>
-    <t>75.86206896551724</t>
-  </si>
-  <si>
-    <t>24.13793103448276</t>
-  </si>
-  <si>
-    <t>71.42857142857143</t>
-  </si>
-  <si>
-    <t>28.57142857142857</t>
-  </si>
-  <si>
-    <t>76.0</t>
-  </si>
-  <si>
-    <t>24.0</t>
-  </si>
-  <si>
-    <t>91.30434782608695</t>
-  </si>
-  <si>
-    <t>8.695652173913047</t>
-  </si>
-  <si>
-    <t>77.14285714285714</t>
-  </si>
-  <si>
-    <t>22.85714285714286</t>
+    <t>Num completados</t>
+  </si>
+  <si>
+    <t>% completados</t>
+  </si>
+  <si>
+    <t>No completados</t>
+  </si>
+  <si>
+    <t>% no completados</t>
+  </si>
+  <si>
+    <t>Media % aciertos</t>
+  </si>
+  <si>
+    <t>Media % errores</t>
+  </si>
+  <si>
+    <t>Stdev % aciertos</t>
+  </si>
+  <si>
+    <t>Stdev % errores</t>
   </si>
 </sst>
 </file>
@@ -2268,11 +1989,11 @@
       <c r="U2">
         <v>0</v>
       </c>
-      <c r="V2" t="s">
-        <v>208</v>
-      </c>
-      <c r="W2" t="s">
-        <v>209</v>
+      <c r="V2">
+        <v>78.571428571428498</v>
+      </c>
+      <c r="W2">
+        <v>21.428571428571399</v>
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.3">
@@ -2339,11 +2060,11 @@
       <c r="U3">
         <v>2</v>
       </c>
-      <c r="V3" t="s">
-        <v>210</v>
-      </c>
-      <c r="W3" t="s">
-        <v>211</v>
+      <c r="V3">
+        <v>88.235294117647001</v>
+      </c>
+      <c r="W3">
+        <v>11.764705882352899</v>
       </c>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.3">
@@ -2410,11 +2131,11 @@
       <c r="U4">
         <v>1</v>
       </c>
-      <c r="V4" t="s">
-        <v>212</v>
-      </c>
-      <c r="W4" t="s">
-        <v>213</v>
+      <c r="V4">
+        <v>84.615384615384599</v>
+      </c>
+      <c r="W4">
+        <v>15.3846153846153</v>
       </c>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.3">
@@ -2481,11 +2202,11 @@
       <c r="U5">
         <v>0</v>
       </c>
-      <c r="V5" t="s">
-        <v>214</v>
-      </c>
-      <c r="W5" t="s">
-        <v>215</v>
+      <c r="V5">
+        <v>84.210526315789394</v>
+      </c>
+      <c r="W5">
+        <v>15.789473684210501</v>
       </c>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.3">
@@ -2552,11 +2273,11 @@
       <c r="U6">
         <v>1</v>
       </c>
-      <c r="V6" t="s">
-        <v>216</v>
-      </c>
-      <c r="W6" t="s">
-        <v>217</v>
+      <c r="V6">
+        <v>88.8888888888888</v>
+      </c>
+      <c r="W6">
+        <v>11.1111111111111</v>
       </c>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.3">
@@ -2623,11 +2344,11 @@
       <c r="U7">
         <v>1</v>
       </c>
-      <c r="V7" t="s">
-        <v>218</v>
-      </c>
-      <c r="W7" t="s">
-        <v>219</v>
+      <c r="V7">
+        <v>95</v>
+      </c>
+      <c r="W7">
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.3">
@@ -2695,10 +2416,10 @@
         <v>2</v>
       </c>
       <c r="V8" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="W8" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.3">
@@ -2765,11 +2486,11 @@
       <c r="U9">
         <v>2</v>
       </c>
-      <c r="V9" t="s">
-        <v>221</v>
-      </c>
-      <c r="W9" t="s">
-        <v>222</v>
+      <c r="V9">
+        <v>62.5</v>
+      </c>
+      <c r="W9">
+        <v>37.5</v>
       </c>
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.3">
@@ -2836,11 +2557,11 @@
       <c r="U10">
         <v>4</v>
       </c>
-      <c r="V10" t="s">
-        <v>223</v>
-      </c>
-      <c r="W10" t="s">
-        <v>224</v>
+      <c r="V10">
+        <v>95.238095238095198</v>
+      </c>
+      <c r="W10">
+        <v>4.7619047619047503</v>
       </c>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.3">
@@ -2907,11 +2628,11 @@
       <c r="U11">
         <v>0</v>
       </c>
-      <c r="V11" t="s">
-        <v>225</v>
-      </c>
-      <c r="W11" t="s">
-        <v>226</v>
+      <c r="V11">
+        <v>92.857142857142804</v>
+      </c>
+      <c r="W11">
+        <v>7.1428571428571299</v>
       </c>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.3">
@@ -2978,11 +2699,11 @@
       <c r="U12">
         <v>1</v>
       </c>
-      <c r="V12" t="s">
-        <v>227</v>
-      </c>
-      <c r="W12" t="s">
-        <v>228</v>
+      <c r="V12">
+        <v>93.75</v>
+      </c>
+      <c r="W12">
+        <v>6.25</v>
       </c>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.3">
@@ -3049,11 +2770,11 @@
       <c r="U13">
         <v>0</v>
       </c>
-      <c r="V13" t="s">
-        <v>229</v>
-      </c>
-      <c r="W13" t="s">
-        <v>230</v>
+      <c r="V13">
+        <v>76.470588235294102</v>
+      </c>
+      <c r="W13">
+        <v>23.529411764705799</v>
       </c>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.3">
@@ -3120,11 +2841,11 @@
       <c r="U14">
         <v>0</v>
       </c>
-      <c r="V14" t="s">
-        <v>231</v>
-      </c>
-      <c r="W14" t="s">
-        <v>232</v>
+      <c r="V14">
+        <v>86.6666666666666</v>
+      </c>
+      <c r="W14">
+        <v>13.3333333333333</v>
       </c>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.3">
@@ -3191,11 +2912,11 @@
       <c r="U15">
         <v>1</v>
       </c>
-      <c r="V15" t="s">
-        <v>233</v>
-      </c>
-      <c r="W15" t="s">
-        <v>234</v>
+      <c r="V15">
+        <v>83.3333333333333</v>
+      </c>
+      <c r="W15">
+        <v>16.6666666666666</v>
       </c>
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.3">
@@ -3262,11 +2983,11 @@
       <c r="U16">
         <v>0</v>
       </c>
-      <c r="V16" t="s">
-        <v>235</v>
-      </c>
-      <c r="W16" t="s">
-        <v>236</v>
+      <c r="V16">
+        <v>81.25</v>
+      </c>
+      <c r="W16">
+        <v>18.75</v>
       </c>
     </row>
     <row r="17" spans="1:23" x14ac:dyDescent="0.3">
@@ -3333,11 +3054,11 @@
       <c r="U17">
         <v>0</v>
       </c>
-      <c r="V17" t="s">
-        <v>237</v>
-      </c>
-      <c r="W17" t="s">
-        <v>238</v>
+      <c r="V17">
+        <v>92.592592592592595</v>
+      </c>
+      <c r="W17">
+        <v>7.4074074074074003</v>
       </c>
     </row>
     <row r="18" spans="1:23" x14ac:dyDescent="0.3">
@@ -3405,10 +3126,10 @@
         <v>0</v>
       </c>
       <c r="V18" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="W18" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
     </row>
     <row r="19" spans="1:23" x14ac:dyDescent="0.3">
@@ -3475,11 +3196,11 @@
       <c r="U19">
         <v>0</v>
       </c>
-      <c r="V19" t="s">
-        <v>239</v>
-      </c>
-      <c r="W19" t="s">
-        <v>240</v>
+      <c r="V19">
+        <v>90.322580645161295</v>
+      </c>
+      <c r="W19">
+        <v>9.6774193548386993</v>
       </c>
     </row>
     <row r="20" spans="1:23" x14ac:dyDescent="0.3">
@@ -3546,11 +3267,11 @@
       <c r="U20">
         <v>1</v>
       </c>
-      <c r="V20" t="s">
-        <v>241</v>
-      </c>
-      <c r="W20" t="s">
-        <v>242</v>
+      <c r="V20">
+        <v>90.909090909090907</v>
+      </c>
+      <c r="W20">
+        <v>9.0909090909090899</v>
       </c>
     </row>
     <row r="21" spans="1:23" x14ac:dyDescent="0.3">
@@ -3617,11 +3338,11 @@
       <c r="U21">
         <v>0</v>
       </c>
-      <c r="V21" t="s">
-        <v>243</v>
-      </c>
-      <c r="W21" t="s">
-        <v>244</v>
+      <c r="V21">
+        <v>94.736842105263094</v>
+      </c>
+      <c r="W21">
+        <v>5.26315789473683</v>
       </c>
     </row>
     <row r="22" spans="1:23" x14ac:dyDescent="0.3">
@@ -3688,11 +3409,11 @@
       <c r="U22">
         <v>0</v>
       </c>
-      <c r="V22" t="s">
-        <v>245</v>
-      </c>
-      <c r="W22" t="s">
-        <v>246</v>
+      <c r="V22">
+        <v>88.636363636363598</v>
+      </c>
+      <c r="W22">
+        <v>11.363636363636299</v>
       </c>
     </row>
     <row r="23" spans="1:23" x14ac:dyDescent="0.3">
@@ -3759,11 +3480,11 @@
       <c r="U23">
         <v>0</v>
       </c>
-      <c r="V23" t="s">
-        <v>208</v>
-      </c>
-      <c r="W23" t="s">
-        <v>209</v>
+      <c r="V23">
+        <v>78.571428571428498</v>
+      </c>
+      <c r="W23">
+        <v>21.428571428571399</v>
       </c>
     </row>
     <row r="24" spans="1:23" x14ac:dyDescent="0.3">
@@ -3830,11 +3551,11 @@
       <c r="U24">
         <v>4</v>
       </c>
-      <c r="V24" t="s">
-        <v>247</v>
-      </c>
-      <c r="W24" t="s">
-        <v>247</v>
+      <c r="V24">
+        <v>50</v>
+      </c>
+      <c r="W24">
+        <v>50</v>
       </c>
     </row>
     <row r="25" spans="1:23" x14ac:dyDescent="0.3">
@@ -3901,11 +3622,11 @@
       <c r="U25">
         <v>0</v>
       </c>
-      <c r="V25" t="s">
-        <v>248</v>
-      </c>
-      <c r="W25" t="s">
-        <v>249</v>
+      <c r="V25">
+        <v>76.744186046511601</v>
+      </c>
+      <c r="W25">
+        <v>23.2558139534883</v>
       </c>
     </row>
     <row r="26" spans="1:23" x14ac:dyDescent="0.3">
@@ -3972,11 +3693,11 @@
       <c r="U26">
         <v>1</v>
       </c>
-      <c r="V26" t="s">
-        <v>218</v>
-      </c>
-      <c r="W26" t="s">
-        <v>219</v>
+      <c r="V26">
+        <v>95</v>
+      </c>
+      <c r="W26">
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:23" x14ac:dyDescent="0.3">
@@ -4043,11 +3764,11 @@
       <c r="U27">
         <v>0</v>
       </c>
-      <c r="V27" t="s">
-        <v>250</v>
-      </c>
-      <c r="W27" t="s">
-        <v>251</v>
+      <c r="V27">
+        <v>87.5</v>
+      </c>
+      <c r="W27">
+        <v>12.5</v>
       </c>
     </row>
     <row r="28" spans="1:23" x14ac:dyDescent="0.3">
@@ -4114,11 +3835,11 @@
       <c r="U28">
         <v>2</v>
       </c>
-      <c r="V28" t="s">
-        <v>252</v>
-      </c>
-      <c r="W28" t="s">
-        <v>253</v>
+      <c r="V28">
+        <v>100</v>
+      </c>
+      <c r="W28">
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:23" x14ac:dyDescent="0.3">
@@ -4185,11 +3906,11 @@
       <c r="U29">
         <v>2</v>
       </c>
-      <c r="V29" t="s">
-        <v>254</v>
-      </c>
-      <c r="W29" t="s">
-        <v>255</v>
+      <c r="V29">
+        <v>75</v>
+      </c>
+      <c r="W29">
+        <v>25</v>
       </c>
     </row>
     <row r="30" spans="1:23" x14ac:dyDescent="0.3">
@@ -4256,11 +3977,11 @@
       <c r="U30">
         <v>0</v>
       </c>
-      <c r="V30" t="s">
-        <v>256</v>
-      </c>
-      <c r="W30" t="s">
-        <v>257</v>
+      <c r="V30">
+        <v>60</v>
+      </c>
+      <c r="W30">
+        <v>40</v>
       </c>
     </row>
     <row r="31" spans="1:23" x14ac:dyDescent="0.3">
@@ -4327,11 +4048,11 @@
       <c r="U31">
         <v>3</v>
       </c>
-      <c r="V31" t="s">
-        <v>254</v>
-      </c>
-      <c r="W31" t="s">
-        <v>255</v>
+      <c r="V31">
+        <v>75</v>
+      </c>
+      <c r="W31">
+        <v>25</v>
       </c>
     </row>
     <row r="32" spans="1:23" x14ac:dyDescent="0.3">
@@ -4398,11 +4119,11 @@
       <c r="U32">
         <v>1</v>
       </c>
-      <c r="V32" t="s">
-        <v>250</v>
-      </c>
-      <c r="W32" t="s">
-        <v>251</v>
+      <c r="V32">
+        <v>87.5</v>
+      </c>
+      <c r="W32">
+        <v>12.5</v>
       </c>
     </row>
     <row r="33" spans="1:23" x14ac:dyDescent="0.3">
@@ -4469,11 +4190,11 @@
       <c r="U33">
         <v>0</v>
       </c>
-      <c r="V33" t="s">
-        <v>258</v>
-      </c>
-      <c r="W33" t="s">
-        <v>259</v>
+      <c r="V33">
+        <v>78.947368421052602</v>
+      </c>
+      <c r="W33">
+        <v>21.052631578947299</v>
       </c>
     </row>
     <row r="34" spans="1:23" x14ac:dyDescent="0.3">
@@ -4540,11 +4261,11 @@
       <c r="U34">
         <v>2</v>
       </c>
-      <c r="V34" t="s">
-        <v>260</v>
-      </c>
-      <c r="W34" t="s">
-        <v>261</v>
+      <c r="V34">
+        <v>76.785714285714207</v>
+      </c>
+      <c r="W34">
+        <v>23.214285714285701</v>
       </c>
     </row>
     <row r="35" spans="1:23" x14ac:dyDescent="0.3">
@@ -4611,11 +4332,11 @@
       <c r="U35">
         <v>3</v>
       </c>
-      <c r="V35" t="s">
-        <v>262</v>
-      </c>
-      <c r="W35" t="s">
-        <v>263</v>
+      <c r="V35">
+        <v>92.307692307692307</v>
+      </c>
+      <c r="W35">
+        <v>7.6923076923076898</v>
       </c>
     </row>
     <row r="36" spans="1:23" x14ac:dyDescent="0.3">
@@ -4682,11 +4403,11 @@
       <c r="U36">
         <v>3</v>
       </c>
-      <c r="V36" t="s">
-        <v>264</v>
-      </c>
-      <c r="W36" t="s">
-        <v>265</v>
+      <c r="V36">
+        <v>83.783783783783704</v>
+      </c>
+      <c r="W36">
+        <v>16.2162162162162</v>
       </c>
     </row>
     <row r="37" spans="1:23" x14ac:dyDescent="0.3">
@@ -4753,11 +4474,11 @@
       <c r="U37">
         <v>1</v>
       </c>
-      <c r="V37" t="s">
-        <v>266</v>
-      </c>
-      <c r="W37" t="s">
-        <v>267</v>
+      <c r="V37">
+        <v>90.243902439024396</v>
+      </c>
+      <c r="W37">
+        <v>9.7560975609756007</v>
       </c>
     </row>
     <row r="38" spans="1:23" x14ac:dyDescent="0.3">
@@ -4824,11 +4545,11 @@
       <c r="U38">
         <v>0</v>
       </c>
-      <c r="V38" t="s">
-        <v>268</v>
-      </c>
-      <c r="W38" t="s">
-        <v>269</v>
+      <c r="V38">
+        <v>90.476190476190396</v>
+      </c>
+      <c r="W38">
+        <v>9.5238095238095095</v>
       </c>
     </row>
     <row r="39" spans="1:23" x14ac:dyDescent="0.3">
@@ -4896,10 +4617,10 @@
         <v>0</v>
       </c>
       <c r="V39" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="W39" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
     </row>
     <row r="40" spans="1:23" x14ac:dyDescent="0.3">
@@ -4967,10 +4688,10 @@
         <v>0</v>
       </c>
       <c r="V40" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="W40" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
     </row>
     <row r="41" spans="1:23" x14ac:dyDescent="0.3">
@@ -5038,10 +4759,10 @@
         <v>4</v>
       </c>
       <c r="V41" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="W41" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
     </row>
     <row r="42" spans="1:23" x14ac:dyDescent="0.3">
@@ -5108,11 +4829,11 @@
       <c r="U42">
         <v>2</v>
       </c>
-      <c r="V42" t="s">
-        <v>270</v>
-      </c>
-      <c r="W42" t="s">
-        <v>271</v>
+      <c r="V42">
+        <v>83.870967741935402</v>
+      </c>
+      <c r="W42">
+        <v>16.129032258064498</v>
       </c>
     </row>
     <row r="43" spans="1:23" x14ac:dyDescent="0.3">
@@ -5179,11 +4900,11 @@
       <c r="U43">
         <v>1</v>
       </c>
-      <c r="V43" t="s">
-        <v>272</v>
-      </c>
-      <c r="W43" t="s">
-        <v>273</v>
+      <c r="V43">
+        <v>80.769230769230703</v>
+      </c>
+      <c r="W43">
+        <v>19.230769230769202</v>
       </c>
     </row>
     <row r="44" spans="1:23" x14ac:dyDescent="0.3">
@@ -5250,11 +4971,11 @@
       <c r="U44">
         <v>2</v>
       </c>
-      <c r="V44" t="s">
-        <v>274</v>
-      </c>
-      <c r="W44" t="s">
-        <v>275</v>
+      <c r="V44">
+        <v>96.428571428571402</v>
+      </c>
+      <c r="W44">
+        <v>3.5714285714285601</v>
       </c>
     </row>
     <row r="45" spans="1:23" x14ac:dyDescent="0.3">
@@ -5322,10 +5043,10 @@
         <v>0</v>
       </c>
       <c r="V45" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="W45" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
     </row>
     <row r="46" spans="1:23" x14ac:dyDescent="0.3">
@@ -5393,10 +5114,10 @@
         <v>0</v>
       </c>
       <c r="V46" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="W46" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
     </row>
     <row r="47" spans="1:23" x14ac:dyDescent="0.3">
@@ -5463,11 +5184,11 @@
       <c r="U47">
         <v>1</v>
       </c>
-      <c r="V47" t="s">
-        <v>276</v>
-      </c>
-      <c r="W47" t="s">
-        <v>277</v>
+      <c r="V47">
+        <v>80.952380952380906</v>
+      </c>
+      <c r="W47">
+        <v>19.047619047619001</v>
       </c>
     </row>
     <row r="48" spans="1:23" x14ac:dyDescent="0.3">
@@ -5535,10 +5256,10 @@
         <v>2</v>
       </c>
       <c r="V48" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="W48" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
     </row>
     <row r="49" spans="1:23" x14ac:dyDescent="0.3">
@@ -5605,11 +5326,11 @@
       <c r="U49">
         <v>0</v>
       </c>
-      <c r="V49" t="s">
-        <v>216</v>
-      </c>
-      <c r="W49" t="s">
-        <v>217</v>
+      <c r="V49">
+        <v>88.8888888888888</v>
+      </c>
+      <c r="W49">
+        <v>11.1111111111111</v>
       </c>
     </row>
     <row r="50" spans="1:23" x14ac:dyDescent="0.3">
@@ -5676,11 +5397,11 @@
       <c r="U50">
         <v>2</v>
       </c>
-      <c r="V50" t="s">
-        <v>278</v>
-      </c>
-      <c r="W50" t="s">
-        <v>279</v>
+      <c r="V50">
+        <v>78.787878787878697</v>
+      </c>
+      <c r="W50">
+        <v>21.2121212121212</v>
       </c>
     </row>
     <row r="51" spans="1:23" x14ac:dyDescent="0.3">
@@ -5748,10 +5469,10 @@
         <v>1</v>
       </c>
       <c r="V51" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="W51" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
     </row>
     <row r="52" spans="1:23" x14ac:dyDescent="0.3">
@@ -5818,11 +5539,11 @@
       <c r="U52">
         <v>5</v>
       </c>
-      <c r="V52" t="s">
-        <v>280</v>
-      </c>
-      <c r="W52" t="s">
-        <v>281</v>
+      <c r="V52">
+        <v>57.142857142857103</v>
+      </c>
+      <c r="W52">
+        <v>42.857142857142797</v>
       </c>
     </row>
     <row r="53" spans="1:23" x14ac:dyDescent="0.3">
@@ -5889,11 +5610,11 @@
       <c r="U53">
         <v>6</v>
       </c>
-      <c r="V53" t="s">
-        <v>282</v>
-      </c>
-      <c r="W53" t="s">
-        <v>283</v>
+      <c r="V53">
+        <v>90</v>
+      </c>
+      <c r="W53">
+        <v>10</v>
       </c>
     </row>
     <row r="54" spans="1:23" x14ac:dyDescent="0.3">
@@ -5960,11 +5681,11 @@
       <c r="U54">
         <v>2</v>
       </c>
-      <c r="V54" t="s">
-        <v>254</v>
-      </c>
-      <c r="W54" t="s">
-        <v>255</v>
+      <c r="V54">
+        <v>75</v>
+      </c>
+      <c r="W54">
+        <v>25</v>
       </c>
     </row>
     <row r="55" spans="1:23" x14ac:dyDescent="0.3">
@@ -6031,11 +5752,11 @@
       <c r="U55">
         <v>0</v>
       </c>
-      <c r="V55" t="s">
-        <v>252</v>
-      </c>
-      <c r="W55" t="s">
-        <v>253</v>
+      <c r="V55">
+        <v>100</v>
+      </c>
+      <c r="W55">
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:23" x14ac:dyDescent="0.3">
@@ -6102,11 +5823,11 @@
       <c r="U56">
         <v>7</v>
       </c>
-      <c r="V56" t="s">
-        <v>247</v>
-      </c>
-      <c r="W56" t="s">
-        <v>247</v>
+      <c r="V56">
+        <v>50</v>
+      </c>
+      <c r="W56">
+        <v>50</v>
       </c>
     </row>
     <row r="57" spans="1:23" x14ac:dyDescent="0.3">
@@ -6173,11 +5894,11 @@
       <c r="U57">
         <v>2</v>
       </c>
-      <c r="V57" t="s">
-        <v>284</v>
-      </c>
-      <c r="W57" t="s">
-        <v>285</v>
+      <c r="V57">
+        <v>94.117647058823493</v>
+      </c>
+      <c r="W57">
+        <v>5.8823529411764603</v>
       </c>
     </row>
     <row r="58" spans="1:23" x14ac:dyDescent="0.3">
@@ -6244,11 +5965,11 @@
       <c r="U58">
         <v>0</v>
       </c>
-      <c r="V58" t="s">
-        <v>286</v>
-      </c>
-      <c r="W58" t="s">
-        <v>287</v>
+      <c r="V58">
+        <v>83.6065573770491</v>
+      </c>
+      <c r="W58">
+        <v>16.393442622950801</v>
       </c>
     </row>
     <row r="59" spans="1:23" x14ac:dyDescent="0.3">
@@ -6315,11 +6036,11 @@
       <c r="U59">
         <v>0</v>
       </c>
-      <c r="V59" t="s">
-        <v>280</v>
-      </c>
-      <c r="W59" t="s">
-        <v>281</v>
+      <c r="V59">
+        <v>57.142857142857103</v>
+      </c>
+      <c r="W59">
+        <v>42.857142857142797</v>
       </c>
     </row>
     <row r="60" spans="1:23" x14ac:dyDescent="0.3">
@@ -6386,11 +6107,11 @@
       <c r="U60">
         <v>0</v>
       </c>
-      <c r="V60" t="s">
-        <v>288</v>
-      </c>
-      <c r="W60" t="s">
-        <v>289</v>
+      <c r="V60">
+        <v>91.6666666666666</v>
+      </c>
+      <c r="W60">
+        <v>8.3333333333333197</v>
       </c>
     </row>
     <row r="61" spans="1:23" x14ac:dyDescent="0.3">
@@ -6457,11 +6178,11 @@
       <c r="U61">
         <v>1</v>
       </c>
-      <c r="V61" t="s">
-        <v>290</v>
-      </c>
-      <c r="W61" t="s">
-        <v>291</v>
+      <c r="V61">
+        <v>90.625</v>
+      </c>
+      <c r="W61">
+        <v>9.375</v>
       </c>
     </row>
     <row r="62" spans="1:23" x14ac:dyDescent="0.3">
@@ -6528,11 +6249,11 @@
       <c r="U62">
         <v>0</v>
       </c>
-      <c r="V62" t="s">
-        <v>231</v>
-      </c>
-      <c r="W62" t="s">
-        <v>232</v>
+      <c r="V62">
+        <v>86.6666666666666</v>
+      </c>
+      <c r="W62">
+        <v>13.3333333333333</v>
       </c>
     </row>
     <row r="63" spans="1:23" x14ac:dyDescent="0.3">
@@ -6599,11 +6320,11 @@
       <c r="U63">
         <v>0</v>
       </c>
-      <c r="V63" t="s">
-        <v>292</v>
-      </c>
-      <c r="W63" t="s">
-        <v>293</v>
+      <c r="V63">
+        <v>89.285714285714207</v>
+      </c>
+      <c r="W63">
+        <v>10.714285714285699</v>
       </c>
     </row>
     <row r="64" spans="1:23" x14ac:dyDescent="0.3">
@@ -6670,11 +6391,11 @@
       <c r="U64">
         <v>3</v>
       </c>
-      <c r="V64" t="s">
-        <v>294</v>
-      </c>
-      <c r="W64" t="s">
-        <v>295</v>
+      <c r="V64">
+        <v>56.25</v>
+      </c>
+      <c r="W64">
+        <v>43.75</v>
       </c>
     </row>
     <row r="65" spans="1:23" x14ac:dyDescent="0.3">
@@ -6741,11 +6462,11 @@
       <c r="U65">
         <v>0</v>
       </c>
-      <c r="V65" t="s">
-        <v>252</v>
-      </c>
-      <c r="W65" t="s">
-        <v>253</v>
+      <c r="V65">
+        <v>100</v>
+      </c>
+      <c r="W65">
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:23" x14ac:dyDescent="0.3">
@@ -6812,11 +6533,11 @@
       <c r="U66">
         <v>0</v>
       </c>
-      <c r="V66" t="s">
-        <v>254</v>
-      </c>
-      <c r="W66" t="s">
-        <v>255</v>
+      <c r="V66">
+        <v>75</v>
+      </c>
+      <c r="W66">
+        <v>25</v>
       </c>
     </row>
     <row r="67" spans="1:23" x14ac:dyDescent="0.3">
@@ -6883,11 +6604,11 @@
       <c r="U67">
         <v>1</v>
       </c>
-      <c r="V67" t="s">
-        <v>262</v>
-      </c>
-      <c r="W67" t="s">
-        <v>263</v>
+      <c r="V67">
+        <v>92.307692307692307</v>
+      </c>
+      <c r="W67">
+        <v>7.6923076923076898</v>
       </c>
     </row>
     <row r="68" spans="1:23" x14ac:dyDescent="0.3">
@@ -6954,11 +6675,11 @@
       <c r="U68">
         <v>0</v>
       </c>
-      <c r="V68" t="s">
-        <v>296</v>
-      </c>
-      <c r="W68" t="s">
-        <v>297</v>
+      <c r="V68">
+        <v>96.296296296296205</v>
+      </c>
+      <c r="W68">
+        <v>3.7037037037037002</v>
       </c>
     </row>
     <row r="69" spans="1:23" x14ac:dyDescent="0.3">
@@ -7025,11 +6746,11 @@
       <c r="U69">
         <v>1</v>
       </c>
-      <c r="V69" t="s">
-        <v>298</v>
-      </c>
-      <c r="W69" t="s">
-        <v>299</v>
+      <c r="V69">
+        <v>66.6666666666666</v>
+      </c>
+      <c r="W69">
+        <v>33.3333333333333</v>
       </c>
     </row>
     <row r="70" spans="1:23" x14ac:dyDescent="0.3">
@@ -7097,10 +6818,10 @@
         <v>0</v>
       </c>
       <c r="V70" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="W70" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
     </row>
     <row r="71" spans="1:23" x14ac:dyDescent="0.3">
@@ -7167,11 +6888,11 @@
       <c r="U71">
         <v>0</v>
       </c>
-      <c r="V71" t="s">
-        <v>300</v>
-      </c>
-      <c r="W71" t="s">
-        <v>301</v>
+      <c r="V71">
+        <v>75.862068965517196</v>
+      </c>
+      <c r="W71">
+        <v>24.137931034482701</v>
       </c>
     </row>
     <row r="72" spans="1:23" x14ac:dyDescent="0.3">
@@ -7239,10 +6960,10 @@
         <v>0</v>
       </c>
       <c r="V72" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="W72" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
     </row>
     <row r="73" spans="1:23" x14ac:dyDescent="0.3">
@@ -7309,11 +7030,11 @@
       <c r="U73">
         <v>0</v>
       </c>
-      <c r="V73" t="s">
-        <v>302</v>
-      </c>
-      <c r="W73" t="s">
-        <v>303</v>
+      <c r="V73">
+        <v>71.428571428571402</v>
+      </c>
+      <c r="W73">
+        <v>28.571428571428498</v>
       </c>
     </row>
     <row r="74" spans="1:23" x14ac:dyDescent="0.3">
@@ -7380,11 +7101,11 @@
       <c r="U74">
         <v>2</v>
       </c>
-      <c r="V74" t="s">
-        <v>304</v>
-      </c>
-      <c r="W74" t="s">
-        <v>305</v>
+      <c r="V74">
+        <v>76</v>
+      </c>
+      <c r="W74">
+        <v>24</v>
       </c>
     </row>
     <row r="75" spans="1:23" x14ac:dyDescent="0.3">
@@ -7451,11 +7172,11 @@
       <c r="U75">
         <v>0</v>
       </c>
-      <c r="V75" t="s">
-        <v>306</v>
-      </c>
-      <c r="W75" t="s">
-        <v>307</v>
+      <c r="V75">
+        <v>91.304347826086897</v>
+      </c>
+      <c r="W75">
+        <v>8.6956521739130395</v>
       </c>
     </row>
     <row r="76" spans="1:23" x14ac:dyDescent="0.3">
@@ -7522,11 +7243,11 @@
       <c r="U76">
         <v>0</v>
       </c>
-      <c r="V76" t="s">
-        <v>308</v>
-      </c>
-      <c r="W76" t="s">
-        <v>309</v>
+      <c r="V76">
+        <v>77.142857142857096</v>
+      </c>
+      <c r="W76">
+        <v>22.857142857142801</v>
       </c>
     </row>
   </sheetData>
@@ -7540,7 +7261,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0EE1E7D-EAFC-4A2F-AF1A-E8C144B15E47}">
-  <dimension ref="A1:AB9"/>
+  <dimension ref="A1:AB14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="11.88671875" bestFit="1" customWidth="1"/>
@@ -7997,6 +7718,18 @@
       <c r="J6" t="s">
         <v>204</v>
       </c>
+      <c r="K6" t="s">
+        <v>213</v>
+      </c>
+      <c r="L6" t="s">
+        <v>215</v>
+      </c>
+      <c r="M6" t="s">
+        <v>214</v>
+      </c>
+      <c r="N6" t="s">
+        <v>216</v>
+      </c>
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.3">
       <c r="C7">
@@ -8031,6 +7764,22 @@
         <f t="array" ref="J7">_xlfn.STDEV.P(IF(data[Sesion]=A2,data[Completados]))</f>
         <v>1.2985826612384852</v>
       </c>
+      <c r="K7">
+        <f>AVERAGEIF(data[Sesion],A2,data[% Aciertos])</f>
+        <v>81.500533061927996</v>
+      </c>
+      <c r="L7" cm="1">
+        <f t="array" ref="L7">_xlfn.STDEV.P(IF(data[Sesion]=A2,data[% Aciertos]))</f>
+        <v>13.661094774056064</v>
+      </c>
+      <c r="M7">
+        <f>AVERAGEIF(data[Sesion],A2,data[% Mal])</f>
+        <v>18.499466938071933</v>
+      </c>
+      <c r="N7" cm="1">
+        <f t="array" ref="N7">_xlfn.STDEV.P(IF(data[Sesion]=A2,data[% Mal]))</f>
+        <v>13.661094774056048</v>
+      </c>
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.3">
       <c r="C8">
@@ -8065,6 +7814,22 @@
         <f t="array" ref="J8">_xlfn.STDEV.P(IF(data[Sesion]=A3,data[Completados]))</f>
         <v>0.8660254037844386</v>
       </c>
+      <c r="K8">
+        <f>AVERAGEIF(data[Sesion],A3,data[% Aciertos])</f>
+        <v>81.868131868131854</v>
+      </c>
+      <c r="L8" cm="1">
+        <f t="array" ref="L8">_xlfn.STDEV.P(IF(data[Sesion]=A3,data[% Aciertos]))</f>
+        <v>10.439560439560449</v>
+      </c>
+      <c r="M8">
+        <f>AVERAGEIF(data[Sesion],A3,data[% Mal])</f>
+        <v>18.131868131868096</v>
+      </c>
+      <c r="N8" cm="1">
+        <f t="array" ref="N8">_xlfn.STDEV.P(IF(data[Sesion]=A3,data[% Mal]))</f>
+        <v>10.439560439560402</v>
+      </c>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.3">
       <c r="C9">
@@ -8099,6 +7864,105 @@
         <f t="array" ref="J9">_xlfn.STDEV.P(IF(data[Sesion]=A4,data[Completados]))</f>
         <v>1.4609691054308163</v>
       </c>
+      <c r="K9">
+        <f>AVERAGEIF(data[Sesion],A4,data[% Aciertos])</f>
+        <v>84.678266813816748</v>
+      </c>
+      <c r="L9" cm="1">
+        <f t="array" ref="L9">_xlfn.STDEV.P(IF(data[Sesion]=A4,data[% Aciertos]))</f>
+        <v>9.7359064227108103</v>
+      </c>
+      <c r="M9">
+        <f>AVERAGEIF(data[Sesion],A4,data[% Mal])</f>
+        <v>15.321733186183183</v>
+      </c>
+      <c r="N9" cm="1">
+        <f t="array" ref="N9">_xlfn.STDEV.P(IF(data[Sesion]=A4,data[% Mal]))</f>
+        <v>9.7359064227106646</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="H11" t="s">
+        <v>3</v>
+      </c>
+      <c r="I11" t="s">
+        <v>209</v>
+      </c>
+      <c r="J11" t="s">
+        <v>210</v>
+      </c>
+      <c r="K11" t="s">
+        <v>211</v>
+      </c>
+      <c r="L11" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="H12">
+        <f>SUMIF(data[Sesion],A2,data[Num intentos])</f>
+        <v>343</v>
+      </c>
+      <c r="I12">
+        <f>SUMIF(data[Sesion],A2,data[Completados])</f>
+        <v>35</v>
+      </c>
+      <c r="J12">
+        <f>100*I12/H12</f>
+        <v>10.204081632653061</v>
+      </c>
+      <c r="K12">
+        <f>H12-I12</f>
+        <v>308</v>
+      </c>
+      <c r="L12">
+        <f>100*K12/H12</f>
+        <v>89.795918367346943</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="H13">
+        <f>SUMIF(data[Sesion],A3,data[Num intentos])</f>
+        <v>14</v>
+      </c>
+      <c r="I13">
+        <f>SUMIF(data[Sesion],A3,data[Completados])</f>
+        <v>2</v>
+      </c>
+      <c r="J13">
+        <f t="shared" ref="J13:J14" si="0">100*I13/H13</f>
+        <v>14.285714285714286</v>
+      </c>
+      <c r="K13">
+        <f t="shared" ref="K13:K14" si="1">H13-I13</f>
+        <v>12</v>
+      </c>
+      <c r="L13">
+        <f t="shared" ref="L13:L14" si="2">100*K13/H13</f>
+        <v>85.714285714285708</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="H14">
+        <f>SUMIF(data[Sesion],A4,data[Num intentos])</f>
+        <v>310</v>
+      </c>
+      <c r="I14">
+        <f>SUMIF(data[Sesion],A4,data[Completados])</f>
+        <v>46</v>
+      </c>
+      <c r="J14">
+        <f t="shared" si="0"/>
+        <v>14.838709677419354</v>
+      </c>
+      <c r="K14">
+        <f t="shared" si="1"/>
+        <v>264</v>
+      </c>
+      <c r="L14">
+        <f t="shared" si="2"/>
+        <v>85.161290322580641</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/datosSesionesPruebaMedias.xlsx
+++ b/datosSesionesPruebaMedias.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\hlocal\C_TFG\Datos\Mision Colombia-20260209T150018Z-3-001\jsonToCsv_TFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEF10A7C-BE4B-4AB3-A375-3AB17A2AD797}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{733D5949-E9D4-4036-82D0-8D59C4F20B2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Hoja1" sheetId="2" r:id="rId2"/>
+    <sheet name="Hoja1" sheetId="3" r:id="rId2"/>
+    <sheet name="Hoja2" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlchart.v1.0" hidden="1">Sheet1!$B$2:$B$76</definedName>
@@ -61,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="217">
   <si>
     <t>ID</t>
   </si>
@@ -7260,6 +7261,712 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{985F84CE-9629-4DFF-819E-3ECA9135BC5B}">
+  <dimension ref="A1:AB14"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D1" t="s">
+        <v>174</v>
+      </c>
+      <c r="E1" t="s">
+        <v>175</v>
+      </c>
+      <c r="F1" t="s">
+        <v>176</v>
+      </c>
+      <c r="G1" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1" t="s">
+        <v>172</v>
+      </c>
+      <c r="I1" t="s">
+        <v>177</v>
+      </c>
+      <c r="J1" t="s">
+        <v>178</v>
+      </c>
+      <c r="K1" t="s">
+        <v>179</v>
+      </c>
+      <c r="L1" t="s">
+        <v>180</v>
+      </c>
+      <c r="M1" t="s">
+        <v>181</v>
+      </c>
+      <c r="N1" t="s">
+        <v>182</v>
+      </c>
+      <c r="O1" t="s">
+        <v>183</v>
+      </c>
+      <c r="P1" t="s">
+        <v>184</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>185</v>
+      </c>
+      <c r="R1" t="s">
+        <v>186</v>
+      </c>
+      <c r="S1" t="s">
+        <v>187</v>
+      </c>
+      <c r="T1" t="s">
+        <v>188</v>
+      </c>
+      <c r="U1" t="s">
+        <v>189</v>
+      </c>
+      <c r="V1" t="s">
+        <v>190</v>
+      </c>
+      <c r="W1" t="s">
+        <v>191</v>
+      </c>
+      <c r="X1" t="s">
+        <v>192</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>193</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>194</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>195</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <f>COUNTIF(data[Sesion],A2)</f>
+        <v>43</v>
+      </c>
+      <c r="C2">
+        <f>AVERAGEIF(data[Sesion],A2,data[Pasos planificados])</f>
+        <v>14.13953488372093</v>
+      </c>
+      <c r="D2" cm="1">
+        <f t="array" ref="D2">_xlfn.STDEV.P(IF(data[Sesion]=A2,data[Pasos planificados]))</f>
+        <v>12.474311082900297</v>
+      </c>
+      <c r="E2">
+        <f>AVERAGEIF(data[Sesion],A2,data[Pasos ejecutados])</f>
+        <v>11.651162790697674</v>
+      </c>
+      <c r="F2" cm="1">
+        <f t="array" ref="F2">_xlfn.STDEV.P(IF(data[Sesion]=A2,data[Pasos ejecutados]))</f>
+        <v>10.573955984377166</v>
+      </c>
+      <c r="G2">
+        <f>AVERAGEIF(data[Sesion],A2,data[Errores ejecucion])</f>
+        <v>2.4883720930232558</v>
+      </c>
+      <c r="H2" cm="1">
+        <f t="array" ref="H2">_xlfn.STDEV.P(IF(data[Sesion]=A2,data[Errores ejecucion]))</f>
+        <v>2.9044640303173401</v>
+      </c>
+      <c r="I2">
+        <f>AVERAGEIF(data[Sesion],A2,data[Num dormir planificado])</f>
+        <v>6.7209302325581399</v>
+      </c>
+      <c r="J2" cm="1">
+        <f t="array" ref="J2">_xlfn.STDEV.P(IF(data[Sesion]=A2,data[Num dormir planificado]))</f>
+        <v>5.7032246341601036</v>
+      </c>
+      <c r="K2">
+        <f>AVERAGEIF(data[Sesion],A2,data[Correctos dormir])</f>
+        <v>6.441860465116279</v>
+      </c>
+      <c r="L2" cm="1">
+        <f t="array" ref="L2">_xlfn.STDEV.P(IF(data[Sesion]=A2,data[Correctos dormir]))</f>
+        <v>5.5543920420937338</v>
+      </c>
+      <c r="M2">
+        <f>AVERAGEIF(data[Sesion],A2,data[Errores dormir])</f>
+        <v>0.27906976744186046</v>
+      </c>
+      <c r="N2" cm="1">
+        <f t="array" ref="N2">_xlfn.STDEV.P(IF(data[Sesion]=A2,data[Errores dormir]))</f>
+        <v>0.54241412975305114</v>
+      </c>
+      <c r="O2">
+        <f>AVERAGEIF(data[Sesion],A2,data[Num ubicacion planificado])</f>
+        <v>7.4186046511627906</v>
+      </c>
+      <c r="P2" cm="1">
+        <f t="array" ref="P2">_xlfn.STDEV.P(IF(data[Sesion]=A2,data[Num ubicacion planificado]))</f>
+        <v>7.4466554319888516</v>
+      </c>
+      <c r="Q2">
+        <f>AVERAGEIF(data[Sesion],A2,data[Correctos ubicacion])</f>
+        <v>5.2093023255813957</v>
+      </c>
+      <c r="R2" cm="1">
+        <f t="array" ref="R2">_xlfn.STDEV.P(IF(data[Sesion]=A2,data[Correctos ubicacion]))</f>
+        <v>5.5888516086892199</v>
+      </c>
+      <c r="S2">
+        <f>AVERAGEIF(data[Sesion],A2,data[Errores ubicacion])</f>
+        <v>2.2093023255813953</v>
+      </c>
+      <c r="T2" cm="1">
+        <f t="array" ref="T2">_xlfn.STDEV.P(IF(data[Sesion]=A2,data[Errores ubicacion]))</f>
+        <v>2.791666498497233</v>
+      </c>
+      <c r="U2">
+        <f>AVERAGEIF(data[Sesion],A2,data[Paradas posibles])</f>
+        <v>16.325581395348838</v>
+      </c>
+      <c r="V2" cm="1">
+        <f t="array" ref="V2">_xlfn.STDEV.P(IF(data[Sesion]=A2,data[Paradas posibles]))</f>
+        <v>8.8678172512470237</v>
+      </c>
+      <c r="W2">
+        <f>AVERAGEIF(data[Sesion],A2,data[Paradas realizadas])</f>
+        <v>11.13953488372093</v>
+      </c>
+      <c r="X2" cm="1">
+        <f t="array" ref="X2">_xlfn.STDEV.P(IF(data[Sesion]=A2,data[Paradas realizadas]))</f>
+        <v>7.2258624506532003</v>
+      </c>
+      <c r="Y2">
+        <f>AVERAGEIF(data[Sesion],A2,data[Errores parada por tiempo excedido])</f>
+        <v>0.81395348837209303</v>
+      </c>
+      <c r="Z2" cm="1">
+        <f t="array" ref="Z2">_xlfn.STDEV.P(IF(data[Sesion]=A2,data[Errores parada por tiempo excedido]))</f>
+        <v>1.1259272964567633</v>
+      </c>
+      <c r="AA2">
+        <f>AVERAGEIF(data[Sesion],A2,data[Num errores por tiempo excedido])</f>
+        <v>0.93023255813953487</v>
+      </c>
+      <c r="AB2" cm="1">
+        <f t="array" ref="AB2">_xlfn.STDEV.P(IF(data[Sesion]=A2,data[Num errores por tiempo excedido]))</f>
+        <v>1.2830803929426717</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <f>COUNTIF(data[Sesion],A3)</f>
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <f>AVERAGEIF(data[Sesion],A3,data[Pasos planificados])</f>
+        <v>5</v>
+      </c>
+      <c r="D3" cm="1">
+        <f t="array" ref="D3">_xlfn.STDEV.P(IF(data[Sesion]=A3,data[Pasos planificados]))</f>
+        <v>5.4313902456001077</v>
+      </c>
+      <c r="E3">
+        <f>AVERAGEIF(data[Sesion],A3,data[Pasos ejecutados])</f>
+        <v>4.25</v>
+      </c>
+      <c r="F3" cm="1">
+        <f t="array" ref="F3">_xlfn.STDEV.P(IF(data[Sesion]=A3,data[Pasos ejecutados]))</f>
+        <v>4.9180788932265003</v>
+      </c>
+      <c r="G3">
+        <f>AVERAGEIF(data[Sesion],A3,data[Errores ejecucion])</f>
+        <v>0.75</v>
+      </c>
+      <c r="H3" cm="1">
+        <f t="array" ref="H3">_xlfn.STDEV.P(IF(data[Sesion]=A3,data[Errores ejecucion]))</f>
+        <v>0.82915619758884995</v>
+      </c>
+      <c r="I3">
+        <f>AVERAGEIF(data[Sesion],A3,data[Num dormir planificado])</f>
+        <v>3.25</v>
+      </c>
+      <c r="J3" cm="1">
+        <f t="array" ref="J3">_xlfn.STDEV.P(IF(data[Sesion]=A3,data[Num dormir planificado]))</f>
+        <v>3.4186985827943359</v>
+      </c>
+      <c r="K3">
+        <f>AVERAGEIF(data[Sesion],A3,data[Correctos dormir])</f>
+        <v>3</v>
+      </c>
+      <c r="L3" cm="1">
+        <f t="array" ref="L3">_xlfn.STDEV.P(IF(data[Sesion]=A3,data[Correctos dormir]))</f>
+        <v>3.3166247903553998</v>
+      </c>
+      <c r="M3">
+        <f>AVERAGEIF(data[Sesion],A3,data[Errores dormir])</f>
+        <v>0.25</v>
+      </c>
+      <c r="N3" cm="1">
+        <f t="array" ref="N3">_xlfn.STDEV.P(IF(data[Sesion]=A3,data[Errores dormir]))</f>
+        <v>0.4330127018922193</v>
+      </c>
+      <c r="O3">
+        <f>AVERAGEIF(data[Sesion],A3,data[Num ubicacion planificado])</f>
+        <v>1.75</v>
+      </c>
+      <c r="P3" cm="1">
+        <f t="array" ref="P3">_xlfn.STDEV.P(IF(data[Sesion]=A3,data[Num ubicacion planificado]))</f>
+        <v>2.0463381929681126</v>
+      </c>
+      <c r="Q3">
+        <f>AVERAGEIF(data[Sesion],A3,data[Correctos ubicacion])</f>
+        <v>1.25</v>
+      </c>
+      <c r="R3" cm="1">
+        <f t="array" ref="R3">_xlfn.STDEV.P(IF(data[Sesion]=A3,data[Correctos ubicacion]))</f>
+        <v>1.6393596310755001</v>
+      </c>
+      <c r="S3">
+        <f>AVERAGEIF(data[Sesion],A3,data[Errores ubicacion])</f>
+        <v>0.5</v>
+      </c>
+      <c r="T3" cm="1">
+        <f t="array" ref="T3">_xlfn.STDEV.P(IF(data[Sesion]=A3,data[Errores ubicacion]))</f>
+        <v>0.5</v>
+      </c>
+      <c r="U3">
+        <f>AVERAGEIF(data[Sesion],A3,data[Paradas posibles])</f>
+        <v>6.25</v>
+      </c>
+      <c r="V3" cm="1">
+        <f t="array" ref="V3">_xlfn.STDEV.P(IF(data[Sesion]=A3,data[Paradas posibles]))</f>
+        <v>5.7608593109014565</v>
+      </c>
+      <c r="W3">
+        <f>AVERAGEIF(data[Sesion],A3,data[Paradas realizadas])</f>
+        <v>4</v>
+      </c>
+      <c r="X3" cm="1">
+        <f t="array" ref="X3">_xlfn.STDEV.P(IF(data[Sesion]=A3,data[Paradas realizadas]))</f>
+        <v>4.0620192023179804</v>
+      </c>
+      <c r="Y3">
+        <f>AVERAGEIF(data[Sesion],A3,data[Errores parada por tiempo excedido])</f>
+        <v>0.25</v>
+      </c>
+      <c r="Z3" cm="1">
+        <f t="array" ref="Z3">_xlfn.STDEV.P(IF(data[Sesion]=A3,data[Errores parada por tiempo excedido]))</f>
+        <v>0.4330127018922193</v>
+      </c>
+      <c r="AA3">
+        <f>AVERAGEIF(data[Sesion],A3,data[Num errores por tiempo excedido])</f>
+        <v>0.25</v>
+      </c>
+      <c r="AB3" cm="1">
+        <f t="array" ref="AB3">_xlfn.STDEV.P(IF(data[Sesion]=A3,data[Num errores por tiempo excedido]))</f>
+        <v>0.4330127018922193</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <f>COUNTIF(data[Sesion],A4)</f>
+        <v>27</v>
+      </c>
+      <c r="C4">
+        <f>AVERAGEIF(data[Sesion],A4,data[Pasos planificados])</f>
+        <v>31.777777777777779</v>
+      </c>
+      <c r="D4" cm="1">
+        <f t="array" ref="D4">_xlfn.STDEV.P(IF(data[Sesion]=A4,data[Pasos planificados]))</f>
+        <v>11.901862080685287</v>
+      </c>
+      <c r="E4">
+        <f>AVERAGEIF(data[Sesion],A4,data[Pasos ejecutados])</f>
+        <v>26.703703703703702</v>
+      </c>
+      <c r="F4" cm="1">
+        <f t="array" ref="F4">_xlfn.STDEV.P(IF(data[Sesion]=A4,data[Pasos ejecutados]))</f>
+        <v>10.10249259603536</v>
+      </c>
+      <c r="G4">
+        <f>AVERAGEIF(data[Sesion],A4,data[Errores ejecucion])</f>
+        <v>5.0740740740740744</v>
+      </c>
+      <c r="H4" cm="1">
+        <f t="array" ref="H4">_xlfn.STDEV.P(IF(data[Sesion]=A4,data[Errores ejecucion]))</f>
+        <v>3.7508115262732336</v>
+      </c>
+      <c r="I4">
+        <f>AVERAGEIF(data[Sesion],A4,data[Num dormir planificado])</f>
+        <v>15.777777777777779</v>
+      </c>
+      <c r="J4" cm="1">
+        <f t="array" ref="J4">_xlfn.STDEV.P(IF(data[Sesion]=A4,data[Num dormir planificado]))</f>
+        <v>5.3147825524895103</v>
+      </c>
+      <c r="K4">
+        <f>AVERAGEIF(data[Sesion],A4,data[Correctos dormir])</f>
+        <v>14.851851851851851</v>
+      </c>
+      <c r="L4" cm="1">
+        <f t="array" ref="L4">_xlfn.STDEV.P(IF(data[Sesion]=A4,data[Correctos dormir]))</f>
+        <v>5.2543012623782719</v>
+      </c>
+      <c r="M4">
+        <f>AVERAGEIF(data[Sesion],A4,data[Errores dormir])</f>
+        <v>0.92592592592592593</v>
+      </c>
+      <c r="N4" cm="1">
+        <f t="array" ref="N4">_xlfn.STDEV.P(IF(data[Sesion]=A4,data[Errores dormir]))</f>
+        <v>2.0534690778709797</v>
+      </c>
+      <c r="O4">
+        <f>AVERAGEIF(data[Sesion],A4,data[Num ubicacion planificado])</f>
+        <v>16</v>
+      </c>
+      <c r="P4" cm="1">
+        <f t="array" ref="P4">_xlfn.STDEV.P(IF(data[Sesion]=A4,data[Num ubicacion planificado]))</f>
+        <v>8.1649658092772608</v>
+      </c>
+      <c r="Q4">
+        <f>AVERAGEIF(data[Sesion],A4,data[Correctos ubicacion])</f>
+        <v>11.851851851851851</v>
+      </c>
+      <c r="R4" cm="1">
+        <f t="array" ref="R4">_xlfn.STDEV.P(IF(data[Sesion]=A4,data[Correctos ubicacion]))</f>
+        <v>6.6092174899835134</v>
+      </c>
+      <c r="S4">
+        <f>AVERAGEIF(data[Sesion],A4,data[Errores ubicacion])</f>
+        <v>4.1481481481481479</v>
+      </c>
+      <c r="T4" cm="1">
+        <f t="array" ref="T4">_xlfn.STDEV.P(IF(data[Sesion]=A4,data[Errores ubicacion]))</f>
+        <v>2.8376268606485855</v>
+      </c>
+      <c r="U4">
+        <f>AVERAGEIF(data[Sesion],A4,data[Paradas posibles])</f>
+        <v>32.111111111111114</v>
+      </c>
+      <c r="V4" cm="1">
+        <f t="array" ref="V4">_xlfn.STDEV.P(IF(data[Sesion]=A4,data[Paradas posibles]))</f>
+        <v>11.951548275133206</v>
+      </c>
+      <c r="W4">
+        <f>AVERAGEIF(data[Sesion],A4,data[Paradas realizadas])</f>
+        <v>23.777777777777779</v>
+      </c>
+      <c r="X4" cm="1">
+        <f t="array" ref="X4">_xlfn.STDEV.P(IF(data[Sesion]=A4,data[Paradas realizadas]))</f>
+        <v>9.1016210738988423</v>
+      </c>
+      <c r="Y4">
+        <f>AVERAGEIF(data[Sesion],A4,data[Errores parada por tiempo excedido])</f>
+        <v>1.1851851851851851</v>
+      </c>
+      <c r="Z4" cm="1">
+        <f t="array" ref="Z4">_xlfn.STDEV.P(IF(data[Sesion]=A4,data[Errores parada por tiempo excedido]))</f>
+        <v>1.4665918424609874</v>
+      </c>
+      <c r="AA4">
+        <f>AVERAGEIF(data[Sesion],A4,data[Num errores por tiempo excedido])</f>
+        <v>1.4814814814814814</v>
+      </c>
+      <c r="AB4" cm="1">
+        <f t="array" ref="AB4">_xlfn.STDEV.P(IF(data[Sesion]=A4,data[Num errores por tiempo excedido]))</f>
+        <v>1.8129241852622839</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="C6" t="s">
+        <v>197</v>
+      </c>
+      <c r="D6" t="s">
+        <v>198</v>
+      </c>
+      <c r="E6" t="s">
+        <v>199</v>
+      </c>
+      <c r="F6" t="s">
+        <v>200</v>
+      </c>
+      <c r="G6" t="s">
+        <v>201</v>
+      </c>
+      <c r="H6" t="s">
+        <v>202</v>
+      </c>
+      <c r="I6" t="s">
+        <v>203</v>
+      </c>
+      <c r="J6" t="s">
+        <v>204</v>
+      </c>
+      <c r="K6" t="s">
+        <v>213</v>
+      </c>
+      <c r="L6" t="s">
+        <v>215</v>
+      </c>
+      <c r="M6" t="s">
+        <v>214</v>
+      </c>
+      <c r="N6" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="C7">
+        <f>AVERAGEIF(data[Sesion],A2,data[Tiempo duracion])</f>
+        <v>1391.2371627906978</v>
+      </c>
+      <c r="D7" cm="1">
+        <f t="array" ref="D7">_xlfn.STDEV.P(IF(data[Sesion]=A2,data[Tiempo duracion]))</f>
+        <v>752.30981030420571</v>
+      </c>
+      <c r="E7">
+        <f>AVERAGEIF(data[Sesion],A2,data[Num niveles])</f>
+        <v>2.5116279069767442</v>
+      </c>
+      <c r="F7" cm="1">
+        <f t="array" ref="F7">_xlfn.STDEV.P(IF(data[Sesion]=A2,data[Num niveles]))</f>
+        <v>1.2270610193742251</v>
+      </c>
+      <c r="G7">
+        <f>AVERAGEIF(data[Sesion],A2,data[Num intentos])</f>
+        <v>7.9767441860465116</v>
+      </c>
+      <c r="H7" cm="1">
+        <f t="array" ref="H7">_xlfn.STDEV.P(IF(data[Sesion]=A2,data[Num intentos]))</f>
+        <v>3.2456652458390702</v>
+      </c>
+      <c r="I7">
+        <f>AVERAGEIF(data[Sesion],A2,data[Completados])</f>
+        <v>0.81395348837209303</v>
+      </c>
+      <c r="J7" cm="1">
+        <f t="array" ref="J7">_xlfn.STDEV.P(IF(data[Sesion]=A2,data[Completados]))</f>
+        <v>1.2985826612384852</v>
+      </c>
+      <c r="K7">
+        <f>AVERAGEIF(data[Sesion],A2,data[% Aciertos])</f>
+        <v>81.500533061927996</v>
+      </c>
+      <c r="L7" cm="1">
+        <f t="array" ref="L7">_xlfn.STDEV.P(IF(data[Sesion]=A2,data[% Aciertos]))</f>
+        <v>13.661094774056064</v>
+      </c>
+      <c r="M7">
+        <f>AVERAGEIF(data[Sesion],A2,data[% Mal])</f>
+        <v>18.499466938071933</v>
+      </c>
+      <c r="N7" cm="1">
+        <f t="array" ref="N7">_xlfn.STDEV.P(IF(data[Sesion]=A2,data[% Mal]))</f>
+        <v>13.661094774056048</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="C8">
+        <f>AVERAGEIF(data[Sesion],A3,data[Tiempo duracion])</f>
+        <v>548.99350000000004</v>
+      </c>
+      <c r="D8" cm="1">
+        <f t="array" ref="D8">_xlfn.STDEV.P(IF(data[Sesion]=A3,data[Tiempo duracion]))</f>
+        <v>399.60607282578923</v>
+      </c>
+      <c r="E8">
+        <f>AVERAGEIF(data[Sesion],A3,data[Num niveles])</f>
+        <v>1.25</v>
+      </c>
+      <c r="F8" cm="1">
+        <f t="array" ref="F8">_xlfn.STDEV.P(IF(data[Sesion]=A3,data[Num niveles]))</f>
+        <v>0.4330127018922193</v>
+      </c>
+      <c r="G8">
+        <f>AVERAGEIF(data[Sesion],A3,data[Num intentos])</f>
+        <v>3.5</v>
+      </c>
+      <c r="H8" cm="1">
+        <f t="array" ref="H8">_xlfn.STDEV.P(IF(data[Sesion]=A3,data[Num intentos]))</f>
+        <v>2.8722813232690143</v>
+      </c>
+      <c r="I8">
+        <f>AVERAGEIF(data[Sesion],A3,data[Completados])</f>
+        <v>0.5</v>
+      </c>
+      <c r="J8" cm="1">
+        <f t="array" ref="J8">_xlfn.STDEV.P(IF(data[Sesion]=A3,data[Completados]))</f>
+        <v>0.8660254037844386</v>
+      </c>
+      <c r="K8">
+        <f>AVERAGEIF(data[Sesion],A3,data[% Aciertos])</f>
+        <v>81.868131868131854</v>
+      </c>
+      <c r="L8" cm="1">
+        <f t="array" ref="L8">_xlfn.STDEV.P(IF(data[Sesion]=A3,data[% Aciertos]))</f>
+        <v>10.439560439560449</v>
+      </c>
+      <c r="M8">
+        <f>AVERAGEIF(data[Sesion],A3,data[% Mal])</f>
+        <v>18.131868131868096</v>
+      </c>
+      <c r="N8" cm="1">
+        <f t="array" ref="N8">_xlfn.STDEV.P(IF(data[Sesion]=A3,data[% Mal]))</f>
+        <v>10.439560439560402</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="C9">
+        <f>AVERAGEIF(data[Sesion],A4,data[Tiempo duracion])</f>
+        <v>2271.3278518518518</v>
+      </c>
+      <c r="D9" cm="1">
+        <f t="array" ref="D9">_xlfn.STDEV.P(IF(data[Sesion]=A4,data[Tiempo duracion]))</f>
+        <v>881.82186350690699</v>
+      </c>
+      <c r="E9">
+        <f>AVERAGEIF(data[Sesion],A4,data[Num niveles])</f>
+        <v>3.5555555555555554</v>
+      </c>
+      <c r="F9" cm="1">
+        <f t="array" ref="F9">_xlfn.STDEV.P(IF(data[Sesion]=A4,data[Num niveles]))</f>
+        <v>1.1653431646335017</v>
+      </c>
+      <c r="G9">
+        <f>AVERAGEIF(data[Sesion],A4,data[Num intentos])</f>
+        <v>11.481481481481481</v>
+      </c>
+      <c r="H9" cm="1">
+        <f t="array" ref="H9">_xlfn.STDEV.P(IF(data[Sesion]=A4,data[Num intentos]))</f>
+        <v>5.3704980827726274</v>
+      </c>
+      <c r="I9">
+        <f>AVERAGEIF(data[Sesion],A4,data[Completados])</f>
+        <v>1.7037037037037037</v>
+      </c>
+      <c r="J9" cm="1">
+        <f t="array" ref="J9">_xlfn.STDEV.P(IF(data[Sesion]=A4,data[Completados]))</f>
+        <v>1.4609691054308163</v>
+      </c>
+      <c r="K9">
+        <f>AVERAGEIF(data[Sesion],A4,data[% Aciertos])</f>
+        <v>84.678266813816748</v>
+      </c>
+      <c r="L9" cm="1">
+        <f t="array" ref="L9">_xlfn.STDEV.P(IF(data[Sesion]=A4,data[% Aciertos]))</f>
+        <v>9.7359064227108103</v>
+      </c>
+      <c r="M9">
+        <f>AVERAGEIF(data[Sesion],A4,data[% Mal])</f>
+        <v>15.321733186183183</v>
+      </c>
+      <c r="N9" cm="1">
+        <f t="array" ref="N9">_xlfn.STDEV.P(IF(data[Sesion]=A4,data[% Mal]))</f>
+        <v>9.7359064227106646</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="H11" t="s">
+        <v>3</v>
+      </c>
+      <c r="I11" t="s">
+        <v>209</v>
+      </c>
+      <c r="J11" t="s">
+        <v>210</v>
+      </c>
+      <c r="K11" t="s">
+        <v>211</v>
+      </c>
+      <c r="L11" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="H12">
+        <f>SUMIF(data[Sesion],A2,data[Num intentos])</f>
+        <v>343</v>
+      </c>
+      <c r="I12">
+        <f>SUMIF(data[Sesion],A2,data[Completados])</f>
+        <v>35</v>
+      </c>
+      <c r="J12">
+        <f>100*I12/H12</f>
+        <v>10.204081632653061</v>
+      </c>
+      <c r="K12">
+        <f>H12-I12</f>
+        <v>308</v>
+      </c>
+      <c r="L12">
+        <f>100*K12/H12</f>
+        <v>89.795918367346943</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="H13">
+        <f>SUMIF(data[Sesion],A3,data[Num intentos])</f>
+        <v>14</v>
+      </c>
+      <c r="I13">
+        <f>SUMIF(data[Sesion],A3,data[Completados])</f>
+        <v>2</v>
+      </c>
+      <c r="J13">
+        <f t="shared" ref="J13:J14" si="0">100*I13/H13</f>
+        <v>14.285714285714286</v>
+      </c>
+      <c r="K13">
+        <f t="shared" ref="K13:K14" si="1">H13-I13</f>
+        <v>12</v>
+      </c>
+      <c r="L13">
+        <f t="shared" ref="L13:L14" si="2">100*K13/H13</f>
+        <v>85.714285714285708</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="H14">
+        <f>SUMIF(data[Sesion],A4,data[Num intentos])</f>
+        <v>310</v>
+      </c>
+      <c r="I14">
+        <f>SUMIF(data[Sesion],A4,data[Completados])</f>
+        <v>46</v>
+      </c>
+      <c r="J14">
+        <f t="shared" si="0"/>
+        <v>14.838709677419354</v>
+      </c>
+      <c r="K14">
+        <f t="shared" si="1"/>
+        <v>264</v>
+      </c>
+      <c r="L14">
+        <f t="shared" si="2"/>
+        <v>85.161290322580641</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0EE1E7D-EAFC-4A2F-AF1A-E8C144B15E47}">
   <dimension ref="A1:AB14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -7363,108 +8070,108 @@
         <v>43</v>
       </c>
       <c r="C2">
-        <f>AVERAGEIF(data[Sesion],A2,data[Pasos planificados])</f>
-        <v>14.13953488372093</v>
+        <f>AVERAGEIFS(data[Pasos planificados],data[Sesion],A2,data[Pasos planificados],"&gt;0")</f>
+        <v>17.882352941176471</v>
       </c>
       <c r="D2" cm="1">
-        <f t="array" ref="D2">_xlfn.STDEV.P(IF(data[Sesion]=A2,data[Pasos planificados]))</f>
-        <v>12.474311082900297</v>
+        <f t="array" ref="D2">_xlfn.STDEV.P(IF((data[Sesion]=A2)*(data[Pasos planificados]&lt;&gt;0),data[Pasos planificados]))</f>
+        <v>11.395986666836999</v>
       </c>
       <c r="E2">
-        <f>AVERAGEIF(data[Sesion],A2,data[Pasos ejecutados])</f>
-        <v>11.651162790697674</v>
+        <f>AVERAGEIFS(data[Pasos ejecutados],data[Sesion],A2,data[Pasos planificados],"&gt;0")</f>
+        <v>14.735294117647058</v>
       </c>
       <c r="F2" cm="1">
-        <f t="array" ref="F2">_xlfn.STDEV.P(IF(data[Sesion]=A2,data[Pasos ejecutados]))</f>
-        <v>10.573955984377166</v>
+        <f t="array" ref="F2">_xlfn.STDEV.P(IF((data[Sesion]=A2)*(data[Pasos planificados]&lt;&gt;0),data[Pasos ejecutados]))</f>
+        <v>9.7958839601413015</v>
       </c>
       <c r="G2">
-        <f>AVERAGEIF(data[Sesion],A2,data[Errores ejecucion])</f>
-        <v>2.4883720930232558</v>
+        <f>AVERAGEIFS(data[Errores ejecucion],data[Sesion],A2,data[Pasos planificados],"&gt;0")</f>
+        <v>3.1470588235294117</v>
       </c>
       <c r="H2" cm="1">
-        <f t="array" ref="H2">_xlfn.STDEV.P(IF(data[Sesion]=A2,data[Errores ejecucion]))</f>
-        <v>2.9044640303173401</v>
+        <f t="array" ref="H2">_xlfn.STDEV.P(IF((data[Sesion]=A2)*(data[Pasos planificados]&lt;&gt;0),data[Errores ejecucion]))</f>
+        <v>2.9318971266478084</v>
       </c>
       <c r="I2">
-        <f>AVERAGEIF(data[Sesion],A2,data[Num dormir planificado])</f>
-        <v>6.7209302325581399</v>
+        <f>AVERAGEIFS(data[Num dormir planificado],data[Sesion],A2,data[Pasos planificados],"&gt;0")</f>
+        <v>8.5</v>
       </c>
       <c r="J2" cm="1">
-        <f t="array" ref="J2">_xlfn.STDEV.P(IF(data[Sesion]=A2,data[Num dormir planificado]))</f>
-        <v>5.7032246341601036</v>
+        <f t="array" ref="J2">_xlfn.STDEV.P(IF((data[Sesion]=A2)*(data[Pasos planificados]&lt;&gt;0),data[Num dormir planificado]))</f>
+        <v>5.1004613401488443</v>
       </c>
       <c r="K2">
-        <f>AVERAGEIF(data[Sesion],A2,data[Correctos dormir])</f>
-        <v>6.441860465116279</v>
+        <f>AVERAGEIFS(data[Correctos dormir],data[Sesion],A2,data[Pasos planificados],"&gt;0")</f>
+        <v>8.1470588235294112</v>
       </c>
       <c r="L2" cm="1">
-        <f t="array" ref="L2">_xlfn.STDEV.P(IF(data[Sesion]=A2,data[Correctos dormir]))</f>
-        <v>5.5543920420937338</v>
+        <f t="array" ref="L2">_xlfn.STDEV.P(IF((data[Sesion]=A2)*(data[Pasos planificados]&lt;&gt;0),data[Correctos dormir]))</f>
+        <v>5.0125275586226516</v>
       </c>
       <c r="M2">
-        <f>AVERAGEIF(data[Sesion],A2,data[Errores dormir])</f>
-        <v>0.27906976744186046</v>
+        <f>AVERAGEIFS(data[Errores dormir],data[Sesion],A2,data[Pasos planificados],"&gt;0")</f>
+        <v>0.35294117647058826</v>
       </c>
       <c r="N2" cm="1">
-        <f t="array" ref="N2">_xlfn.STDEV.P(IF(data[Sesion]=A2,data[Errores dormir]))</f>
-        <v>0.54241412975305114</v>
+        <f t="array" ref="N2">_xlfn.STDEV.P(IF((data[Sesion]=A2)*(data[Pasos planificados]&lt;&gt;0),data[Errores dormir]))</f>
+        <v>0.58823529411764708</v>
       </c>
       <c r="O2">
-        <f>AVERAGEIF(data[Sesion],A2,data[Num ubicacion planificado])</f>
-        <v>7.4186046511627906</v>
+        <f>AVERAGEIFS(data[Num ubicacion planificado],data[Sesion],A2,data[Pasos planificados],"&gt;0")</f>
+        <v>9.382352941176471</v>
       </c>
       <c r="P2" cm="1">
-        <f t="array" ref="P2">_xlfn.STDEV.P(IF(data[Sesion]=A2,data[Num ubicacion planificado]))</f>
-        <v>7.4466554319888516</v>
+        <f t="array" ref="P2">_xlfn.STDEV.P(IF((data[Sesion]=A2)*(data[Pasos planificados]&lt;&gt;0),data[Num ubicacion planificado]))</f>
+        <v>7.1907403933700937</v>
       </c>
       <c r="Q2">
-        <f>AVERAGEIF(data[Sesion],A2,data[Correctos ubicacion])</f>
-        <v>5.2093023255813957</v>
+        <f>AVERAGEIFS(data[Correctos ubicacion],data[Sesion],A2,data[Pasos planificados],"&gt;0")</f>
+        <v>6.5882352941176467</v>
       </c>
       <c r="R2" cm="1">
-        <f t="array" ref="R2">_xlfn.STDEV.P(IF(data[Sesion]=A2,data[Correctos ubicacion]))</f>
-        <v>5.5888516086892199</v>
+        <f t="array" ref="R2">_xlfn.STDEV.P(IF((data[Sesion]=A2)*(data[Pasos planificados]&lt;&gt;0),data[Correctos ubicacion]))</f>
+        <v>5.5153136919949768</v>
       </c>
       <c r="S2">
-        <f>AVERAGEIF(data[Sesion],A2,data[Errores ubicacion])</f>
-        <v>2.2093023255813953</v>
+        <f>AVERAGEIFS(data[Errores ubicacion],data[Sesion],A2,data[Pasos planificados],"&gt;0")</f>
+        <v>2.7941176470588234</v>
       </c>
       <c r="T2" cm="1">
-        <f t="array" ref="T2">_xlfn.STDEV.P(IF(data[Sesion]=A2,data[Errores ubicacion]))</f>
-        <v>2.791666498497233</v>
+        <f t="array" ref="T2">_xlfn.STDEV.P(IF((data[Sesion]=A2)*(data[Pasos planificados]&lt;&gt;0),data[Errores ubicacion]))</f>
+        <v>2.8674585156720829</v>
       </c>
       <c r="U2">
-        <f>AVERAGEIF(data[Sesion],A2,data[Paradas posibles])</f>
-        <v>16.325581395348838</v>
+        <f>AVERAGEIFS(data[Paradas posibles],data[Sesion],A2,data[Pasos planificados],"&gt;0")</f>
+        <v>18.911764705882351</v>
       </c>
       <c r="V2" cm="1">
-        <f t="array" ref="V2">_xlfn.STDEV.P(IF(data[Sesion]=A2,data[Paradas posibles]))</f>
-        <v>8.8678172512470237</v>
+        <f t="array" ref="V2">_xlfn.STDEV.P(IF((data[Sesion]=A2)*(data[Pasos planificados]&lt;&gt;0),data[Paradas posibles]))</f>
+        <v>7.8903054703366786</v>
       </c>
       <c r="W2">
-        <f>AVERAGEIF(data[Sesion],A2,data[Paradas realizadas])</f>
-        <v>11.13953488372093</v>
+        <f>AVERAGEIFS(data[Paradas realizadas],data[Sesion],A2,data[Pasos planificados],"&gt;0")</f>
+        <v>13.205882352941176</v>
       </c>
       <c r="X2" cm="1">
-        <f t="array" ref="X2">_xlfn.STDEV.P(IF(data[Sesion]=A2,data[Paradas realizadas]))</f>
-        <v>7.2258624506532003</v>
+        <f t="array" ref="X2">_xlfn.STDEV.P(IF((data[Sesion]=A2)*(data[Pasos planificados]&lt;&gt;0),data[Paradas realizadas]))</f>
+        <v>6.6499863412717133</v>
       </c>
       <c r="Y2">
-        <f>AVERAGEIF(data[Sesion],A2,data[Errores parada por tiempo excedido])</f>
-        <v>0.81395348837209303</v>
+        <f>AVERAGEIFS(data[Errores parada por tiempo excedido],data[Sesion],A2,data[Pasos planificados],"&gt;0")</f>
+        <v>0.76470588235294112</v>
       </c>
       <c r="Z2" cm="1">
-        <f t="array" ref="Z2">_xlfn.STDEV.P(IF(data[Sesion]=A2,data[Errores parada por tiempo excedido]))</f>
-        <v>1.1259272964567633</v>
+        <f t="array" ref="Z2">_xlfn.STDEV.P(IF((data[Sesion]=A2)*(data[Pasos planificados]&lt;&gt;0),data[Errores parada por tiempo excedido]))</f>
+        <v>1.0588235294117647</v>
       </c>
       <c r="AA2">
-        <f>AVERAGEIF(data[Sesion],A2,data[Num errores por tiempo excedido])</f>
-        <v>0.93023255813953487</v>
+        <f>AVERAGEIFS(data[Num errores por tiempo excedido],data[Sesion],A2,data[Pasos planificados],"&gt;0")</f>
+        <v>0.91176470588235292</v>
       </c>
       <c r="AB2" cm="1">
-        <f t="array" ref="AB2">_xlfn.STDEV.P(IF(data[Sesion]=A2,data[Num errores por tiempo excedido]))</f>
-        <v>1.2830803929426717</v>
+        <f t="array" ref="AB2">_xlfn.STDEV.P(IF((data[Sesion]=A2)*(data[Pasos planificados]&lt;&gt;0),data[Num errores por tiempo excedido]))</f>
+        <v>1.268803212360176</v>
       </c>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.3">
@@ -7476,108 +8183,108 @@
         <v>4</v>
       </c>
       <c r="C3">
-        <f>AVERAGEIF(data[Sesion],A3,data[Pasos planificados])</f>
-        <v>5</v>
+        <f>AVERAGEIFS(data[Pasos planificados],data[Sesion],A3,data[Pasos planificados],"&gt;0")</f>
+        <v>10</v>
       </c>
       <c r="D3" cm="1">
-        <f t="array" ref="D3">_xlfn.STDEV.P(IF(data[Sesion]=A3,data[Pasos planificados]))</f>
-        <v>5.4313902456001077</v>
+        <f t="array" ref="D3">_xlfn.STDEV.P(IF((data[Sesion]=A3)*(data[Pasos planificados]&lt;&gt;0),data[Pasos planificados]))</f>
+        <v>3</v>
       </c>
       <c r="E3">
-        <f>AVERAGEIF(data[Sesion],A3,data[Pasos ejecutados])</f>
-        <v>4.25</v>
+        <f>AVERAGEIFS(data[Pasos ejecutados],data[Sesion],A3,data[Pasos planificados],"&gt;0")</f>
+        <v>8.5</v>
       </c>
       <c r="F3" cm="1">
-        <f t="array" ref="F3">_xlfn.STDEV.P(IF(data[Sesion]=A3,data[Pasos ejecutados]))</f>
-        <v>4.9180788932265003</v>
+        <f t="array" ref="F3">_xlfn.STDEV.P(IF((data[Sesion]=A3)*(data[Pasos planificados]&lt;&gt;0),data[Pasos ejecutados]))</f>
+        <v>3.5</v>
       </c>
       <c r="G3">
-        <f>AVERAGEIF(data[Sesion],A3,data[Errores ejecucion])</f>
-        <v>0.75</v>
+        <f>AVERAGEIFS(data[Errores ejecucion],data[Sesion],A3,data[Pasos planificados],"&gt;0")</f>
+        <v>1.5</v>
       </c>
       <c r="H3" cm="1">
-        <f t="array" ref="H3">_xlfn.STDEV.P(IF(data[Sesion]=A3,data[Errores ejecucion]))</f>
-        <v>0.82915619758884995</v>
+        <f t="array" ref="H3">_xlfn.STDEV.P(IF((data[Sesion]=A3)*(data[Pasos planificados]&lt;&gt;0),data[Errores ejecucion]))</f>
+        <v>0.5</v>
       </c>
       <c r="I3">
-        <f>AVERAGEIF(data[Sesion],A3,data[Num dormir planificado])</f>
-        <v>3.25</v>
+        <f>AVERAGEIFS(data[Num dormir planificado],data[Sesion],A3,data[Pasos planificados],"&gt;0")</f>
+        <v>6.5</v>
       </c>
       <c r="J3" cm="1">
-        <f t="array" ref="J3">_xlfn.STDEV.P(IF(data[Sesion]=A3,data[Num dormir planificado]))</f>
-        <v>3.4186985827943359</v>
+        <f t="array" ref="J3">_xlfn.STDEV.P(IF((data[Sesion]=A3)*(data[Pasos planificados]&lt;&gt;0),data[Num dormir planificado]))</f>
+        <v>1.5</v>
       </c>
       <c r="K3">
-        <f>AVERAGEIF(data[Sesion],A3,data[Correctos dormir])</f>
-        <v>3</v>
+        <f>AVERAGEIFS(data[Correctos dormir],data[Sesion],A3,data[Pasos planificados],"&gt;0")</f>
+        <v>6</v>
       </c>
       <c r="L3" cm="1">
-        <f t="array" ref="L3">_xlfn.STDEV.P(IF(data[Sesion]=A3,data[Correctos dormir]))</f>
-        <v>3.3166247903553998</v>
+        <f t="array" ref="L3">_xlfn.STDEV.P(IF((data[Sesion]=A3)*(data[Pasos planificados]&lt;&gt;0),data[Correctos dormir]))</f>
+        <v>2</v>
       </c>
       <c r="M3">
-        <f>AVERAGEIF(data[Sesion],A3,data[Errores dormir])</f>
-        <v>0.25</v>
+        <f>AVERAGEIFS(data[Errores dormir],data[Sesion],A3,data[Pasos planificados],"&gt;0")</f>
+        <v>0.5</v>
       </c>
       <c r="N3" cm="1">
-        <f t="array" ref="N3">_xlfn.STDEV.P(IF(data[Sesion]=A3,data[Errores dormir]))</f>
-        <v>0.4330127018922193</v>
+        <f t="array" ref="N3">_xlfn.STDEV.P(IF((data[Sesion]=A3)*(data[Pasos planificados]&lt;&gt;0),data[Errores dormir]))</f>
+        <v>0.5</v>
       </c>
       <c r="O3">
-        <f>AVERAGEIF(data[Sesion],A3,data[Num ubicacion planificado])</f>
-        <v>1.75</v>
+        <f>AVERAGEIFS(data[Num ubicacion planificado],data[Sesion],A3,data[Pasos planificados],"&gt;0")</f>
+        <v>3.5</v>
       </c>
       <c r="P3" cm="1">
-        <f t="array" ref="P3">_xlfn.STDEV.P(IF(data[Sesion]=A3,data[Num ubicacion planificado]))</f>
-        <v>2.0463381929681126</v>
+        <f t="array" ref="P3">_xlfn.STDEV.P(IF((data[Sesion]=A3)*(data[Pasos planificados]&lt;&gt;0),data[Num ubicacion planificado]))</f>
+        <v>1.5</v>
       </c>
       <c r="Q3">
-        <f>AVERAGEIF(data[Sesion],A3,data[Correctos ubicacion])</f>
-        <v>1.25</v>
+        <f>AVERAGEIFS(data[Correctos ubicacion],data[Sesion],A3,data[Pasos planificados],"&gt;0")</f>
+        <v>2.5</v>
       </c>
       <c r="R3" cm="1">
-        <f t="array" ref="R3">_xlfn.STDEV.P(IF(data[Sesion]=A3,data[Correctos ubicacion]))</f>
-        <v>1.6393596310755001</v>
+        <f t="array" ref="R3">_xlfn.STDEV.P(IF((data[Sesion]=A3)*(data[Pasos planificados]&lt;&gt;0),data[Correctos ubicacion]))</f>
+        <v>1.5</v>
       </c>
       <c r="S3">
-        <f>AVERAGEIF(data[Sesion],A3,data[Errores ubicacion])</f>
+        <f>AVERAGEIFS(data[Errores ubicacion],data[Sesion],A3,data[Pasos planificados],"&gt;0")</f>
+        <v>1</v>
+      </c>
+      <c r="T3" cm="1">
+        <f t="array" ref="T3">_xlfn.STDEV.P(IF((data[Sesion]=A3)*(data[Pasos planificados]&lt;&gt;0),data[Errores ubicacion]))</f>
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <f>AVERAGEIFS(data[Paradas posibles],data[Sesion],A3,data[Pasos planificados],"&gt;0")</f>
+        <v>12</v>
+      </c>
+      <c r="V3" cm="1">
+        <f t="array" ref="V3">_xlfn.STDEV.P(IF((data[Sesion]=A3)*(data[Pasos planificados]&lt;&gt;0),data[Paradas posibles]))</f>
+        <v>0</v>
+      </c>
+      <c r="W3">
+        <f>AVERAGEIFS(data[Paradas realizadas],data[Sesion],A3,data[Pasos planificados],"&gt;0")</f>
+        <v>8</v>
+      </c>
+      <c r="X3" cm="1">
+        <f t="array" ref="X3">_xlfn.STDEV.P(IF((data[Sesion]=A3)*(data[Pasos planificados]&lt;&gt;0),data[Paradas realizadas]))</f>
+        <v>1</v>
+      </c>
+      <c r="Y3">
+        <f>AVERAGEIFS(data[Errores parada por tiempo excedido],data[Sesion],A3,data[Pasos planificados],"&gt;0")</f>
         <v>0.5</v>
       </c>
-      <c r="T3" cm="1">
-        <f t="array" ref="T3">_xlfn.STDEV.P(IF(data[Sesion]=A3,data[Errores ubicacion]))</f>
+      <c r="Z3" cm="1">
+        <f t="array" ref="Z3">_xlfn.STDEV.P(IF((data[Sesion]=A3)*(data[Pasos planificados]&lt;&gt;0),data[Errores parada por tiempo excedido]))</f>
         <v>0.5</v>
       </c>
-      <c r="U3">
-        <f>AVERAGEIF(data[Sesion],A3,data[Paradas posibles])</f>
-        <v>6.25</v>
-      </c>
-      <c r="V3" cm="1">
-        <f t="array" ref="V3">_xlfn.STDEV.P(IF(data[Sesion]=A3,data[Paradas posibles]))</f>
-        <v>5.7608593109014565</v>
-      </c>
-      <c r="W3">
-        <f>AVERAGEIF(data[Sesion],A3,data[Paradas realizadas])</f>
-        <v>4</v>
-      </c>
-      <c r="X3" cm="1">
-        <f t="array" ref="X3">_xlfn.STDEV.P(IF(data[Sesion]=A3,data[Paradas realizadas]))</f>
-        <v>4.0620192023179804</v>
-      </c>
-      <c r="Y3">
-        <f>AVERAGEIF(data[Sesion],A3,data[Errores parada por tiempo excedido])</f>
-        <v>0.25</v>
-      </c>
-      <c r="Z3" cm="1">
-        <f t="array" ref="Z3">_xlfn.STDEV.P(IF(data[Sesion]=A3,data[Errores parada por tiempo excedido]))</f>
-        <v>0.4330127018922193</v>
-      </c>
       <c r="AA3">
-        <f>AVERAGEIF(data[Sesion],A3,data[Num errores por tiempo excedido])</f>
-        <v>0.25</v>
+        <f>AVERAGEIFS(data[Num errores por tiempo excedido],data[Sesion],A3,data[Pasos planificados],"&gt;0")</f>
+        <v>0.5</v>
       </c>
       <c r="AB3" cm="1">
-        <f t="array" ref="AB3">_xlfn.STDEV.P(IF(data[Sesion]=A3,data[Num errores por tiempo excedido]))</f>
-        <v>0.4330127018922193</v>
+        <f t="array" ref="AB3">_xlfn.STDEV.P(IF((data[Sesion]=A3)*(data[Pasos planificados]&lt;&gt;0),data[Num errores por tiempo excedido]))</f>
+        <v>0.5</v>
       </c>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.3">
@@ -7589,107 +8296,107 @@
         <v>27</v>
       </c>
       <c r="C4">
-        <f>AVERAGEIF(data[Sesion],A4,data[Pasos planificados])</f>
+        <f>AVERAGEIFS(data[Pasos planificados],data[Sesion],A4,data[Pasos planificados],"&gt;0")</f>
         <v>31.777777777777779</v>
       </c>
       <c r="D4" cm="1">
-        <f t="array" ref="D4">_xlfn.STDEV.P(IF(data[Sesion]=A4,data[Pasos planificados]))</f>
+        <f t="array" ref="D4">_xlfn.STDEV.P(IF((data[Sesion]=A4)*(data[Pasos planificados]&lt;&gt;0),data[Pasos planificados]))</f>
         <v>11.901862080685287</v>
       </c>
       <c r="E4">
-        <f>AVERAGEIF(data[Sesion],A4,data[Pasos ejecutados])</f>
+        <f>AVERAGEIFS(data[Pasos ejecutados],data[Sesion],A4,data[Pasos planificados],"&gt;0")</f>
         <v>26.703703703703702</v>
       </c>
       <c r="F4" cm="1">
-        <f t="array" ref="F4">_xlfn.STDEV.P(IF(data[Sesion]=A4,data[Pasos ejecutados]))</f>
+        <f t="array" ref="F4">_xlfn.STDEV.P(IF((data[Sesion]=A4)*(data[Pasos planificados]&lt;&gt;0),data[Pasos ejecutados]))</f>
         <v>10.10249259603536</v>
       </c>
       <c r="G4">
-        <f>AVERAGEIF(data[Sesion],A4,data[Errores ejecucion])</f>
+        <f>AVERAGEIFS(data[Errores ejecucion],data[Sesion],A4,data[Pasos planificados],"&gt;0")</f>
         <v>5.0740740740740744</v>
       </c>
       <c r="H4" cm="1">
-        <f t="array" ref="H4">_xlfn.STDEV.P(IF(data[Sesion]=A4,data[Errores ejecucion]))</f>
+        <f t="array" ref="H4">_xlfn.STDEV.P(IF((data[Sesion]=A4)*(data[Pasos planificados]&lt;&gt;0),data[Errores ejecucion]))</f>
         <v>3.7508115262732336</v>
       </c>
       <c r="I4">
-        <f>AVERAGEIF(data[Sesion],A4,data[Num dormir planificado])</f>
+        <f>AVERAGEIFS(data[Num dormir planificado],data[Sesion],A4,data[Pasos planificados],"&gt;0")</f>
         <v>15.777777777777779</v>
       </c>
       <c r="J4" cm="1">
-        <f t="array" ref="J4">_xlfn.STDEV.P(IF(data[Sesion]=A4,data[Num dormir planificado]))</f>
+        <f t="array" ref="J4">_xlfn.STDEV.P(IF((data[Sesion]=A4)*(data[Pasos planificados]&lt;&gt;0),data[Num dormir planificado]))</f>
         <v>5.3147825524895103</v>
       </c>
       <c r="K4">
-        <f>AVERAGEIF(data[Sesion],A4,data[Correctos dormir])</f>
+        <f>AVERAGEIFS(data[Correctos dormir],data[Sesion],A4,data[Pasos planificados],"&gt;0")</f>
         <v>14.851851851851851</v>
       </c>
       <c r="L4" cm="1">
-        <f t="array" ref="L4">_xlfn.STDEV.P(IF(data[Sesion]=A4,data[Correctos dormir]))</f>
+        <f t="array" ref="L4">_xlfn.STDEV.P(IF((data[Sesion]=A4)*(data[Pasos planificados]&lt;&gt;0),data[Correctos dormir]))</f>
         <v>5.2543012623782719</v>
       </c>
       <c r="M4">
-        <f>AVERAGEIF(data[Sesion],A4,data[Errores dormir])</f>
+        <f>AVERAGEIFS(data[Errores dormir],data[Sesion],A4,data[Pasos planificados],"&gt;0")</f>
         <v>0.92592592592592593</v>
       </c>
       <c r="N4" cm="1">
-        <f t="array" ref="N4">_xlfn.STDEV.P(IF(data[Sesion]=A4,data[Errores dormir]))</f>
+        <f t="array" ref="N4">_xlfn.STDEV.P(IF((data[Sesion]=A4)*(data[Pasos planificados]&lt;&gt;0),data[Errores dormir]))</f>
         <v>2.0534690778709797</v>
       </c>
       <c r="O4">
-        <f>AVERAGEIF(data[Sesion],A4,data[Num ubicacion planificado])</f>
+        <f>AVERAGEIFS(data[Num ubicacion planificado],data[Sesion],A4,data[Pasos planificados],"&gt;0")</f>
         <v>16</v>
       </c>
       <c r="P4" cm="1">
-        <f t="array" ref="P4">_xlfn.STDEV.P(IF(data[Sesion]=A4,data[Num ubicacion planificado]))</f>
+        <f t="array" ref="P4">_xlfn.STDEV.P(IF((data[Sesion]=A4)*(data[Pasos planificados]&lt;&gt;0),data[Num ubicacion planificado]))</f>
         <v>8.1649658092772608</v>
       </c>
       <c r="Q4">
-        <f>AVERAGEIF(data[Sesion],A4,data[Correctos ubicacion])</f>
+        <f>AVERAGEIFS(data[Correctos ubicacion],data[Sesion],A4,data[Pasos planificados],"&gt;0")</f>
         <v>11.851851851851851</v>
       </c>
       <c r="R4" cm="1">
-        <f t="array" ref="R4">_xlfn.STDEV.P(IF(data[Sesion]=A4,data[Correctos ubicacion]))</f>
+        <f t="array" ref="R4">_xlfn.STDEV.P(IF((data[Sesion]=A4)*(data[Pasos planificados]&lt;&gt;0),data[Correctos ubicacion]))</f>
         <v>6.6092174899835134</v>
       </c>
       <c r="S4">
-        <f>AVERAGEIF(data[Sesion],A4,data[Errores ubicacion])</f>
+        <f>AVERAGEIFS(data[Errores ubicacion],data[Sesion],A4,data[Pasos planificados],"&gt;0")</f>
         <v>4.1481481481481479</v>
       </c>
       <c r="T4" cm="1">
-        <f t="array" ref="T4">_xlfn.STDEV.P(IF(data[Sesion]=A4,data[Errores ubicacion]))</f>
+        <f t="array" ref="T4">_xlfn.STDEV.P(IF((data[Sesion]=A4)*(data[Pasos planificados]&lt;&gt;0),data[Errores ubicacion]))</f>
         <v>2.8376268606485855</v>
       </c>
       <c r="U4">
-        <f>AVERAGEIF(data[Sesion],A4,data[Paradas posibles])</f>
+        <f>AVERAGEIFS(data[Paradas posibles],data[Sesion],A4,data[Pasos planificados],"&gt;0")</f>
         <v>32.111111111111114</v>
       </c>
       <c r="V4" cm="1">
-        <f t="array" ref="V4">_xlfn.STDEV.P(IF(data[Sesion]=A4,data[Paradas posibles]))</f>
+        <f t="array" ref="V4">_xlfn.STDEV.P(IF((data[Sesion]=A4)*(data[Pasos planificados]&lt;&gt;0),data[Paradas posibles]))</f>
         <v>11.951548275133206</v>
       </c>
       <c r="W4">
-        <f>AVERAGEIF(data[Sesion],A4,data[Paradas realizadas])</f>
+        <f>AVERAGEIFS(data[Paradas realizadas],data[Sesion],A4,data[Pasos planificados],"&gt;0")</f>
         <v>23.777777777777779</v>
       </c>
       <c r="X4" cm="1">
-        <f t="array" ref="X4">_xlfn.STDEV.P(IF(data[Sesion]=A4,data[Paradas realizadas]))</f>
+        <f t="array" ref="X4">_xlfn.STDEV.P(IF((data[Sesion]=A4)*(data[Pasos planificados]&lt;&gt;0),data[Paradas realizadas]))</f>
         <v>9.1016210738988423</v>
       </c>
       <c r="Y4">
-        <f>AVERAGEIF(data[Sesion],A4,data[Errores parada por tiempo excedido])</f>
+        <f>AVERAGEIFS(data[Errores parada por tiempo excedido],data[Sesion],A4,data[Pasos planificados],"&gt;0")</f>
         <v>1.1851851851851851</v>
       </c>
       <c r="Z4" cm="1">
-        <f t="array" ref="Z4">_xlfn.STDEV.P(IF(data[Sesion]=A4,data[Errores parada por tiempo excedido]))</f>
+        <f t="array" ref="Z4">_xlfn.STDEV.P(IF((data[Sesion]=A4)*(data[Pasos planificados]&lt;&gt;0),data[Errores parada por tiempo excedido]))</f>
         <v>1.4665918424609874</v>
       </c>
       <c r="AA4">
-        <f>AVERAGEIF(data[Sesion],A4,data[Num errores por tiempo excedido])</f>
+        <f>AVERAGEIFS(data[Num errores por tiempo excedido],data[Sesion],A4,data[Pasos planificados],"&gt;0")</f>
         <v>1.4814814814814814</v>
       </c>
       <c r="AB4" cm="1">
-        <f t="array" ref="AB4">_xlfn.STDEV.P(IF(data[Sesion]=A4,data[Num errores por tiempo excedido]))</f>
+        <f t="array" ref="AB4">_xlfn.STDEV.P(IF((data[Sesion]=A4)*(data[Pasos planificados]&lt;&gt;0),data[Num errores por tiempo excedido]))</f>
         <v>1.8129241852622839</v>
       </c>
     </row>
@@ -7733,151 +8440,151 @@
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.3">
       <c r="C7">
-        <f>AVERAGEIF(data[Sesion],A2,data[Tiempo duracion])</f>
-        <v>1391.2371627906978</v>
+        <f>AVERAGEIFS(data[Tiempo duracion],data[Sesion],A2,data[Pasos planificados],"&gt;0")</f>
+        <v>1499.0487352941179</v>
       </c>
       <c r="D7" cm="1">
-        <f t="array" ref="D7">_xlfn.STDEV.P(IF(data[Sesion]=A2,data[Tiempo duracion]))</f>
-        <v>752.30981030420571</v>
+        <f t="array" ref="D7">_xlfn.STDEV.P(IF((data[Sesion]=A2)*(data[Pasos planificados]&lt;&gt;0),data[Tiempo duracion]))</f>
+        <v>765.3270031362332</v>
       </c>
       <c r="E7">
-        <f>AVERAGEIF(data[Sesion],A2,data[Num niveles])</f>
-        <v>2.5116279069767442</v>
+        <f>AVERAGEIFS(data[Num niveles],data[Sesion],A2,data[Pasos planificados],"&gt;0")</f>
+        <v>2.6176470588235294</v>
       </c>
       <c r="F7" cm="1">
-        <f t="array" ref="F7">_xlfn.STDEV.P(IF(data[Sesion]=A2,data[Num niveles]))</f>
-        <v>1.2270610193742251</v>
+        <f t="array" ref="F7">_xlfn.STDEV.P(IF((data[Sesion]=A2)*(data[Pasos planificados]&lt;&gt;0),data[Num niveles]))</f>
+        <v>1.2605952348080494</v>
       </c>
       <c r="G7">
-        <f>AVERAGEIF(data[Sesion],A2,data[Num intentos])</f>
-        <v>7.9767441860465116</v>
+        <f>AVERAGEIFS(data[Num intentos],data[Sesion],A2,data[Pasos planificados],"&gt;0")</f>
+        <v>8.5</v>
       </c>
       <c r="H7" cm="1">
-        <f t="array" ref="H7">_xlfn.STDEV.P(IF(data[Sesion]=A2,data[Num intentos]))</f>
-        <v>3.2456652458390702</v>
+        <f t="array" ref="H7">_xlfn.STDEV.P(IF((data[Sesion]=A2)*(data[Pasos planificados]&lt;&gt;0),data[Num intentos]))</f>
+        <v>2.9129528176142947</v>
       </c>
       <c r="I7">
-        <f>AVERAGEIF(data[Sesion],A2,data[Completados])</f>
-        <v>0.81395348837209303</v>
+        <f>AVERAGEIFS(data[Completados],data[Sesion],A2,data[Pasos planificados],"&gt;0")</f>
+        <v>1.0294117647058822</v>
       </c>
       <c r="J7" cm="1">
-        <f t="array" ref="J7">_xlfn.STDEV.P(IF(data[Sesion]=A2,data[Completados]))</f>
-        <v>1.2985826612384852</v>
+        <f t="array" ref="J7">_xlfn.STDEV.P(IF((data[Sesion]=A2)*(data[Pasos planificados]&lt;&gt;0),data[Completados]))</f>
+        <v>1.3823529411764706</v>
       </c>
       <c r="K7">
-        <f>AVERAGEIF(data[Sesion],A2,data[% Aciertos])</f>
+        <f>AVERAGEIFS(data[% Aciertos],data[Sesion],A2,data[Pasos planificados],"&gt;0")</f>
         <v>81.500533061927996</v>
       </c>
       <c r="L7" cm="1">
-        <f t="array" ref="L7">_xlfn.STDEV.P(IF(data[Sesion]=A2,data[% Aciertos]))</f>
+        <f t="array" ref="L7">_xlfn.STDEV.P(IF((data[Sesion]=A2)*(data[Pasos planificados]&lt;&gt;0),data[% Aciertos]))</f>
         <v>13.661094774056064</v>
       </c>
       <c r="M7">
-        <f>AVERAGEIF(data[Sesion],A2,data[% Mal])</f>
+        <f>AVERAGEIFS(data[% Mal],data[Sesion],A2,data[Pasos planificados],"&gt;0")</f>
         <v>18.499466938071933</v>
       </c>
       <c r="N7" cm="1">
-        <f t="array" ref="N7">_xlfn.STDEV.P(IF(data[Sesion]=A2,data[% Mal]))</f>
+        <f t="array" ref="N7">_xlfn.STDEV.P(IF((data[Sesion]=A2)*(data[Pasos planificados]&lt;&gt;0),data[% Mal]))</f>
         <v>13.661094774056048</v>
       </c>
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.3">
       <c r="C8">
-        <f>AVERAGEIF(data[Sesion],A3,data[Tiempo duracion])</f>
-        <v>548.99350000000004</v>
+        <f>AVERAGEIFS(data[Tiempo duracion],data[Sesion],A3,data[Pasos planificados],"&gt;0")</f>
+        <v>865.94650000000001</v>
       </c>
       <c r="D8" cm="1">
-        <f t="array" ref="D8">_xlfn.STDEV.P(IF(data[Sesion]=A3,data[Tiempo duracion]))</f>
-        <v>399.60607282578923</v>
+        <f t="array" ref="D8">_xlfn.STDEV.P(IF((data[Sesion]=A3)*(data[Pasos planificados]&lt;&gt;0),data[Tiempo duracion]))</f>
+        <v>280.89949999999999</v>
       </c>
       <c r="E8">
-        <f>AVERAGEIF(data[Sesion],A3,data[Num niveles])</f>
-        <v>1.25</v>
+        <f>AVERAGEIFS(data[Num niveles],data[Sesion],A3,data[Pasos planificados],"&gt;0")</f>
+        <v>1.5</v>
       </c>
       <c r="F8" cm="1">
-        <f t="array" ref="F8">_xlfn.STDEV.P(IF(data[Sesion]=A3,data[Num niveles]))</f>
-        <v>0.4330127018922193</v>
+        <f t="array" ref="F8">_xlfn.STDEV.P(IF((data[Sesion]=A3)*(data[Pasos planificados]&lt;&gt;0),data[Num niveles]))</f>
+        <v>0.5</v>
       </c>
       <c r="G8">
-        <f>AVERAGEIF(data[Sesion],A3,data[Num intentos])</f>
-        <v>3.5</v>
+        <f>AVERAGEIFS(data[Num intentos],data[Sesion],A3,data[Pasos planificados],"&gt;0")</f>
+        <v>6</v>
       </c>
       <c r="H8" cm="1">
-        <f t="array" ref="H8">_xlfn.STDEV.P(IF(data[Sesion]=A3,data[Num intentos]))</f>
-        <v>2.8722813232690143</v>
+        <f t="array" ref="H8">_xlfn.STDEV.P(IF((data[Sesion]=A3)*(data[Pasos planificados]&lt;&gt;0),data[Num intentos]))</f>
+        <v>2</v>
       </c>
       <c r="I8">
-        <f>AVERAGEIF(data[Sesion],A3,data[Completados])</f>
-        <v>0.5</v>
+        <f>AVERAGEIFS(data[Completados],data[Sesion],A3,data[Pasos planificados],"&gt;0")</f>
+        <v>1</v>
       </c>
       <c r="J8" cm="1">
-        <f t="array" ref="J8">_xlfn.STDEV.P(IF(data[Sesion]=A3,data[Completados]))</f>
-        <v>0.8660254037844386</v>
+        <f t="array" ref="J8">_xlfn.STDEV.P(IF((data[Sesion]=A3)*(data[Pasos planificados]&lt;&gt;0),data[Completados]))</f>
+        <v>1</v>
       </c>
       <c r="K8">
-        <f>AVERAGEIF(data[Sesion],A3,data[% Aciertos])</f>
+        <f>AVERAGEIFS(data[% Aciertos],data[Sesion],A3,data[Pasos planificados],"&gt;0")</f>
         <v>81.868131868131854</v>
       </c>
       <c r="L8" cm="1">
-        <f t="array" ref="L8">_xlfn.STDEV.P(IF(data[Sesion]=A3,data[% Aciertos]))</f>
+        <f t="array" ref="L8">_xlfn.STDEV.P(IF((data[Sesion]=A3)*(data[Pasos planificados]&lt;&gt;0),data[% Aciertos]))</f>
         <v>10.439560439560449</v>
       </c>
       <c r="M8">
-        <f>AVERAGEIF(data[Sesion],A3,data[% Mal])</f>
+        <f>AVERAGEIFS(data[% Mal],data[Sesion],A3,data[Pasos planificados],"&gt;0")</f>
         <v>18.131868131868096</v>
       </c>
       <c r="N8" cm="1">
-        <f t="array" ref="N8">_xlfn.STDEV.P(IF(data[Sesion]=A3,data[% Mal]))</f>
+        <f t="array" ref="N8">_xlfn.STDEV.P(IF((data[Sesion]=A3)*(data[Pasos planificados]&lt;&gt;0),data[% Mal]))</f>
         <v>10.439560439560402</v>
       </c>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.3">
       <c r="C9">
-        <f>AVERAGEIF(data[Sesion],A4,data[Tiempo duracion])</f>
+        <f>AVERAGEIFS(data[Tiempo duracion],data[Sesion],A4,data[Pasos planificados],"&gt;0")</f>
         <v>2271.3278518518518</v>
       </c>
       <c r="D9" cm="1">
-        <f t="array" ref="D9">_xlfn.STDEV.P(IF(data[Sesion]=A4,data[Tiempo duracion]))</f>
+        <f t="array" ref="D9">_xlfn.STDEV.P(IF((data[Sesion]=A4)*(data[Pasos planificados]&lt;&gt;0),data[Tiempo duracion]))</f>
         <v>881.82186350690699</v>
       </c>
       <c r="E9">
-        <f>AVERAGEIF(data[Sesion],A4,data[Num niveles])</f>
+        <f>AVERAGEIFS(data[Num niveles],data[Sesion],A4,data[Pasos planificados],"&gt;0")</f>
         <v>3.5555555555555554</v>
       </c>
       <c r="F9" cm="1">
-        <f t="array" ref="F9">_xlfn.STDEV.P(IF(data[Sesion]=A4,data[Num niveles]))</f>
+        <f t="array" ref="F9">_xlfn.STDEV.P(IF((data[Sesion]=A4)*(data[Pasos planificados]&lt;&gt;0),data[Num niveles]))</f>
         <v>1.1653431646335017</v>
       </c>
       <c r="G9">
-        <f>AVERAGEIF(data[Sesion],A4,data[Num intentos])</f>
+        <f>AVERAGEIFS(data[Num intentos],data[Sesion],A4,data[Pasos planificados],"&gt;0")</f>
         <v>11.481481481481481</v>
       </c>
       <c r="H9" cm="1">
-        <f t="array" ref="H9">_xlfn.STDEV.P(IF(data[Sesion]=A4,data[Num intentos]))</f>
+        <f t="array" ref="H9">_xlfn.STDEV.P(IF((data[Sesion]=A4)*(data[Pasos planificados]&lt;&gt;0),data[Num intentos]))</f>
         <v>5.3704980827726274</v>
       </c>
       <c r="I9">
-        <f>AVERAGEIF(data[Sesion],A4,data[Completados])</f>
+        <f>AVERAGEIFS(data[Completados],data[Sesion],A4,data[Pasos planificados],"&gt;0")</f>
         <v>1.7037037037037037</v>
       </c>
       <c r="J9" cm="1">
-        <f t="array" ref="J9">_xlfn.STDEV.P(IF(data[Sesion]=A4,data[Completados]))</f>
+        <f t="array" ref="J9">_xlfn.STDEV.P(IF((data[Sesion]=A4)*(data[Pasos planificados]&lt;&gt;0),data[Completados]))</f>
         <v>1.4609691054308163</v>
       </c>
       <c r="K9">
-        <f>AVERAGEIF(data[Sesion],A4,data[% Aciertos])</f>
+        <f>AVERAGEIFS(data[% Aciertos],data[Sesion],A4,data[Pasos planificados],"&gt;0")</f>
         <v>84.678266813816748</v>
       </c>
       <c r="L9" cm="1">
-        <f t="array" ref="L9">_xlfn.STDEV.P(IF(data[Sesion]=A4,data[% Aciertos]))</f>
+        <f t="array" ref="L9">_xlfn.STDEV.P(IF((data[Sesion]=A4)*(data[Pasos planificados]&lt;&gt;0),data[% Aciertos]))</f>
         <v>9.7359064227108103</v>
       </c>
       <c r="M9">
-        <f>AVERAGEIF(data[Sesion],A4,data[% Mal])</f>
+        <f>AVERAGEIFS(data[% Mal],data[Sesion],A4,data[Pasos planificados],"&gt;0")</f>
         <v>15.321733186183183</v>
       </c>
       <c r="N9" cm="1">
-        <f t="array" ref="N9">_xlfn.STDEV.P(IF(data[Sesion]=A4,data[% Mal]))</f>
+        <f t="array" ref="N9">_xlfn.STDEV.P(IF((data[Sesion]=A4)*(data[Pasos planificados]&lt;&gt;0),data[% Mal]))</f>
         <v>9.7359064227106646</v>
       </c>
     </row>
@@ -7900,55 +8607,55 @@
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.3">
       <c r="H12">
-        <f>SUMIF(data[Sesion],A2,data[Num intentos])</f>
-        <v>343</v>
+        <f>SUMIFS(data[Num intentos],data[Sesion],A2,data[Pasos planificados],"&gt;0")</f>
+        <v>289</v>
       </c>
       <c r="I12">
-        <f>SUMIF(data[Sesion],A2,data[Completados])</f>
+        <f>SUMIFS(data[Completados],data[Sesion],A2,data[Pasos planificados],"&gt;0")</f>
         <v>35</v>
       </c>
       <c r="J12">
         <f>100*I12/H12</f>
-        <v>10.204081632653061</v>
+        <v>12.110726643598616</v>
       </c>
       <c r="K12">
         <f>H12-I12</f>
-        <v>308</v>
+        <v>254</v>
       </c>
       <c r="L12">
         <f>100*K12/H12</f>
-        <v>89.795918367346943</v>
+        <v>87.889273356401389</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.3">
       <c r="H13">
-        <f>SUMIF(data[Sesion],A3,data[Num intentos])</f>
-        <v>14</v>
+        <f>SUMIFS(data[Num intentos],data[Sesion],A3,data[Pasos planificados],"&gt;0")</f>
+        <v>12</v>
       </c>
       <c r="I13">
-        <f>SUMIF(data[Sesion],A3,data[Completados])</f>
+        <f>SUMIFS(data[Completados],data[Sesion],A3,data[Pasos planificados],"&gt;0")</f>
         <v>2</v>
       </c>
       <c r="J13">
         <f t="shared" ref="J13:J14" si="0">100*I13/H13</f>
-        <v>14.285714285714286</v>
+        <v>16.666666666666668</v>
       </c>
       <c r="K13">
         <f t="shared" ref="K13:K14" si="1">H13-I13</f>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L13">
         <f t="shared" ref="L13:L14" si="2">100*K13/H13</f>
-        <v>85.714285714285708</v>
+        <v>83.333333333333329</v>
       </c>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.3">
       <c r="H14">
-        <f>SUMIF(data[Sesion],A4,data[Num intentos])</f>
+        <f>SUMIFS(data[Num intentos],data[Sesion],A4,data[Pasos planificados],"&gt;0")</f>
         <v>310</v>
       </c>
       <c r="I14">
-        <f>SUMIF(data[Sesion],A4,data[Completados])</f>
+        <f>SUMIFS(data[Completados],data[Sesion],A4,data[Pasos planificados],"&gt;0")</f>
         <v>46</v>
       </c>
       <c r="J14">

--- a/datosSesionesPruebaMedias.xlsx
+++ b/datosSesionesPruebaMedias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\hlocal\C_TFG\Datos\Mision Colombia-20260209T150018Z-3-001\jsonToCsv_TFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{733D5949-E9D4-4036-82D0-8D59C4F20B2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{266D01B4-6635-42CB-A21C-FED8AC6AA5A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8066,8 +8066,8 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <f>COUNTIF(data[Sesion],A2)</f>
-        <v>43</v>
+        <f>COUNTIFS(data[Sesion],A2,data[Pasos planificados],"&gt;0")</f>
+        <v>34</v>
       </c>
       <c r="C2">
         <f>AVERAGEIFS(data[Pasos planificados],data[Sesion],A2,data[Pasos planificados],"&gt;0")</f>
@@ -8179,8 +8179,8 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <f>COUNTIF(data[Sesion],A3)</f>
-        <v>4</v>
+        <f>COUNTIFS(data[Sesion],A3,data[Pasos planificados],"&gt;0")</f>
+        <v>2</v>
       </c>
       <c r="C3">
         <f>AVERAGEIFS(data[Pasos planificados],data[Sesion],A3,data[Pasos planificados],"&gt;0")</f>
@@ -8292,7 +8292,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <f>COUNTIF(data[Sesion],A4)</f>
+        <f>COUNTIFS(data[Sesion],A4,data[Pasos planificados],"&gt;0")</f>
         <v>27</v>
       </c>
       <c r="C4">

--- a/datosSesionesPruebaMedias.xlsx
+++ b/datosSesionesPruebaMedias.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\hlocal\C_TFG\Datos\Mision Colombia-20260209T150018Z-3-001\jsonToCsv_TFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{266D01B4-6635-42CB-A21C-FED8AC6AA5A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{387F6732-6879-460C-8DFA-A2D7D09E8A47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="233">
   <si>
     <t>ID</t>
   </si>
@@ -713,6 +713,54 @@
   </si>
   <si>
     <t>Stdev % errores</t>
+  </si>
+  <si>
+    <t>Stdev dormir planificado</t>
+  </si>
+  <si>
+    <t>Sesión</t>
+  </si>
+  <si>
+    <t>Media ubicación planificado</t>
+  </si>
+  <si>
+    <t>Stdev ubicación planificado</t>
+  </si>
+  <si>
+    <t>Media correctos ubicación</t>
+  </si>
+  <si>
+    <t>Stdev correctos ubicación</t>
+  </si>
+  <si>
+    <t>Media errores ubicación</t>
+  </si>
+  <si>
+    <t>Stdev errores ubicación</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Media duración</t>
+  </si>
+  <si>
+    <t>Stdev duración</t>
+  </si>
+  <si>
+    <t>Media número de niveles</t>
+  </si>
+  <si>
+    <t>Stdev número de niveles</t>
+  </si>
+  <si>
+    <t>Media número de intentos</t>
+  </si>
+  <si>
+    <t>Stdev número de intentos</t>
+  </si>
+  <si>
+    <t>Número de intentos</t>
+  </si>
+  <si>
+    <t>Número de completados</t>
   </si>
 </sst>
 </file>
@@ -733,15 +781,33 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -762,14 +828,38 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -7968,96 +8058,97 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0EE1E7D-EAFC-4A2F-AF1A-E8C144B15E47}">
-  <dimension ref="A1:AB14"/>
+  <dimension ref="A1:AB9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="11.88671875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11.6640625" customWidth="1"/>
+    <col min="17" max="17" width="14.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1" spans="1:28" ht="72" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="J1" t="s">
-        <v>178</v>
-      </c>
-      <c r="K1" t="s">
+      <c r="J1" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="K1" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="O1" t="s">
-        <v>183</v>
-      </c>
-      <c r="P1" t="s">
-        <v>184</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>185</v>
-      </c>
-      <c r="R1" t="s">
-        <v>186</v>
-      </c>
-      <c r="S1" t="s">
-        <v>187</v>
-      </c>
-      <c r="T1" t="s">
-        <v>188</v>
-      </c>
-      <c r="U1" t="s">
+      <c r="O1" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="Q1" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="R1" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="S1" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="T1" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="U1" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="V1" t="s">
+      <c r="V1" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="W1" t="s">
+      <c r="W1" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="X1" t="s">
+      <c r="X1" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Y1" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="Z1" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AA1" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AB1" s="3" t="s">
         <v>196</v>
       </c>
     </row>
@@ -8400,45 +8491,73 @@
         <v>1.8129241852622839</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="C6" t="s">
-        <v>197</v>
-      </c>
-      <c r="D6" t="s">
-        <v>198</v>
-      </c>
-      <c r="E6" t="s">
-        <v>199</v>
-      </c>
-      <c r="F6" t="s">
-        <v>200</v>
-      </c>
-      <c r="G6" t="s">
-        <v>201</v>
-      </c>
-      <c r="H6" t="s">
-        <v>202</v>
-      </c>
-      <c r="I6" t="s">
+    <row r="6" spans="1:28" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="I6" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="J6" t="s">
+      <c r="J6" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="K6" t="s">
+      <c r="K6" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="L6" t="s">
+      <c r="L6" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="M6" t="s">
+      <c r="M6" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="N6" t="s">
+      <c r="N6" s="3" t="s">
         <v>216</v>
       </c>
+      <c r="O6" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="P6" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="Q6" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="R6" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="S6" s="4" t="s">
+        <v>212</v>
+      </c>
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7">
+        <f>COUNTIFS(data[Sesion],A7,data[Pasos planificados],"&gt;0")</f>
+        <v>34</v>
+      </c>
       <c r="C7">
         <f>AVERAGEIFS(data[Tiempo duracion],data[Sesion],A2,data[Pasos planificados],"&gt;0")</f>
         <v>1499.0487352941179</v>
@@ -8487,8 +8606,35 @@
         <f t="array" ref="N7">_xlfn.STDEV.P(IF((data[Sesion]=A2)*(data[Pasos planificados]&lt;&gt;0),data[% Mal]))</f>
         <v>13.661094774056048</v>
       </c>
+      <c r="O7">
+        <f>SUMIFS(data[Num intentos],data[Sesion],A2,data[Pasos planificados],"&gt;0")</f>
+        <v>289</v>
+      </c>
+      <c r="P7">
+        <f>SUMIFS(data[Completados],data[Sesion],A2,data[Pasos planificados],"&gt;0")</f>
+        <v>35</v>
+      </c>
+      <c r="Q7">
+        <f>100*P7/O7</f>
+        <v>12.110726643598616</v>
+      </c>
+      <c r="R7">
+        <f>O7-P7</f>
+        <v>254</v>
+      </c>
+      <c r="S7">
+        <f>100*R7/O7</f>
+        <v>87.889273356401389</v>
+      </c>
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>2</v>
+      </c>
+      <c r="B8">
+        <f>COUNTIFS(data[Sesion],A8,data[Pasos planificados],"&gt;0")</f>
+        <v>2</v>
+      </c>
       <c r="C8">
         <f>AVERAGEIFS(data[Tiempo duracion],data[Sesion],A3,data[Pasos planificados],"&gt;0")</f>
         <v>865.94650000000001</v>
@@ -8537,8 +8683,35 @@
         <f t="array" ref="N8">_xlfn.STDEV.P(IF((data[Sesion]=A3)*(data[Pasos planificados]&lt;&gt;0),data[% Mal]))</f>
         <v>10.439560439560402</v>
       </c>
+      <c r="O8">
+        <f>SUMIFS(data[Num intentos],data[Sesion],A3,data[Pasos planificados],"&gt;0")</f>
+        <v>12</v>
+      </c>
+      <c r="P8">
+        <f>SUMIFS(data[Completados],data[Sesion],A3,data[Pasos planificados],"&gt;0")</f>
+        <v>2</v>
+      </c>
+      <c r="Q8">
+        <f t="shared" ref="Q8:Q9" si="0">100*P8/O8</f>
+        <v>16.666666666666668</v>
+      </c>
+      <c r="R8">
+        <f t="shared" ref="R8:R9" si="1">O8-P8</f>
+        <v>10</v>
+      </c>
+      <c r="S8">
+        <f t="shared" ref="S8:S9" si="2">100*R8/O8</f>
+        <v>83.333333333333329</v>
+      </c>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>3</v>
+      </c>
+      <c r="B9">
+        <f>COUNTIFS(data[Sesion],A9,data[Pasos planificados],"&gt;0")</f>
+        <v>27</v>
+      </c>
       <c r="C9">
         <f>AVERAGEIFS(data[Tiempo duracion],data[Sesion],A4,data[Pasos planificados],"&gt;0")</f>
         <v>2271.3278518518518</v>
@@ -8587,87 +8760,24 @@
         <f t="array" ref="N9">_xlfn.STDEV.P(IF((data[Sesion]=A4)*(data[Pasos planificados]&lt;&gt;0),data[% Mal]))</f>
         <v>9.7359064227106646</v>
       </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="H11" t="s">
-        <v>3</v>
-      </c>
-      <c r="I11" t="s">
-        <v>209</v>
-      </c>
-      <c r="J11" t="s">
-        <v>210</v>
-      </c>
-      <c r="K11" t="s">
-        <v>211</v>
-      </c>
-      <c r="L11" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="H12">
-        <f>SUMIFS(data[Num intentos],data[Sesion],A2,data[Pasos planificados],"&gt;0")</f>
-        <v>289</v>
-      </c>
-      <c r="I12">
-        <f>SUMIFS(data[Completados],data[Sesion],A2,data[Pasos planificados],"&gt;0")</f>
-        <v>35</v>
-      </c>
-      <c r="J12">
-        <f>100*I12/H12</f>
-        <v>12.110726643598616</v>
-      </c>
-      <c r="K12">
-        <f>H12-I12</f>
-        <v>254</v>
-      </c>
-      <c r="L12">
-        <f>100*K12/H12</f>
-        <v>87.889273356401389</v>
-      </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="H13">
-        <f>SUMIFS(data[Num intentos],data[Sesion],A3,data[Pasos planificados],"&gt;0")</f>
-        <v>12</v>
-      </c>
-      <c r="I13">
-        <f>SUMIFS(data[Completados],data[Sesion],A3,data[Pasos planificados],"&gt;0")</f>
-        <v>2</v>
-      </c>
-      <c r="J13">
-        <f t="shared" ref="J13:J14" si="0">100*I13/H13</f>
-        <v>16.666666666666668</v>
-      </c>
-      <c r="K13">
-        <f t="shared" ref="K13:K14" si="1">H13-I13</f>
-        <v>10</v>
-      </c>
-      <c r="L13">
-        <f t="shared" ref="L13:L14" si="2">100*K13/H13</f>
-        <v>83.333333333333329</v>
-      </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="H14">
+      <c r="O9">
         <f>SUMIFS(data[Num intentos],data[Sesion],A4,data[Pasos planificados],"&gt;0")</f>
         <v>310</v>
       </c>
-      <c r="I14">
+      <c r="P9">
         <f>SUMIFS(data[Completados],data[Sesion],A4,data[Pasos planificados],"&gt;0")</f>
         <v>46</v>
       </c>
-      <c r="J14">
+      <c r="Q9">
         <f t="shared" si="0"/>
         <v>14.838709677419354</v>
       </c>
-      <c r="K14">
+      <c r="R9">
         <f t="shared" si="1"/>
         <v>264</v>
       </c>
-      <c r="L14">
-        <f t="shared" si="2"/>
+      <c r="S9">
+        <f>100*R9/O9</f>
         <v>85.161290322580641</v>
       </c>
     </row>

--- a/datosSesionesPruebaMedias.xlsx
+++ b/datosSesionesPruebaMedias.xlsx
@@ -8700,7 +8700,7 @@
         <v>10</v>
       </c>
       <c r="S8">
-        <f t="shared" ref="S8:S9" si="2">100*R8/O8</f>
+        <f t="shared" ref="S8" si="2">100*R8/O8</f>
         <v>83.333333333333329</v>
       </c>
     </row>
